--- a/chromite-quarry-feasibility/Chromite-Quarry-Feasibility-Monthly-Production.xlsx
+++ b/chromite-quarry-feasibility/Chromite-Quarry-Feasibility-Monthly-Production.xlsx
@@ -68,6 +68,8 @@
     <definedName name="K_NPV">'المؤشرات المالية'!$B$6</definedName>
     <definedName name="K_NPVNew">'المؤشرات المالية'!$B$12</definedName>
     <definedName name="K_Payback">'المؤشرات المالية'!$B$8</definedName>
+    <definedName name="LocalPrice">'السوق والسعر'!$B$38</definedName>
+    <definedName name="LocalShare">'السوق والسعر'!$B$39</definedName>
     <definedName name="LicFees">التراخيص!$D$10</definedName>
     <definedName name="LicRenew">الافتراضات!$B$53</definedName>
     <definedName name="Loan">الافتراضات!$B$55</definedName>
@@ -96,7 +98,7 @@
     <definedName name="ROMCap">'الخطة الفنية والإنتاج'!$C$8</definedName>
     <definedName name="RoyaltyRate">الافتراضات!$B$31</definedName>
     <definedName name="SaleCap">'الخطة الفنية والإنتاج'!$C$10</definedName>
-    <definedName name="SalePrice">'السوق والسعر'!$B$32</definedName>
+    <definedName name="SalePrice">'السوق والسعر'!$B$41</definedName>
     <definedName name="SeaFreight">الافتراضات!$B$23</definedName>
     <definedName name="ShiftHrs">الافتراضات!$B$17</definedName>
     <definedName name="SiteRent">الإيجارات!$E$9</definedName>
@@ -5758,8 +5760,10 @@
       <c r="B11" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="9" t="s">
-        <v>14</v>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>بيانات السوق والأسعار المرجعية، وبناء سعر التصدير، والبيع المحلي وسعر البيع المعتمد</t>
+        </is>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.2">
@@ -6489,7 +6493,7 @@
       </c>
       <c r="B22" s="19">
         <f>B20/(B20+B21)</f>
-        <v>0.45454545454545453</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>72</v>
@@ -6578,7 +6582,7 @@
       </c>
       <c r="B31" s="11">
         <f>B24*SPFEx</f>
-        <v>871.19999999999993</v>
+        <v>871.2</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>75</v>
@@ -6614,7 +6618,7 @@
       </c>
       <c r="B34" s="12">
         <f>SUM(B30:B33)</f>
-        <v>17419.800000000003</v>
+        <v>17419.8</v>
       </c>
       <c r="C34" s="29"/>
     </row>
@@ -7063,7 +7067,7 @@
       </c>
       <c r="F6" s="11">
         <f>E6*DieselPrice</f>
-        <v>26006.400000000001</v>
+        <v>26006.4</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>541</v>
@@ -7093,7 +7097,7 @@
       </c>
       <c r="F7" s="11">
         <f>E7*DieselPrice</f>
-        <v>8359.2000000000007</v>
+        <v>8359.2</v>
       </c>
       <c r="G7" s="7" t="s">
         <v>541</v>
@@ -7121,7 +7125,7 @@
       </c>
       <c r="F8" s="11">
         <f>E8*DieselPrice</f>
-        <v>7430.4000000000005</v>
+        <v>7430.4</v>
       </c>
       <c r="G8" s="7" t="s">
         <v>541</v>
@@ -7228,7 +7232,7 @@
       </c>
       <c r="F12" s="12">
         <f>SUM(F6:F11)</f>
-        <v>50604.12000000001</v>
+        <v>50604.12</v>
       </c>
       <c r="G12" s="29"/>
       <c r="H12" s="29"/>
@@ -7259,7 +7263,7 @@
       <c r="E14" s="9"/>
       <c r="F14" s="11">
         <f>C14*F12</f>
-        <v>5060.4120000000012</v>
+        <v>5060.412</v>
       </c>
       <c r="G14" s="7" t="s">
         <v>541</v>
@@ -7393,7 +7397,7 @@
       <c r="E20" s="29"/>
       <c r="F20" s="12">
         <f>F12+SUM(F14:F19)</f>
-        <v>74924.532000000007</v>
+        <v>74924.532</v>
       </c>
       <c r="G20" s="29"/>
       <c r="H20" s="29"/>
@@ -7404,7 +7408,7 @@
       </c>
       <c r="F21" s="11">
         <f>SUMIF(G6:G19,"متغير",F6:F19)</f>
-        <v>62660.412000000011</v>
+        <v>62660.412</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
@@ -7413,7 +7417,7 @@
       </c>
       <c r="F22" s="11">
         <f>SUMIF(G6:G19,"ثابت",F6:F19)</f>
-        <v>12264.119999999999</v>
+        <v>12264.12</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
@@ -7568,43 +7572,43 @@
       <c r="C6" s="18"/>
       <c r="D6" s="18">
         <f>SalePrice*F_Price*(1+PriceG)^(D$4-1)</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="E6" s="18">
         <f>SalePrice*F_Price*(1+PriceG)^(E$4-1)</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="F6" s="18">
         <f>SalePrice*F_Price*(1+PriceG)^(F$4-1)</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="G6" s="18">
         <f>SalePrice*F_Price*(1+PriceG)^(G$4-1)</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="H6" s="18">
         <f>SalePrice*F_Price*(1+PriceG)^(H$4-1)</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="I6" s="18">
         <f>SalePrice*F_Price*(1+PriceG)^(I$4-1)</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="J6" s="18">
         <f>SalePrice*F_Price*(1+PriceG)^(J$4-1)</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="K6" s="18">
         <f>SalePrice*F_Price*(1+PriceG)^(K$4-1)</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="L6" s="18">
         <f>SalePrice*F_Price*(1+PriceG)^(L$4-1)</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="M6" s="18">
         <f>SalePrice*F_Price*(1+PriceG)^(M$4-1)</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="N6" s="18"/>
     </row>
@@ -7618,47 +7622,47 @@
       <c r="C7" s="12"/>
       <c r="D7" s="13">
         <f t="shared" ref="D7:M7" si="0">D5*D6</f>
-        <v>393749.3619612903</v>
+        <v>322037.8</v>
       </c>
       <c r="E7" s="13">
         <f t="shared" si="0"/>
-        <v>506249.17966451612</v>
+        <v>414048.6</v>
       </c>
       <c r="F7" s="13">
         <f t="shared" si="0"/>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="G7" s="13">
         <f t="shared" si="0"/>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="H7" s="13">
         <f t="shared" si="0"/>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="J7" s="13">
         <f t="shared" si="0"/>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="K7" s="13">
         <f t="shared" si="0"/>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="0"/>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="M7" s="13">
         <f t="shared" si="0"/>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="N7" s="12">
         <f>SUM(D7:M7)</f>
-        <v>5399991.2497548396</v>
+        <v>4416518.4</v>
       </c>
     </row>
   </sheetData>
@@ -7753,39 +7757,39 @@
       </c>
       <c r="E5" s="44">
         <f>(1+InflRate)^(E$4-1)</f>
-        <v>1.0149999999999999</v>
+        <v>1.015</v>
       </c>
       <c r="F5" s="44">
         <f>(1+InflRate)^(F$4-1)</f>
-        <v>1.0302249999999997</v>
+        <v>1.030225</v>
       </c>
       <c r="G5" s="44">
         <f>(1+InflRate)^(G$4-1)</f>
-        <v>1.0456783749999996</v>
+        <v>1.045678375</v>
       </c>
       <c r="H5" s="44">
         <f>(1+InflRate)^(H$4-1)</f>
-        <v>1.0613635506249994</v>
+        <v>1.061363550625</v>
       </c>
       <c r="I5" s="44">
         <f>(1+InflRate)^(I$4-1)</f>
-        <v>1.0772840038843743</v>
+        <v>1.07728400388437</v>
       </c>
       <c r="J5" s="44">
         <f>(1+InflRate)^(J$4-1)</f>
-        <v>1.0934432639426397</v>
+        <v>1.09344326394264</v>
       </c>
       <c r="K5" s="44">
         <f>(1+InflRate)^(K$4-1)</f>
-        <v>1.1098449129017791</v>
+        <v>1.10984491290178</v>
       </c>
       <c r="L5" s="44">
         <f>(1+InflRate)^(L$4-1)</f>
-        <v>1.1264925865953057</v>
+        <v>1.12649258659531</v>
       </c>
       <c r="M5" s="44">
         <f>(1+InflRate)^(M$4-1)</f>
-        <v>1.1433899753942351</v>
+        <v>1.14338997539424</v>
       </c>
       <c r="N5" s="11"/>
     </row>
@@ -7871,43 +7875,43 @@
       </c>
       <c r="E8" s="11">
         <f>Payroll*E$5*F_Opex</f>
-        <v>93420.599999999991</v>
+        <v>93420.6</v>
       </c>
       <c r="F8" s="11">
         <f>Payroll*F$5*F_Opex</f>
-        <v>94821.908999999971</v>
+        <v>94821.909</v>
       </c>
       <c r="G8" s="11">
         <f>Payroll*G$5*F_Opex</f>
-        <v>96244.237634999969</v>
+        <v>96244.237635</v>
       </c>
       <c r="H8" s="11">
         <f>Payroll*H$5*F_Opex</f>
-        <v>97687.901199524946</v>
+        <v>97687.901199525</v>
       </c>
       <c r="I8" s="11">
         <f>Payroll*I$5*F_Opex</f>
-        <v>99153.219717517815</v>
+        <v>99153.2197175178</v>
       </c>
       <c r="J8" s="11">
         <f>Payroll*J$5*F_Opex</f>
-        <v>100640.51801328055</v>
+        <v>100640.518013281</v>
       </c>
       <c r="K8" s="11">
         <f>Payroll*K$5*F_Opex</f>
-        <v>102150.12578347974</v>
+        <v>102150.12578348</v>
       </c>
       <c r="L8" s="11">
         <f>Payroll*L$5*F_Opex</f>
-        <v>103682.37767023194</v>
+        <v>103682.377670232</v>
       </c>
       <c r="M8" s="11">
         <f>Payroll*M$5*F_Opex</f>
-        <v>105237.61333528541</v>
+        <v>105237.613335285</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" ref="N8:N12" si="0">SUM(D8:M8)</f>
-        <v>985078.50235432049</v>
+        <v>985078.502354321</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -7920,11 +7924,11 @@
       <c r="C9" s="11"/>
       <c r="D9" s="11">
         <f>StaffOnCost*D$5*F_Opex</f>
-        <v>17419.800000000003</v>
+        <v>17419.8</v>
       </c>
       <c r="E9" s="11">
         <f>StaffOnCost*E$5*F_Opex</f>
-        <v>17681.097000000002</v>
+        <v>17681.097</v>
       </c>
       <c r="F9" s="11">
         <f>StaffOnCost*F$5*F_Opex</f>
@@ -7932,35 +7936,35 @@
       </c>
       <c r="G9" s="11">
         <f>StaffOnCost*G$5*F_Opex</f>
-        <v>18215.508156824995</v>
+        <v>18215.508156825</v>
       </c>
       <c r="H9" s="11">
         <f>StaffOnCost*H$5*F_Opex</f>
-        <v>18488.740779177369</v>
+        <v>18488.7407791774</v>
       </c>
       <c r="I9" s="11">
         <f>StaffOnCost*I$5*F_Opex</f>
-        <v>18766.071890865027</v>
+        <v>18766.071890865</v>
       </c>
       <c r="J9" s="11">
         <f>StaffOnCost*J$5*F_Opex</f>
-        <v>19047.562969227998</v>
+        <v>19047.562969228</v>
       </c>
       <c r="K9" s="11">
         <f>StaffOnCost*K$5*F_Opex</f>
-        <v>19333.276413766416</v>
+        <v>19333.2764137664</v>
       </c>
       <c r="L9" s="11">
         <f>StaffOnCost*L$5*F_Opex</f>
-        <v>19623.27555997291</v>
+        <v>19623.2755599729</v>
       </c>
       <c r="M9" s="11">
         <f>StaffOnCost*M$5*F_Opex</f>
-        <v>19917.624693372501</v>
+        <v>19917.6246933725</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="0"/>
-        <v>186439.27091820721</v>
+        <v>186439.270918207</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -7977,43 +7981,43 @@
       </c>
       <c r="E10" s="11">
         <f>SiteRent*E$5*F_Opex</f>
-        <v>10352.999999999998</v>
+        <v>10353</v>
       </c>
       <c r="F10" s="11">
         <f>SiteRent*F$5*F_Opex</f>
-        <v>10508.294999999996</v>
+        <v>10508.295</v>
       </c>
       <c r="G10" s="11">
         <f>SiteRent*G$5*F_Opex</f>
-        <v>10665.919424999996</v>
+        <v>10665.919425</v>
       </c>
       <c r="H10" s="11">
         <f>SiteRent*H$5*F_Opex</f>
-        <v>10825.908216374994</v>
+        <v>10825.908216375</v>
       </c>
       <c r="I10" s="11">
         <f>SiteRent*I$5*F_Opex</f>
-        <v>10988.296839620618</v>
+        <v>10988.2968396206</v>
       </c>
       <c r="J10" s="11">
         <f>SiteRent*J$5*F_Opex</f>
-        <v>11153.121292214924</v>
+        <v>11153.1212922149</v>
       </c>
       <c r="K10" s="11">
         <f>SiteRent*K$5*F_Opex</f>
-        <v>11320.418111598146</v>
+        <v>11320.4181115982</v>
       </c>
       <c r="L10" s="11">
         <f>SiteRent*L$5*F_Opex</f>
-        <v>11490.224383272118</v>
+        <v>11490.2243832721</v>
       </c>
       <c r="M10" s="11">
         <f>SiteRent*M$5*F_Opex</f>
-        <v>11662.577749021199</v>
+        <v>11662.5777490212</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="0"/>
-        <v>109167.76101710199</v>
+        <v>109167.761017102</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -8034,39 +8038,39 @@
       </c>
       <c r="F11" s="11">
         <f>EquipRent*F$5*F_Opex</f>
-        <v>67376.714999999982</v>
+        <v>67376.715</v>
       </c>
       <c r="G11" s="11">
         <f>EquipRent*G$5*F_Opex</f>
-        <v>68387.365724999967</v>
+        <v>68387.365725</v>
       </c>
       <c r="H11" s="11">
         <f>EquipRent*H$5*F_Opex</f>
-        <v>69413.176210874968</v>
+        <v>69413.176210875</v>
       </c>
       <c r="I11" s="11">
         <f>EquipRent*I$5*F_Opex</f>
-        <v>70454.373854038073</v>
+        <v>70454.3738540381</v>
       </c>
       <c r="J11" s="11">
         <f>EquipRent*J$5*F_Opex</f>
-        <v>71511.18946184864</v>
+        <v>71511.1894618487</v>
       </c>
       <c r="K11" s="11">
         <f>EquipRent*K$5*F_Opex</f>
-        <v>72583.857303776356</v>
+        <v>72583.8573037764</v>
       </c>
       <c r="L11" s="11">
         <f>EquipRent*L$5*F_Opex</f>
-        <v>73672.615163332986</v>
+        <v>73672.615163333</v>
       </c>
       <c r="M11" s="11">
         <f>EquipRent*M$5*F_Opex</f>
-        <v>74777.704390782979</v>
+        <v>74777.704390783</v>
       </c>
       <c r="N11" s="12">
         <f t="shared" si="0"/>
-        <v>699957.99710965401</v>
+        <v>699957.997109654</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.2">
@@ -8079,47 +8083,47 @@
       <c r="C12" s="11"/>
       <c r="D12" s="11">
         <f>ConsFix*D$5*F_Opex</f>
-        <v>12264.119999999999</v>
+        <v>12264.12</v>
       </c>
       <c r="E12" s="11">
         <f>ConsFix*E$5*F_Opex</f>
-        <v>12448.081799999998</v>
+        <v>12448.0818</v>
       </c>
       <c r="F12" s="11">
         <f>ConsFix*F$5*F_Opex</f>
-        <v>12634.803026999996</v>
+        <v>12634.803027</v>
       </c>
       <c r="G12" s="11">
         <f>ConsFix*G$5*F_Opex</f>
-        <v>12824.325072404994</v>
+        <v>12824.325072405</v>
       </c>
       <c r="H12" s="11">
         <f>ConsFix*H$5*F_Opex</f>
-        <v>13016.689948491066</v>
+        <v>13016.6899484911</v>
       </c>
       <c r="I12" s="11">
         <f>ConsFix*I$5*F_Opex</f>
-        <v>13211.940297718431</v>
+        <v>13211.9402977184</v>
       </c>
       <c r="J12" s="11">
         <f>ConsFix*J$5*F_Opex</f>
-        <v>13410.119402184206</v>
+        <v>13410.1194021842</v>
       </c>
       <c r="K12" s="11">
         <f>ConsFix*K$5*F_Opex</f>
-        <v>13611.271193216966</v>
+        <v>13611.271193217</v>
       </c>
       <c r="L12" s="11">
         <f>ConsFix*L$5*F_Opex</f>
-        <v>13815.44026111522</v>
+        <v>13815.4402611152</v>
       </c>
       <c r="M12" s="11">
         <f>ConsFix*M$5*F_Opex</f>
-        <v>14022.671865031945</v>
+        <v>14022.671865032</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="0"/>
-        <v>131259.46286716283</v>
+        <v>131259.462867163</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -8180,39 +8184,39 @@
       </c>
       <c r="F14" s="11">
         <f>'الأصول والإهلاك'!$D$5*F13*F$5*F_Opex</f>
-        <v>8859.9349999999977</v>
+        <v>8859.935</v>
       </c>
       <c r="G14" s="11">
         <f>'الأصول والإهلاك'!$D$5*G13*G$5*F_Opex</f>
-        <v>13489.251037499995</v>
+        <v>13489.2510375</v>
       </c>
       <c r="H14" s="11">
         <f>'الأصول والإهلاك'!$D$5*H13*H$5*F_Opex</f>
-        <v>13691.589803062492</v>
+        <v>13691.5898030625</v>
       </c>
       <c r="I14" s="11">
         <f>'الأصول والإهلاك'!$D$5*I13*I$5*F_Opex</f>
-        <v>13896.963650108428</v>
+        <v>13896.9636501084</v>
       </c>
       <c r="J14" s="11">
         <f>'الأصول والإهلاك'!$D$5*J13*J$5*F_Opex</f>
-        <v>18807.224139813403</v>
+        <v>18807.2241398134</v>
       </c>
       <c r="K14" s="11">
         <f>'الأصول والإهلاك'!$D$5*K13*K$5*F_Opex</f>
-        <v>19089.332501910601</v>
+        <v>19089.3325019106</v>
       </c>
       <c r="L14" s="11">
         <f>'الأصول والإهلاك'!$D$5*L13*L$5*F_Opex</f>
-        <v>19375.672489439257</v>
+        <v>19375.6724894393</v>
       </c>
       <c r="M14" s="11">
         <f>'الأصول والإهلاك'!$D$5*M13*M$5*F_Opex</f>
-        <v>19666.307576780844</v>
+        <v>19666.3075767809</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" ref="N14:N23" si="1">SUM(D14:M14)</f>
-        <v>144205.27619861503</v>
+        <v>144205.276198615</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -8282,43 +8286,43 @@
       </c>
       <c r="E16" s="11">
         <f>LicRenew*E$5*F_Opex</f>
-        <v>1623.9999999999998</v>
+        <v>1624</v>
       </c>
       <c r="F16" s="11">
         <f>LicRenew*F$5*F_Opex</f>
-        <v>1648.3599999999997</v>
+        <v>1648.36</v>
       </c>
       <c r="G16" s="11">
         <f>LicRenew*G$5*F_Opex</f>
-        <v>1673.0853999999995</v>
+        <v>1673.0854</v>
       </c>
       <c r="H16" s="11">
         <f>LicRenew*H$5*F_Opex</f>
-        <v>1698.1816809999991</v>
+        <v>1698.181681</v>
       </c>
       <c r="I16" s="11">
         <f>LicRenew*I$5*F_Opex</f>
-        <v>1723.6544062149987</v>
+        <v>1723.654406215</v>
       </c>
       <c r="J16" s="11">
         <f>LicRenew*J$5*F_Opex</f>
-        <v>1749.5092223082236</v>
+        <v>1749.50922230822</v>
       </c>
       <c r="K16" s="11">
         <f>LicRenew*K$5*F_Opex</f>
-        <v>1775.7518606428466</v>
+        <v>1775.75186064285</v>
       </c>
       <c r="L16" s="11">
         <f>LicRenew*L$5*F_Opex</f>
-        <v>1802.3881385524892</v>
+        <v>1802.38813855249</v>
       </c>
       <c r="M16" s="11">
         <f>LicRenew*M$5*F_Opex</f>
-        <v>1829.4239606307763</v>
+        <v>1829.42396063078</v>
       </c>
       <c r="N16" s="12">
         <f t="shared" si="1"/>
-        <v>17124.354669349334</v>
+        <v>17124.3546693493</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -8388,43 +8392,43 @@
       </c>
       <c r="E18" s="11">
         <f>GenAdmin*E$5*F_Opex</f>
-        <v>4871.9999999999991</v>
+        <v>4872</v>
       </c>
       <c r="F18" s="11">
         <f>GenAdmin*F$5*F_Opex</f>
-        <v>4945.079999999999</v>
+        <v>4945.08</v>
       </c>
       <c r="G18" s="11">
         <f>GenAdmin*G$5*F_Opex</f>
-        <v>5019.256199999998</v>
+        <v>5019.2562</v>
       </c>
       <c r="H18" s="11">
         <f>GenAdmin*H$5*F_Opex</f>
-        <v>5094.5450429999973</v>
+        <v>5094.545043</v>
       </c>
       <c r="I18" s="11">
         <f>GenAdmin*I$5*F_Opex</f>
-        <v>5170.9632186449962</v>
+        <v>5170.963218645</v>
       </c>
       <c r="J18" s="11">
         <f>GenAdmin*J$5*F_Opex</f>
-        <v>5248.5276669246705</v>
+        <v>5248.52766692467</v>
       </c>
       <c r="K18" s="11">
         <f>GenAdmin*K$5*F_Opex</f>
-        <v>5327.2555819285399</v>
+        <v>5327.25558192854</v>
       </c>
       <c r="L18" s="11">
         <f>GenAdmin*L$5*F_Opex</f>
-        <v>5407.1644156574675</v>
+        <v>5407.16441565747</v>
       </c>
       <c r="M18" s="11">
         <f>GenAdmin*M$5*F_Opex</f>
-        <v>5488.2718818923286</v>
+        <v>5488.27188189233</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" si="1"/>
-        <v>51373.064008048008</v>
+        <v>51373.064008048</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -8441,43 +8445,43 @@
       </c>
       <c r="E19" s="11">
         <f>Utilities*E$5*F_Opex</f>
-        <v>1826.9999999999998</v>
+        <v>1827</v>
       </c>
       <c r="F19" s="11">
         <f>Utilities*F$5*F_Opex</f>
-        <v>1854.4049999999995</v>
+        <v>1854.405</v>
       </c>
       <c r="G19" s="11">
         <f>Utilities*G$5*F_Opex</f>
-        <v>1882.2210749999992</v>
+        <v>1882.221075</v>
       </c>
       <c r="H19" s="11">
         <f>Utilities*H$5*F_Opex</f>
-        <v>1910.4543911249989</v>
+        <v>1910.454391125</v>
       </c>
       <c r="I19" s="11">
         <f>Utilities*I$5*F_Opex</f>
-        <v>1939.1112069918738</v>
+        <v>1939.11120699187</v>
       </c>
       <c r="J19" s="11">
         <f>Utilities*J$5*F_Opex</f>
-        <v>1968.1978750967514</v>
+        <v>1968.19787509675</v>
       </c>
       <c r="K19" s="11">
         <f>Utilities*K$5*F_Opex</f>
-        <v>1997.7208432232023</v>
+        <v>1997.7208432232</v>
       </c>
       <c r="L19" s="11">
         <f>Utilities*L$5*F_Opex</f>
-        <v>2027.6866558715503</v>
+        <v>2027.68665587155</v>
       </c>
       <c r="M19" s="11">
         <f>Utilities*M$5*F_Opex</f>
-        <v>2058.1019557096233</v>
+        <v>2058.10195570962</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="1"/>
-        <v>19264.899003017999</v>
+        <v>19264.899003018</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -8494,43 +8498,43 @@
       </c>
       <c r="E20" s="11">
         <f>AssayCost*E$5*F_Opex</f>
-        <v>2435.9999999999995</v>
+        <v>2436</v>
       </c>
       <c r="F20" s="11">
         <f>AssayCost*F$5*F_Opex</f>
-        <v>2472.5399999999995</v>
+        <v>2472.54</v>
       </c>
       <c r="G20" s="11">
         <f>AssayCost*G$5*F_Opex</f>
-        <v>2509.628099999999</v>
+        <v>2509.6281</v>
       </c>
       <c r="H20" s="11">
         <f>AssayCost*H$5*F_Opex</f>
-        <v>2547.2725214999987</v>
+        <v>2547.2725215</v>
       </c>
       <c r="I20" s="11">
         <f>AssayCost*I$5*F_Opex</f>
-        <v>2585.4816093224981</v>
+        <v>2585.4816093225</v>
       </c>
       <c r="J20" s="11">
         <f>AssayCost*J$5*F_Opex</f>
-        <v>2624.2638334623352</v>
+        <v>2624.26383346234</v>
       </c>
       <c r="K20" s="11">
         <f>AssayCost*K$5*F_Opex</f>
-        <v>2663.6277909642699</v>
+        <v>2663.62779096427</v>
       </c>
       <c r="L20" s="11">
         <f>AssayCost*L$5*F_Opex</f>
-        <v>2703.5822078287338</v>
+        <v>2703.58220782873</v>
       </c>
       <c r="M20" s="11">
         <f>AssayCost*M$5*F_Opex</f>
-        <v>2744.1359409461643</v>
+        <v>2744.13594094617</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="1"/>
-        <v>25686.532004024004</v>
+        <v>25686.532004024</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -8600,43 +8604,43 @@
       </c>
       <c r="E22" s="11">
         <f>RehabCost*E$5*F_Opex</f>
-        <v>2537.4999999999995</v>
+        <v>2537.5</v>
       </c>
       <c r="F22" s="11">
         <f>RehabCost*F$5*F_Opex</f>
-        <v>2575.5624999999991</v>
+        <v>2575.5625</v>
       </c>
       <c r="G22" s="11">
         <f>RehabCost*G$5*F_Opex</f>
-        <v>2614.1959374999992</v>
+        <v>2614.1959375</v>
       </c>
       <c r="H22" s="11">
         <f>RehabCost*H$5*F_Opex</f>
-        <v>2653.4088765624988</v>
+        <v>2653.4088765625</v>
       </c>
       <c r="I22" s="11">
         <f>RehabCost*I$5*F_Opex</f>
-        <v>2693.2100097109355</v>
+        <v>2693.21000971094</v>
       </c>
       <c r="J22" s="11">
         <f>RehabCost*J$5*F_Opex</f>
-        <v>2733.6081598565993</v>
+        <v>2733.6081598566</v>
       </c>
       <c r="K22" s="11">
         <f>RehabCost*K$5*F_Opex</f>
-        <v>2774.6122822544476</v>
+        <v>2774.61228225445</v>
       </c>
       <c r="L22" s="11">
         <f>RehabCost*L$5*F_Opex</f>
-        <v>2816.2314664882642</v>
+        <v>2816.23146648827</v>
       </c>
       <c r="M22" s="11">
         <f>RehabCost*M$5*F_Opex</f>
-        <v>2858.4749384855877</v>
+        <v>2858.47493848559</v>
       </c>
       <c r="N22" s="12">
         <f t="shared" si="1"/>
-        <v>26756.804170858333</v>
+        <v>26756.8041708583</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
@@ -8649,47 +8653,47 @@
       <c r="C23" s="11"/>
       <c r="D23" s="12">
         <f t="shared" ref="D23:M23" si="2">SUM(D8:D12)+SUM(D14:D22)</f>
-        <v>223073.91999999998</v>
+        <v>223073.92</v>
       </c>
       <c r="E23" s="12">
         <f t="shared" si="2"/>
-        <v>226359.27879999997</v>
+        <v>226359.2788</v>
       </c>
       <c r="F23" s="12">
         <f t="shared" si="2"/>
-        <v>232405.91798199993</v>
+        <v>232405.917982</v>
       </c>
       <c r="G23" s="12">
         <f t="shared" si="2"/>
-        <v>237574.99376422993</v>
+        <v>237574.99376423</v>
       </c>
       <c r="H23" s="12">
         <f t="shared" si="2"/>
-        <v>243789.86867069334</v>
+        <v>243789.868670693</v>
       </c>
       <c r="I23" s="12">
         <f t="shared" si="2"/>
-        <v>244633.28670075367</v>
+        <v>244633.286700754</v>
       </c>
       <c r="J23" s="12">
         <f t="shared" si="2"/>
-        <v>255655.84203621832</v>
+        <v>255655.842036218</v>
       </c>
       <c r="K23" s="12">
         <f t="shared" si="2"/>
-        <v>256677.24966676152</v>
+        <v>256677.249666762</v>
       </c>
       <c r="L23" s="12">
         <f t="shared" si="2"/>
-        <v>263178.65841176297</v>
+        <v>263178.658411763</v>
       </c>
       <c r="M23" s="12">
         <f t="shared" si="2"/>
-        <v>264312.90828793938</v>
+        <v>264312.908287939</v>
       </c>
       <c r="N23" s="12">
         <f t="shared" si="1"/>
-        <v>2447661.9243203588</v>
+        <v>2447661.92432036</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.2">
@@ -8720,47 +8724,47 @@
       <c r="C25" s="11"/>
       <c r="D25" s="11">
         <f>ConsVar*D6*D$5*F_Opex</f>
-        <v>43862.288400000005</v>
+        <v>43862.2884</v>
       </c>
       <c r="E25" s="11">
         <f>ConsVar*E6*E$5*F_Opex</f>
-        <v>57240.286362000006</v>
+        <v>57240.286362</v>
       </c>
       <c r="F25" s="11">
         <f>ConsVar*F6*F$5*F_Opex</f>
-        <v>64554.322952699993</v>
+        <v>64554.3229527</v>
       </c>
       <c r="G25" s="11">
         <f>ConsVar*G6*G$5*F_Opex</f>
-        <v>65522.637796990486</v>
+        <v>65522.6377969905</v>
       </c>
       <c r="H25" s="11">
         <f>ConsVar*H6*H$5*F_Opex</f>
-        <v>66505.477363945334</v>
+        <v>66505.4773639453</v>
       </c>
       <c r="I25" s="11">
         <f>ConsVar*I6*I$5*F_Opex</f>
-        <v>67503.059524404511</v>
+        <v>67503.0595244045</v>
       </c>
       <c r="J25" s="11">
         <f>ConsVar*J6*J$5*F_Opex</f>
-        <v>68515.605417270563</v>
+        <v>68515.6054172706</v>
       </c>
       <c r="K25" s="11">
         <f>ConsVar*K6*K$5*F_Opex</f>
-        <v>69543.339498529604</v>
+        <v>69543.3394985296</v>
       </c>
       <c r="L25" s="11">
         <f>ConsVar*L6*L$5*F_Opex</f>
-        <v>70586.489591007543</v>
+        <v>70586.4895910076</v>
       </c>
       <c r="M25" s="11">
         <f>ConsVar*M6*M$5*F_Opex</f>
-        <v>71645.286934872653</v>
+        <v>71645.2869348727</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" ref="N25:N29" si="3">SUM(D25:M25)</f>
-        <v>645478.79384172068</v>
+        <v>645478.793841721</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -8773,47 +8777,47 @@
       <c r="C26" s="11"/>
       <c r="D26" s="11">
         <f>الإيرادات!D7*RoyaltyRate</f>
-        <v>19687.468098064517</v>
+        <v>16101.89</v>
       </c>
       <c r="E26" s="11">
         <f>الإيرادات!E7*RoyaltyRate</f>
-        <v>25312.458983225806</v>
+        <v>20702.43</v>
       </c>
       <c r="F26" s="11">
         <f>الإيرادات!F7*RoyaltyRate</f>
-        <v>28124.954425806456</v>
+        <v>23002.7</v>
       </c>
       <c r="G26" s="11">
         <f>الإيرادات!G7*RoyaltyRate</f>
-        <v>28124.954425806456</v>
+        <v>23002.7</v>
       </c>
       <c r="H26" s="11">
         <f>الإيرادات!H7*RoyaltyRate</f>
-        <v>28124.954425806456</v>
+        <v>23002.7</v>
       </c>
       <c r="I26" s="11">
         <f>الإيرادات!I7*RoyaltyRate</f>
-        <v>28124.954425806456</v>
+        <v>23002.7</v>
       </c>
       <c r="J26" s="11">
         <f>الإيرادات!J7*RoyaltyRate</f>
-        <v>28124.954425806456</v>
+        <v>23002.7</v>
       </c>
       <c r="K26" s="11">
         <f>الإيرادات!K7*RoyaltyRate</f>
-        <v>28124.954425806456</v>
+        <v>23002.7</v>
       </c>
       <c r="L26" s="11">
         <f>الإيرادات!L7*RoyaltyRate</f>
-        <v>28124.954425806456</v>
+        <v>23002.7</v>
       </c>
       <c r="M26" s="11">
         <f>الإيرادات!M7*RoyaltyRate</f>
-        <v>28124.954425806456</v>
+        <v>23002.7</v>
       </c>
       <c r="N26" s="12">
         <f t="shared" si="3"/>
-        <v>269999.56248774205</v>
+        <v>220825.92</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -8826,47 +8830,47 @@
       <c r="C27" s="11"/>
       <c r="D27" s="11">
         <f>الإيرادات!D7*CommunityRate</f>
-        <v>3937.4936196129029</v>
+        <v>3220.378</v>
       </c>
       <c r="E27" s="11">
         <f>الإيرادات!E7*CommunityRate</f>
-        <v>5062.4917966451612</v>
+        <v>4140.486</v>
       </c>
       <c r="F27" s="11">
         <f>الإيرادات!F7*CommunityRate</f>
-        <v>5624.9908851612909</v>
+        <v>4600.54</v>
       </c>
       <c r="G27" s="11">
         <f>الإيرادات!G7*CommunityRate</f>
-        <v>5624.9908851612909</v>
+        <v>4600.54</v>
       </c>
       <c r="H27" s="11">
         <f>الإيرادات!H7*CommunityRate</f>
-        <v>5624.9908851612909</v>
+        <v>4600.54</v>
       </c>
       <c r="I27" s="11">
         <f>الإيرادات!I7*CommunityRate</f>
-        <v>5624.9908851612909</v>
+        <v>4600.54</v>
       </c>
       <c r="J27" s="11">
         <f>الإيرادات!J7*CommunityRate</f>
-        <v>5624.9908851612909</v>
+        <v>4600.54</v>
       </c>
       <c r="K27" s="11">
         <f>الإيرادات!K7*CommunityRate</f>
-        <v>5624.9908851612909</v>
+        <v>4600.54</v>
       </c>
       <c r="L27" s="11">
         <f>الإيرادات!L7*CommunityRate</f>
-        <v>5624.9908851612909</v>
+        <v>4600.54</v>
       </c>
       <c r="M27" s="11">
         <f>الإيرادات!M7*CommunityRate</f>
-        <v>5624.9908851612909</v>
+        <v>4600.54</v>
       </c>
       <c r="N27" s="12">
         <f t="shared" si="3"/>
-        <v>53999.912497548401</v>
+        <v>44165.184</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -8879,47 +8883,47 @@
       <c r="C28" s="11"/>
       <c r="D28" s="12">
         <f t="shared" ref="D28:M28" si="4">SUM(D25:D27)</f>
-        <v>67487.250117677424</v>
+        <v>63184.5564</v>
       </c>
       <c r="E28" s="12">
         <f t="shared" si="4"/>
-        <v>87615.237141870981</v>
+        <v>82083.202362</v>
       </c>
       <c r="F28" s="12">
         <f t="shared" si="4"/>
-        <v>98304.268263667735</v>
+        <v>92157.5629527</v>
       </c>
       <c r="G28" s="12">
         <f t="shared" si="4"/>
-        <v>99272.583107958228</v>
+        <v>93125.8777969905</v>
       </c>
       <c r="H28" s="12">
         <f t="shared" si="4"/>
-        <v>100255.42267491308</v>
+        <v>94108.7173639453</v>
       </c>
       <c r="I28" s="12">
         <f t="shared" si="4"/>
-        <v>101253.00483537225</v>
+        <v>95106.2995244045</v>
       </c>
       <c r="J28" s="12">
         <f t="shared" si="4"/>
-        <v>102265.5507282383</v>
+        <v>96118.8454172706</v>
       </c>
       <c r="K28" s="12">
         <f t="shared" si="4"/>
-        <v>103293.28480949735</v>
+        <v>97146.5794985296</v>
       </c>
       <c r="L28" s="12">
         <f t="shared" si="4"/>
-        <v>104336.43490197528</v>
+        <v>98189.7295910076</v>
       </c>
       <c r="M28" s="12">
         <f t="shared" si="4"/>
-        <v>105395.23224584039</v>
+        <v>99248.5269348727</v>
       </c>
       <c r="N28" s="12">
         <f t="shared" si="3"/>
-        <v>969478.26882701099</v>
+        <v>910469.897841721</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
@@ -8932,47 +8936,47 @@
       <c r="C29" s="11"/>
       <c r="D29" s="13">
         <f t="shared" ref="D29:M29" si="5">D23+D28</f>
-        <v>290561.17011767742</v>
+        <v>286258.4764</v>
       </c>
       <c r="E29" s="13">
         <f t="shared" si="5"/>
-        <v>313974.51594187098</v>
+        <v>308442.481162</v>
       </c>
       <c r="F29" s="13">
         <f t="shared" si="5"/>
-        <v>330710.18624566763</v>
+        <v>324563.4809347</v>
       </c>
       <c r="G29" s="13">
         <f t="shared" si="5"/>
-        <v>336847.57687218813</v>
+        <v>330700.87156122</v>
       </c>
       <c r="H29" s="13">
         <f t="shared" si="5"/>
-        <v>344045.29134560644</v>
+        <v>337898.586034639</v>
       </c>
       <c r="I29" s="13">
         <f t="shared" si="5"/>
-        <v>345886.29153612594</v>
+        <v>339739.586225158</v>
       </c>
       <c r="J29" s="13">
         <f t="shared" si="5"/>
-        <v>357921.39276445663</v>
+        <v>351774.687453489</v>
       </c>
       <c r="K29" s="13">
         <f t="shared" si="5"/>
-        <v>359970.53447625885</v>
+        <v>353823.829165291</v>
       </c>
       <c r="L29" s="13">
         <f t="shared" si="5"/>
-        <v>367515.09331373824</v>
+        <v>361368.388002771</v>
       </c>
       <c r="M29" s="13">
         <f t="shared" si="5"/>
-        <v>369708.14053377975</v>
+        <v>363561.435222812</v>
       </c>
       <c r="N29" s="12">
         <f t="shared" si="3"/>
-        <v>3417140.1931473697</v>
+        <v>3358131.82216208</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -8985,47 +8989,47 @@
       <c r="C30" s="11"/>
       <c r="D30" s="18">
         <f>IF(الإيرادات!D5&gt;0,D29/الإيرادات!D5,0)</f>
-        <v>34.881292931293807</v>
+        <v>34.3647630732293</v>
       </c>
       <c r="E30" s="18">
         <f>IF(الإيرادات!E5&gt;0,E29/الإيرادات!E5,0)</f>
-        <v>29.316014560398784</v>
+        <v>28.7994847023343</v>
       </c>
       <c r="F30" s="18">
         <f>IF(الإيرادات!F5&gt;0,F29/الإيرادات!F5,0)</f>
-        <v>27.790771953417448</v>
+        <v>27.2742420953529</v>
       </c>
       <c r="G30" s="18">
         <f>IF(الإيرادات!G5&gt;0,G29/الإيرادات!G5,0)</f>
-        <v>28.306519064889759</v>
+        <v>27.7899892068252</v>
       </c>
       <c r="H30" s="18">
         <f>IF(الإيرادات!H5&gt;0,H29/الإيرادات!H5,0)</f>
-        <v>28.911369020639196</v>
+        <v>28.3948391625747</v>
       </c>
       <c r="I30" s="18">
         <f>IF(الإيرادات!I5&gt;0,I29/الإيرادات!I5,0)</f>
-        <v>29.06607491900218</v>
+        <v>28.5495450609377</v>
       </c>
       <c r="J30" s="18">
         <f>IF(الإيرادات!J5&gt;0,J29/الإيرادات!J5,0)</f>
-        <v>30.077427963399717</v>
+        <v>29.5608981053352</v>
       </c>
       <c r="K30" s="18">
         <f>IF(الإيرادات!K5&gt;0,K29/الإيرادات!K5,0)</f>
-        <v>30.249624745904104</v>
+        <v>29.7330948878396</v>
       </c>
       <c r="L30" s="18">
         <f>IF(الإيرادات!L5&gt;0,L29/الإيرادات!L5,0)</f>
-        <v>30.88362128686876</v>
+        <v>30.3670914288043</v>
       </c>
       <c r="M30" s="18">
         <f>IF(الإيرادات!M5&gt;0,M29/الإيرادات!M5,0)</f>
-        <v>31.067910969225188</v>
+        <v>30.5513811111607</v>
       </c>
       <c r="N30" s="33">
         <f>IF(الإيرادات!N5&gt;0,N29/الإيرادات!N5,0)</f>
-        <v>29.911941466626136</v>
+        <v>29.3954116085616</v>
       </c>
     </row>
   </sheetData>
@@ -9102,7 +9106,7 @@
       </c>
       <c r="C6" s="17">
         <f>B6/$B$10</f>
-        <v>0.38393028804120533</v>
+        <v>0.38464422854419</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>342</v>
@@ -9118,7 +9122,7 @@
       </c>
       <c r="C7" s="17">
         <f>B7/$B$10</f>
-        <v>0.39582263655886818</v>
+        <v>0.396558691569478</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>599</v>
@@ -9134,7 +9138,7 @@
       </c>
       <c r="C8" s="17">
         <f>B8/$B$10</f>
-        <v>9.4904116145017037E-2</v>
+        <v>0.0950805958199122</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>601</v>
@@ -9146,11 +9150,11 @@
       </c>
       <c r="B9" s="11">
         <f>B17</f>
-        <v>72640.292529419356</v>
+        <v>71564.6191</v>
       </c>
       <c r="C9" s="17">
         <f>B9/$B$10</f>
-        <v>0.1253429592549096</v>
+        <v>0.123716484066419</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>603</v>
@@ -9162,11 +9166,11 @@
       </c>
       <c r="B10" s="13">
         <f>SUM(B6:B9)</f>
-        <v>579532.2925294193</v>
+        <v>578456.6191</v>
       </c>
       <c r="C10" s="46">
         <f>SUM(C6:C9)</f>
-        <v>1.0000000000000002</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
@@ -9179,7 +9183,7 @@
       </c>
       <c r="C11" s="17">
         <f>B11/$B$10</f>
-        <v>0.34510587689097105</v>
+        <v>0.345747621163317</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>605</v>
@@ -9191,11 +9195,11 @@
       </c>
       <c r="B12" s="12">
         <f>B10-B11</f>
-        <v>379532.2925294193</v>
+        <v>378456.6191</v>
       </c>
       <c r="C12" s="46">
         <f>B12/$B$10</f>
-        <v>0.65489412310902895</v>
+        <v>0.654252378836683</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
@@ -9216,7 +9220,7 @@
       </c>
       <c r="B15" s="11">
         <f>'التكاليف التشغيلية'!D29</f>
-        <v>290561.17011767742</v>
+        <v>286258.4764</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>608</v>
@@ -9237,7 +9241,7 @@
       </c>
       <c r="B17" s="12">
         <f>B15*B16/12</f>
-        <v>72640.292529419356</v>
+        <v>71564.6191</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -9262,7 +9266,7 @@
       </c>
       <c r="C20" s="17">
         <f>B20/$B$23</f>
-        <v>0.25882940766822832</v>
+        <v>0.259310715872488</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -9275,7 +9279,7 @@
       </c>
       <c r="C21" s="17">
         <f>B21/$B$23</f>
-        <v>0.34510587689097105</v>
+        <v>0.345747621163317</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
@@ -9284,11 +9288,11 @@
       </c>
       <c r="B22" s="11">
         <f>B10-B20-B21</f>
-        <v>229532.2925294193</v>
+        <v>228456.6191</v>
       </c>
       <c r="C22" s="17">
         <f>B22/$B$23</f>
-        <v>0.39606471544080063</v>
+        <v>0.394941662964195</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
@@ -9297,7 +9301,7 @@
       </c>
       <c r="B23" s="12">
         <f>SUM(B20:B22)</f>
-        <v>579532.2925294193</v>
+        <v>578456.6191</v>
       </c>
       <c r="C23" s="46">
         <f>SUM(C20:C22)</f>
@@ -9310,7 +9314,7 @@
       </c>
       <c r="B24" s="17">
         <f>IF(NewInv&gt;0,Loan/NewInv,0)</f>
-        <v>0.39522328653594824</v>
+        <v>0.396346615251999</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -9371,19 +9375,19 @@
       </c>
       <c r="E27" s="11">
         <f t="shared" si="0"/>
-        <v>123390.53993532155</v>
+        <v>123390.539935322</v>
       </c>
       <c r="F27" s="11">
         <f t="shared" si="0"/>
-        <v>95184.512266762395</v>
+        <v>95184.5122667624</v>
       </c>
       <c r="G27" s="11">
         <f t="shared" si="0"/>
-        <v>65286.122938089691</v>
+        <v>65286.1229380897</v>
       </c>
       <c r="H27" s="11">
         <f t="shared" si="0"/>
-        <v>33593.830249696628</v>
+        <v>33593.8302496966</v>
       </c>
       <c r="I27" s="11">
         <f t="shared" si="0"/>
@@ -9417,23 +9421,23 @@
       <c r="C28" s="11"/>
       <c r="D28" s="11">
         <f>IF(AND(D$26&lt;=LoanYrs,Loan&gt;0),-PMT(LoanRate,LoanYrs,Loan),0)</f>
-        <v>35609.460064678446</v>
+        <v>35609.4600646784</v>
       </c>
       <c r="E28" s="11">
         <f>IF(AND(E$26&lt;=LoanYrs,Loan&gt;0),-PMT(LoanRate,LoanYrs,Loan),0)</f>
-        <v>35609.460064678446</v>
+        <v>35609.4600646784</v>
       </c>
       <c r="F28" s="11">
         <f>IF(AND(F$26&lt;=LoanYrs,Loan&gt;0),-PMT(LoanRate,LoanYrs,Loan),0)</f>
-        <v>35609.460064678446</v>
+        <v>35609.4600646784</v>
       </c>
       <c r="G28" s="11">
         <f>IF(AND(G$26&lt;=LoanYrs,Loan&gt;0),-PMT(LoanRate,LoanYrs,Loan),0)</f>
-        <v>35609.460064678446</v>
+        <v>35609.4600646784</v>
       </c>
       <c r="H28" s="11">
         <f>IF(AND(H$26&lt;=LoanYrs,Loan&gt;0),-PMT(LoanRate,LoanYrs,Loan),0)</f>
-        <v>35609.460064678446</v>
+        <v>35609.4600646784</v>
       </c>
       <c r="I28" s="11">
         <f>IF(AND(I$26&lt;=LoanYrs,Loan&gt;0),-PMT(LoanRate,LoanYrs,Loan),0)</f>
@@ -9457,7 +9461,7 @@
       </c>
       <c r="N28" s="12">
         <f>SUM(D28:M28)</f>
-        <v>178047.30032339224</v>
+        <v>178047.300323392</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
@@ -9474,19 +9478,19 @@
       </c>
       <c r="E29" s="11">
         <f>E27*LoanRate</f>
-        <v>7403.4323961192922</v>
+        <v>7403.43239611929</v>
       </c>
       <c r="F29" s="11">
         <f>F27*LoanRate</f>
-        <v>5711.0707360057431</v>
+        <v>5711.07073600574</v>
       </c>
       <c r="G29" s="11">
         <f>G27*LoanRate</f>
-        <v>3917.1673762853811</v>
+        <v>3917.16737628538</v>
       </c>
       <c r="H29" s="11">
         <f>H27*LoanRate</f>
-        <v>2015.6298149817976</v>
+        <v>2015.6298149818</v>
       </c>
       <c r="I29" s="11">
         <f>I27*LoanRate</f>
@@ -9510,7 +9514,7 @@
       </c>
       <c r="N29" s="12">
         <f>SUM(D29:M29)</f>
-        <v>28047.300323392214</v>
+        <v>28047.3003233922</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -9523,23 +9527,23 @@
       <c r="C30" s="11"/>
       <c r="D30" s="11">
         <f t="shared" ref="D30:M30" si="1">D28-D29</f>
-        <v>26609.460064678446</v>
+        <v>26609.4600646784</v>
       </c>
       <c r="E30" s="11">
         <f t="shared" si="1"/>
-        <v>28206.027668559153</v>
+        <v>28206.0276685592</v>
       </c>
       <c r="F30" s="11">
         <f t="shared" si="1"/>
-        <v>29898.389328672703</v>
+        <v>29898.3893286727</v>
       </c>
       <c r="G30" s="11">
         <f t="shared" si="1"/>
-        <v>31692.292688393063</v>
+        <v>31692.2926883931</v>
       </c>
       <c r="H30" s="11">
         <f t="shared" si="1"/>
-        <v>33593.83024969665</v>
+        <v>33593.8302496967</v>
       </c>
       <c r="I30" s="11">
         <f t="shared" si="1"/>
@@ -9579,19 +9583,19 @@
       </c>
       <c r="D31" s="12">
         <f t="shared" ref="D31:M31" si="2">D27-D30</f>
-        <v>123390.53993532155</v>
+        <v>123390.539935322</v>
       </c>
       <c r="E31" s="12">
         <f t="shared" si="2"/>
-        <v>95184.512266762395</v>
+        <v>95184.5122667624</v>
       </c>
       <c r="F31" s="12">
         <f t="shared" si="2"/>
-        <v>65286.122938089691</v>
+        <v>65286.1229380897</v>
       </c>
       <c r="G31" s="12">
         <f t="shared" si="2"/>
-        <v>33593.830249696628</v>
+        <v>33593.8302496966</v>
       </c>
       <c r="H31" s="12">
         <f t="shared" si="2"/>
@@ -9707,47 +9711,47 @@
       <c r="C5" s="11"/>
       <c r="D5" s="47">
         <f>الإيرادات!D7</f>
-        <v>393749.3619612903</v>
+        <v>322037.8</v>
       </c>
       <c r="E5" s="47">
         <f>الإيرادات!E7</f>
-        <v>506249.17966451612</v>
+        <v>414048.6</v>
       </c>
       <c r="F5" s="47">
         <f>الإيرادات!F7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="G5" s="47">
         <f>الإيرادات!G7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="H5" s="47">
         <f>الإيرادات!H7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="I5" s="47">
         <f>الإيرادات!I7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="J5" s="47">
         <f>الإيرادات!J7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="K5" s="47">
         <f>الإيرادات!K7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="L5" s="47">
         <f>الإيرادات!L7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="M5" s="47">
         <f>الإيرادات!M7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="N5" s="12">
         <f t="shared" ref="N5:N15" si="0">SUM(D5:M5)</f>
-        <v>5399991.2497548396</v>
+        <v>4416518.4</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.2">
@@ -9760,47 +9764,47 @@
       <c r="C6" s="11"/>
       <c r="D6" s="11">
         <f>'التكاليف التشغيلية'!D23</f>
-        <v>223073.91999999998</v>
+        <v>223073.92</v>
       </c>
       <c r="E6" s="11">
         <f>'التكاليف التشغيلية'!E23</f>
-        <v>226359.27879999997</v>
+        <v>226359.2788</v>
       </c>
       <c r="F6" s="11">
         <f>'التكاليف التشغيلية'!F23</f>
-        <v>232405.91798199993</v>
+        <v>232405.917982</v>
       </c>
       <c r="G6" s="11">
         <f>'التكاليف التشغيلية'!G23</f>
-        <v>237574.99376422993</v>
+        <v>237574.99376423</v>
       </c>
       <c r="H6" s="11">
         <f>'التكاليف التشغيلية'!H23</f>
-        <v>243789.86867069334</v>
+        <v>243789.868670693</v>
       </c>
       <c r="I6" s="11">
         <f>'التكاليف التشغيلية'!I23</f>
-        <v>244633.28670075367</v>
+        <v>244633.286700754</v>
       </c>
       <c r="J6" s="11">
         <f>'التكاليف التشغيلية'!J23</f>
-        <v>255655.84203621832</v>
+        <v>255655.842036218</v>
       </c>
       <c r="K6" s="11">
         <f>'التكاليف التشغيلية'!K23</f>
-        <v>256677.24966676152</v>
+        <v>256677.249666762</v>
       </c>
       <c r="L6" s="11">
         <f>'التكاليف التشغيلية'!L23</f>
-        <v>263178.65841176297</v>
+        <v>263178.658411763</v>
       </c>
       <c r="M6" s="11">
         <f>'التكاليف التشغيلية'!M23</f>
-        <v>264312.90828793938</v>
+        <v>264312.908287939</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" si="0"/>
-        <v>2447661.9243203588</v>
+        <v>2447661.92432036</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -9813,47 +9817,47 @@
       <c r="C7" s="11"/>
       <c r="D7" s="11">
         <f>'التكاليف التشغيلية'!D25</f>
-        <v>43862.288400000005</v>
+        <v>43862.2884</v>
       </c>
       <c r="E7" s="11">
         <f>'التكاليف التشغيلية'!E25</f>
-        <v>57240.286362000006</v>
+        <v>57240.286362</v>
       </c>
       <c r="F7" s="11">
         <f>'التكاليف التشغيلية'!F25</f>
-        <v>64554.322952699993</v>
+        <v>64554.3229527</v>
       </c>
       <c r="G7" s="11">
         <f>'التكاليف التشغيلية'!G25</f>
-        <v>65522.637796990486</v>
+        <v>65522.6377969905</v>
       </c>
       <c r="H7" s="11">
         <f>'التكاليف التشغيلية'!H25</f>
-        <v>66505.477363945334</v>
+        <v>66505.4773639453</v>
       </c>
       <c r="I7" s="11">
         <f>'التكاليف التشغيلية'!I25</f>
-        <v>67503.059524404511</v>
+        <v>67503.0595244045</v>
       </c>
       <c r="J7" s="11">
         <f>'التكاليف التشغيلية'!J25</f>
-        <v>68515.605417270563</v>
+        <v>68515.6054172706</v>
       </c>
       <c r="K7" s="11">
         <f>'التكاليف التشغيلية'!K25</f>
-        <v>69543.339498529604</v>
+        <v>69543.3394985296</v>
       </c>
       <c r="L7" s="11">
         <f>'التكاليف التشغيلية'!L25</f>
-        <v>70586.489591007543</v>
+        <v>70586.4895910076</v>
       </c>
       <c r="M7" s="11">
         <f>'التكاليف التشغيلية'!M25</f>
-        <v>71645.286934872653</v>
+        <v>71645.2869348727</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>645478.79384172068</v>
+        <v>645478.793841721</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -9866,47 +9870,47 @@
       <c r="C8" s="11"/>
       <c r="D8" s="11">
         <f>'التكاليف التشغيلية'!D26+'التكاليف التشغيلية'!D27</f>
-        <v>23624.961717677419</v>
+        <v>19322.268</v>
       </c>
       <c r="E8" s="11">
         <f>'التكاليف التشغيلية'!E26+'التكاليف التشغيلية'!E27</f>
-        <v>30374.950779870967</v>
+        <v>24842.916</v>
       </c>
       <c r="F8" s="11">
         <f>'التكاليف التشغيلية'!F26+'التكاليف التشغيلية'!F27</f>
-        <v>33749.945310967749</v>
+        <v>27603.24</v>
       </c>
       <c r="G8" s="11">
         <f>'التكاليف التشغيلية'!G26+'التكاليف التشغيلية'!G27</f>
-        <v>33749.945310967749</v>
+        <v>27603.24</v>
       </c>
       <c r="H8" s="11">
         <f>'التكاليف التشغيلية'!H26+'التكاليف التشغيلية'!H27</f>
-        <v>33749.945310967749</v>
+        <v>27603.24</v>
       </c>
       <c r="I8" s="11">
         <f>'التكاليف التشغيلية'!I26+'التكاليف التشغيلية'!I27</f>
-        <v>33749.945310967749</v>
+        <v>27603.24</v>
       </c>
       <c r="J8" s="11">
         <f>'التكاليف التشغيلية'!J26+'التكاليف التشغيلية'!J27</f>
-        <v>33749.945310967749</v>
+        <v>27603.24</v>
       </c>
       <c r="K8" s="11">
         <f>'التكاليف التشغيلية'!K26+'التكاليف التشغيلية'!K27</f>
-        <v>33749.945310967749</v>
+        <v>27603.24</v>
       </c>
       <c r="L8" s="11">
         <f>'التكاليف التشغيلية'!L26+'التكاليف التشغيلية'!L27</f>
-        <v>33749.945310967749</v>
+        <v>27603.24</v>
       </c>
       <c r="M8" s="11">
         <f>'التكاليف التشغيلية'!M26+'التكاليف التشغيلية'!M27</f>
-        <v>33749.945310967749</v>
+        <v>27603.24</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="0"/>
-        <v>323999.47498529032</v>
+        <v>264991.104</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -9919,47 +9923,47 @@
       <c r="C9" s="11"/>
       <c r="D9" s="12">
         <f t="shared" ref="D9:M9" si="1">SUM(D6:D8)</f>
-        <v>290561.17011767742</v>
+        <v>286258.4764</v>
       </c>
       <c r="E9" s="12">
         <f t="shared" si="1"/>
-        <v>313974.51594187092</v>
+        <v>308442.481162</v>
       </c>
       <c r="F9" s="12">
         <f t="shared" si="1"/>
-        <v>330710.18624566763</v>
+        <v>324563.4809347</v>
       </c>
       <c r="G9" s="12">
         <f t="shared" si="1"/>
-        <v>336847.57687218813</v>
+        <v>330700.87156122</v>
       </c>
       <c r="H9" s="12">
         <f t="shared" si="1"/>
-        <v>344045.29134560644</v>
+        <v>337898.586034639</v>
       </c>
       <c r="I9" s="12">
         <f t="shared" si="1"/>
-        <v>345886.29153612594</v>
+        <v>339739.586225158</v>
       </c>
       <c r="J9" s="12">
         <f t="shared" si="1"/>
-        <v>357921.39276445663</v>
+        <v>351774.687453489</v>
       </c>
       <c r="K9" s="12">
         <f t="shared" si="1"/>
-        <v>359970.53447625885</v>
+        <v>353823.829165291</v>
       </c>
       <c r="L9" s="12">
         <f t="shared" si="1"/>
-        <v>367515.09331373824</v>
+        <v>361368.388002771</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="1"/>
-        <v>369708.14053377975</v>
+        <v>363561.435222812</v>
       </c>
       <c r="N9" s="12">
         <f t="shared" si="0"/>
-        <v>3417140.1931473697</v>
+        <v>3358131.82216208</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.2">
@@ -9972,47 +9976,47 @@
       <c r="C10" s="11"/>
       <c r="D10" s="13">
         <f t="shared" ref="D10:M10" si="2">D5-D9</f>
-        <v>103188.19184361288</v>
+        <v>35779.3236</v>
       </c>
       <c r="E10" s="13">
         <f t="shared" si="2"/>
-        <v>192274.6637226452</v>
+        <v>105606.118838</v>
       </c>
       <c r="F10" s="13">
         <f t="shared" si="2"/>
-        <v>231788.90227046143</v>
+        <v>135490.5190653</v>
       </c>
       <c r="G10" s="13">
         <f t="shared" si="2"/>
-        <v>225651.51164394093</v>
+        <v>129353.12843878</v>
       </c>
       <c r="H10" s="13">
         <f t="shared" si="2"/>
-        <v>218453.79717052262</v>
+        <v>122155.413965361</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="2"/>
-        <v>216612.79698000313</v>
+        <v>120314.413774842</v>
       </c>
       <c r="J10" s="13">
         <f t="shared" si="2"/>
-        <v>204577.69575167244</v>
+        <v>108279.312546511</v>
       </c>
       <c r="K10" s="13">
         <f t="shared" si="2"/>
-        <v>202528.55403987021</v>
+        <v>106230.170834709</v>
       </c>
       <c r="L10" s="13">
         <f t="shared" si="2"/>
-        <v>194983.99520239083</v>
+        <v>98685.6119972293</v>
       </c>
       <c r="M10" s="13">
         <f t="shared" si="2"/>
-        <v>192790.94798234932</v>
+        <v>96492.5647771878</v>
       </c>
       <c r="N10" s="12">
         <f t="shared" si="0"/>
-        <v>1982851.056607469</v>
+        <v>1058386.57783792</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.2">
@@ -10078,47 +10082,47 @@
       <c r="C12" s="11"/>
       <c r="D12" s="11">
         <f>IF(D$4&lt;=AmortYrs,PreOp/AmortYrs,0)</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="E12" s="11">
         <f>IF(E$4&lt;=AmortYrs,PreOp/AmortYrs,0)</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="F12" s="11">
         <f>IF(F$4&lt;=AmortYrs,PreOp/AmortYrs,0)</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="G12" s="11">
         <f>IF(G$4&lt;=AmortYrs,PreOp/AmortYrs,0)</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="H12" s="11">
         <f>IF(H$4&lt;=AmortYrs,PreOp/AmortYrs,0)</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="I12" s="11">
         <f>IF(I$4&lt;=AmortYrs,PreOp/AmortYrs,0)</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="J12" s="11">
         <f>IF(J$4&lt;=AmortYrs,PreOp/AmortYrs,0)</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="K12" s="11">
         <f>IF(K$4&lt;=AmortYrs,PreOp/AmortYrs,0)</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="L12" s="11">
         <f>IF(L$4&lt;=AmortYrs,PreOp/AmortYrs,0)</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="M12" s="11">
         <f>IF(M$4&lt;=AmortYrs,PreOp/AmortYrs,0)</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="0"/>
-        <v>229392.00000000006</v>
+        <v>229392</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.2">
@@ -10131,47 +10135,47 @@
       <c r="C13" s="11"/>
       <c r="D13" s="12">
         <f t="shared" ref="D13:M13" si="3">D10-D11-D12</f>
-        <v>59398.991843612879</v>
+        <v>-8009.8764</v>
       </c>
       <c r="E13" s="12">
         <f t="shared" si="3"/>
-        <v>148485.46372264519</v>
+        <v>61816.918838</v>
       </c>
       <c r="F13" s="12">
         <f t="shared" si="3"/>
-        <v>187999.70227046142</v>
+        <v>91701.3190653001</v>
       </c>
       <c r="G13" s="12">
         <f t="shared" si="3"/>
-        <v>181862.31164394092</v>
+        <v>85563.9284387796</v>
       </c>
       <c r="H13" s="12">
         <f t="shared" si="3"/>
-        <v>174664.59717052261</v>
+        <v>78366.2139653613</v>
       </c>
       <c r="I13" s="12">
         <f t="shared" si="3"/>
-        <v>172823.59698000312</v>
+        <v>76525.2137748417</v>
       </c>
       <c r="J13" s="12">
         <f t="shared" si="3"/>
-        <v>160788.49575167242</v>
+        <v>64490.112546511</v>
       </c>
       <c r="K13" s="12">
         <f t="shared" si="3"/>
-        <v>158739.3540398702</v>
+        <v>62440.9708347087</v>
       </c>
       <c r="L13" s="12">
         <f t="shared" si="3"/>
-        <v>151194.79520239081</v>
+        <v>54896.4119972293</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="3"/>
-        <v>149001.7479823493</v>
+        <v>52703.3647771878</v>
       </c>
       <c r="N13" s="12">
         <f t="shared" si="0"/>
-        <v>1544959.0566074688</v>
+        <v>620494.57783792</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.2">
@@ -10188,19 +10192,19 @@
       </c>
       <c r="E14" s="11">
         <f>'التكلفة الاستثمارية والتمويل'!E29</f>
-        <v>7403.4323961192922</v>
+        <v>7403.43239611929</v>
       </c>
       <c r="F14" s="11">
         <f>'التكلفة الاستثمارية والتمويل'!F29</f>
-        <v>5711.0707360057431</v>
+        <v>5711.07073600574</v>
       </c>
       <c r="G14" s="11">
         <f>'التكلفة الاستثمارية والتمويل'!G29</f>
-        <v>3917.1673762853811</v>
+        <v>3917.16737628538</v>
       </c>
       <c r="H14" s="11">
         <f>'التكلفة الاستثمارية والتمويل'!H29</f>
-        <v>2015.6298149817976</v>
+        <v>2015.6298149818</v>
       </c>
       <c r="I14" s="11">
         <f>'التكلفة الاستثمارية والتمويل'!I29</f>
@@ -10224,7 +10228,7 @@
       </c>
       <c r="N14" s="12">
         <f t="shared" si="0"/>
-        <v>28047.300323392214</v>
+        <v>28047.3003233922</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -10237,47 +10241,47 @@
       <c r="C15" s="11"/>
       <c r="D15" s="12">
         <f t="shared" ref="D15:M15" si="4">D13-D14</f>
-        <v>50398.991843612879</v>
+        <v>-17009.8764</v>
       </c>
       <c r="E15" s="12">
         <f t="shared" si="4"/>
-        <v>141082.0313265259</v>
+        <v>54413.4864418807</v>
       </c>
       <c r="F15" s="12">
         <f t="shared" si="4"/>
-        <v>182288.63153445566</v>
+        <v>85990.2483292943</v>
       </c>
       <c r="G15" s="12">
         <f t="shared" si="4"/>
-        <v>177945.14426765553</v>
+        <v>81646.7610624942</v>
       </c>
       <c r="H15" s="12">
         <f t="shared" si="4"/>
-        <v>172648.96735554081</v>
+        <v>76350.5841503795</v>
       </c>
       <c r="I15" s="12">
         <f t="shared" si="4"/>
-        <v>172823.59698000312</v>
+        <v>76525.2137748417</v>
       </c>
       <c r="J15" s="12">
         <f t="shared" si="4"/>
-        <v>160788.49575167242</v>
+        <v>64490.112546511</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="4"/>
-        <v>158739.3540398702</v>
+        <v>62440.9708347087</v>
       </c>
       <c r="L15" s="12">
         <f t="shared" si="4"/>
-        <v>151194.79520239081</v>
+        <v>54896.4119972293</v>
       </c>
       <c r="M15" s="12">
         <f t="shared" si="4"/>
-        <v>149001.7479823493</v>
+        <v>52703.3647771878</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="0"/>
-        <v>1516911.7562840765</v>
+        <v>592447.277514527</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -10294,7 +10298,7 @@
       </c>
       <c r="E16" s="11">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>17009.8764</v>
       </c>
       <c r="F16" s="11">
         <f t="shared" si="5"/>
@@ -10342,7 +10346,7 @@
       </c>
       <c r="D17" s="11">
         <f t="shared" ref="D17:M17" si="6">MAX(0,D16-D15)</f>
-        <v>0</v>
+        <v>17009.8764</v>
       </c>
       <c r="E17" s="11">
         <f t="shared" si="6"/>
@@ -10392,47 +10396,47 @@
       <c r="C18" s="11"/>
       <c r="D18" s="11">
         <f t="shared" ref="D18:M18" si="7">MAX(0,D15-D16)</f>
-        <v>50398.991843612879</v>
+        <v>0</v>
       </c>
       <c r="E18" s="11">
         <f t="shared" si="7"/>
-        <v>141082.0313265259</v>
+        <v>37403.6100418807</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="7"/>
-        <v>182288.63153445566</v>
+        <v>85990.2483292943</v>
       </c>
       <c r="G18" s="11">
         <f t="shared" si="7"/>
-        <v>177945.14426765553</v>
+        <v>81646.7610624942</v>
       </c>
       <c r="H18" s="11">
         <f t="shared" si="7"/>
-        <v>172648.96735554081</v>
+        <v>76350.5841503795</v>
       </c>
       <c r="I18" s="11">
         <f t="shared" si="7"/>
-        <v>172823.59698000312</v>
+        <v>76525.2137748417</v>
       </c>
       <c r="J18" s="11">
         <f t="shared" si="7"/>
-        <v>160788.49575167242</v>
+        <v>64490.112546511</v>
       </c>
       <c r="K18" s="11">
         <f t="shared" si="7"/>
-        <v>158739.3540398702</v>
+        <v>62440.9708347087</v>
       </c>
       <c r="L18" s="11">
         <f t="shared" si="7"/>
-        <v>151194.79520239081</v>
+        <v>54896.4119972293</v>
       </c>
       <c r="M18" s="11">
         <f t="shared" si="7"/>
-        <v>149001.7479823493</v>
+        <v>52703.3647771878</v>
       </c>
       <c r="N18" s="12">
         <f t="shared" ref="N18:N20" si="8">SUM(D18:M18)</f>
-        <v>1516911.7562840765</v>
+        <v>592447.277514527</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -10445,47 +10449,47 @@
       <c r="C19" s="11"/>
       <c r="D19" s="11">
         <f>D18*TaxRate</f>
-        <v>7559.8487765419313</v>
+        <v>0</v>
       </c>
       <c r="E19" s="11">
         <f>E18*TaxRate</f>
-        <v>21162.304698978885</v>
+        <v>5610.54150628211</v>
       </c>
       <c r="F19" s="11">
         <f>F18*TaxRate</f>
-        <v>27343.294730168349</v>
+        <v>12898.5372493941</v>
       </c>
       <c r="G19" s="11">
         <f>G18*TaxRate</f>
-        <v>26691.77164014833</v>
+        <v>12247.0141593741</v>
       </c>
       <c r="H19" s="11">
         <f>H18*TaxRate</f>
-        <v>25897.345103331121</v>
+        <v>11452.5876225569</v>
       </c>
       <c r="I19" s="11">
         <f>I18*TaxRate</f>
-        <v>25923.539547000466</v>
+        <v>11478.7820662263</v>
       </c>
       <c r="J19" s="11">
         <f>J18*TaxRate</f>
-        <v>24118.274362750864</v>
+        <v>9673.51688197665</v>
       </c>
       <c r="K19" s="11">
         <f>K18*TaxRate</f>
-        <v>23810.903105980531</v>
+        <v>9366.1456252063</v>
       </c>
       <c r="L19" s="11">
         <f>L18*TaxRate</f>
-        <v>22679.219280358622</v>
+        <v>8234.4617995844</v>
       </c>
       <c r="M19" s="11">
         <f>M18*TaxRate</f>
-        <v>22350.262197352396</v>
+        <v>7905.50471657817</v>
       </c>
       <c r="N19" s="12">
         <f t="shared" si="8"/>
-        <v>227536.76344261153</v>
+        <v>88867.0916271791</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -10498,47 +10502,47 @@
       <c r="C20" s="11"/>
       <c r="D20" s="13">
         <f t="shared" ref="D20:M20" si="9">D15-D19</f>
-        <v>42839.143067070945</v>
+        <v>-17009.8764</v>
       </c>
       <c r="E20" s="13">
         <f t="shared" si="9"/>
-        <v>119919.72662754702</v>
+        <v>48802.9449355986</v>
       </c>
       <c r="F20" s="13">
         <f t="shared" si="9"/>
-        <v>154945.3368042873</v>
+        <v>73091.7110799002</v>
       </c>
       <c r="G20" s="13">
         <f t="shared" si="9"/>
-        <v>151253.3726275072</v>
+        <v>69399.7469031201</v>
       </c>
       <c r="H20" s="13">
         <f t="shared" si="9"/>
-        <v>146751.62225220969</v>
+        <v>64897.9965278225</v>
       </c>
       <c r="I20" s="13">
         <f t="shared" si="9"/>
-        <v>146900.05743300266</v>
+        <v>65046.4317086155</v>
       </c>
       <c r="J20" s="13">
         <f t="shared" si="9"/>
-        <v>136670.22138892155</v>
+        <v>54816.5956645344</v>
       </c>
       <c r="K20" s="13">
         <f t="shared" si="9"/>
-        <v>134928.45093388966</v>
+        <v>53074.8252095024</v>
       </c>
       <c r="L20" s="13">
         <f t="shared" si="9"/>
-        <v>128515.57592203219</v>
+        <v>46661.9501976449</v>
       </c>
       <c r="M20" s="13">
         <f t="shared" si="9"/>
-        <v>126651.48578499691</v>
+        <v>44797.8600606097</v>
       </c>
       <c r="N20" s="12">
         <f t="shared" si="8"/>
-        <v>1289374.9928414652</v>
+        <v>503580.185887348</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -10551,47 +10555,47 @@
       <c r="C21" s="11"/>
       <c r="D21" s="17">
         <f t="shared" ref="D21:M21" si="10">IF(D5&gt;0,D10/D5,0)</f>
-        <v>0.26206567378198664</v>
+        <v>0.111102869290499</v>
       </c>
       <c r="E21" s="17">
         <f t="shared" si="10"/>
-        <v>0.37980242032206907</v>
+        <v>0.255057302060676</v>
       </c>
       <c r="F21" s="17">
         <f t="shared" si="10"/>
-        <v>0.4120698273163782</v>
+        <v>0.294510033746691</v>
       </c>
       <c r="G21" s="17">
         <f t="shared" si="10"/>
-        <v>0.40115889296675833</v>
+        <v>0.28116944627974</v>
       </c>
       <c r="H21" s="17">
         <f t="shared" si="10"/>
-        <v>0.38836293539035432</v>
+        <v>0.265524077532988</v>
       </c>
       <c r="I21" s="17">
         <f t="shared" si="10"/>
-        <v>0.3850900408593142</v>
+        <v>0.26152237297109</v>
       </c>
       <c r="J21" s="17">
         <f t="shared" si="10"/>
-        <v>0.36369427067223842</v>
+        <v>0.235362180410367</v>
       </c>
       <c r="K21" s="17">
         <f t="shared" si="10"/>
-        <v>0.36005134617042661</v>
+        <v>0.230908047391629</v>
       </c>
       <c r="L21" s="17">
         <f t="shared" si="10"/>
-        <v>0.3466387753920776</v>
+        <v>0.214508757661556</v>
       </c>
       <c r="M21" s="17">
         <f t="shared" si="10"/>
-        <v>0.34274001846106322</v>
+        <v>0.209741823301586</v>
       </c>
       <c r="N21" s="46">
         <f>IF(N5&gt;0,N10/N5,0)</f>
-        <v>0.36719523512144409</v>
+        <v>0.239642741630584</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
@@ -10604,47 +10608,47 @@
       <c r="C22" s="11"/>
       <c r="D22" s="17">
         <f t="shared" ref="D22:M22" si="11">IF(D5&gt;0,D20/D5,0)</f>
-        <v>0.10879799996039735</v>
+        <v>-0.0528195025552901</v>
       </c>
       <c r="E22" s="17">
         <f t="shared" si="11"/>
-        <v>0.23687885619294446</v>
+        <v>0.117867672866419</v>
       </c>
       <c r="F22" s="17">
         <f t="shared" si="11"/>
-        <v>0.27545882289877599</v>
+        <v>0.158876373382038</v>
       </c>
       <c r="G22" s="17">
         <f t="shared" si="11"/>
-        <v>0.26889532039334169</v>
+        <v>0.150851306375165</v>
       </c>
       <c r="H22" s="17">
         <f t="shared" si="11"/>
-        <v>0.26089219564664545</v>
+        <v>0.141066041220862</v>
       </c>
       <c r="I22" s="17">
         <f t="shared" si="11"/>
-        <v>0.26115608084010333</v>
+        <v>0.141388688520512</v>
       </c>
       <c r="J22" s="17">
         <f t="shared" si="11"/>
-        <v>0.24296967618108892</v>
+        <v>0.119152524843897</v>
       </c>
       <c r="K22" s="17">
         <f t="shared" si="11"/>
-        <v>0.23987319035454888</v>
+        <v>0.11536651177797</v>
       </c>
       <c r="L22" s="17">
         <f t="shared" si="11"/>
-        <v>0.22847250519295223</v>
+        <v>0.101427115507408</v>
       </c>
       <c r="M22" s="17">
         <f t="shared" si="11"/>
-        <v>0.22515856180159005</v>
+        <v>0.0973752213014335</v>
       </c>
       <c r="N22" s="46">
         <f>IF(N5&gt;0,N20/N5,0)</f>
-        <v>0.23877353373489318</v>
+        <v>0.114021982991704</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.2">
@@ -10760,47 +10764,47 @@
       </c>
       <c r="D6" s="11">
         <f>الإيرادات!D7</f>
-        <v>393749.3619612903</v>
+        <v>322037.8</v>
       </c>
       <c r="E6" s="11">
         <f>الإيرادات!E7</f>
-        <v>506249.17966451612</v>
+        <v>414048.6</v>
       </c>
       <c r="F6" s="11">
         <f>الإيرادات!F7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="G6" s="11">
         <f>الإيرادات!G7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="H6" s="11">
         <f>الإيرادات!H7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="I6" s="11">
         <f>الإيرادات!I7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="J6" s="11">
         <f>الإيرادات!J7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="K6" s="11">
         <f>الإيرادات!K7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="L6" s="11">
         <f>الإيرادات!L7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="M6" s="11">
         <f>الإيرادات!M7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="N6" s="12">
         <f t="shared" ref="N6:N14" si="0">SUM(C6:M6)</f>
-        <v>5399991.2497548396</v>
+        <v>4416518.4</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.2">
@@ -10815,47 +10819,47 @@
       </c>
       <c r="D7" s="11">
         <f>-'التكاليف التشغيلية'!D29</f>
-        <v>-290561.17011767742</v>
+        <v>-286258.4764</v>
       </c>
       <c r="E7" s="11">
         <f>-'التكاليف التشغيلية'!E29</f>
-        <v>-313974.51594187098</v>
+        <v>-308442.481162</v>
       </c>
       <c r="F7" s="11">
         <f>-'التكاليف التشغيلية'!F29</f>
-        <v>-330710.18624566763</v>
+        <v>-324563.4809347</v>
       </c>
       <c r="G7" s="11">
         <f>-'التكاليف التشغيلية'!G29</f>
-        <v>-336847.57687218813</v>
+        <v>-330700.87156122</v>
       </c>
       <c r="H7" s="11">
         <f>-'التكاليف التشغيلية'!H29</f>
-        <v>-344045.29134560644</v>
+        <v>-337898.586034639</v>
       </c>
       <c r="I7" s="11">
         <f>-'التكاليف التشغيلية'!I29</f>
-        <v>-345886.29153612594</v>
+        <v>-339739.586225158</v>
       </c>
       <c r="J7" s="11">
         <f>-'التكاليف التشغيلية'!J29</f>
-        <v>-357921.39276445663</v>
+        <v>-351774.687453489</v>
       </c>
       <c r="K7" s="11">
         <f>-'التكاليف التشغيلية'!K29</f>
-        <v>-359970.53447625885</v>
+        <v>-353823.829165291</v>
       </c>
       <c r="L7" s="11">
         <f>-'التكاليف التشغيلية'!L29</f>
-        <v>-367515.09331373824</v>
+        <v>-361368.388002771</v>
       </c>
       <c r="M7" s="11">
         <f>-'التكاليف التشغيلية'!M29</f>
-        <v>-369708.14053377975</v>
+        <v>-363561.435222812</v>
       </c>
       <c r="N7" s="12">
         <f t="shared" si="0"/>
-        <v>-3417140.1931473697</v>
+        <v>-3358131.82216208</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.2">
@@ -10870,47 +10874,47 @@
       </c>
       <c r="D8" s="11">
         <f>-'قائمة الدخل'!D19</f>
-        <v>-7559.8487765419313</v>
+        <v>0</v>
       </c>
       <c r="E8" s="11">
         <f>-'قائمة الدخل'!E19</f>
-        <v>-21162.304698978885</v>
+        <v>-5610.54150628211</v>
       </c>
       <c r="F8" s="11">
         <f>-'قائمة الدخل'!F19</f>
-        <v>-27343.294730168349</v>
+        <v>-12898.5372493941</v>
       </c>
       <c r="G8" s="11">
         <f>-'قائمة الدخل'!G19</f>
-        <v>-26691.77164014833</v>
+        <v>-12247.0141593741</v>
       </c>
       <c r="H8" s="11">
         <f>-'قائمة الدخل'!H19</f>
-        <v>-25897.345103331121</v>
+        <v>-11452.5876225569</v>
       </c>
       <c r="I8" s="11">
         <f>-'قائمة الدخل'!I19</f>
-        <v>-25923.539547000466</v>
+        <v>-11478.7820662263</v>
       </c>
       <c r="J8" s="11">
         <f>-'قائمة الدخل'!J19</f>
-        <v>-24118.274362750864</v>
+        <v>-9673.51688197665</v>
       </c>
       <c r="K8" s="11">
         <f>-'قائمة الدخل'!K19</f>
-        <v>-23810.903105980531</v>
+        <v>-9366.1456252063</v>
       </c>
       <c r="L8" s="11">
         <f>-'قائمة الدخل'!L19</f>
-        <v>-22679.219280358622</v>
+        <v>-8234.4617995844</v>
       </c>
       <c r="M8" s="11">
         <f>-'قائمة الدخل'!M19</f>
-        <v>-22350.262197352396</v>
+        <v>-7905.50471657817</v>
       </c>
       <c r="N8" s="12">
         <f t="shared" si="0"/>
-        <v>-227536.76344261153</v>
+        <v>-88867.0916271791</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.2">
@@ -11090,7 +11094,7 @@
       </c>
       <c r="C12" s="11">
         <f>-WorkCap</f>
-        <v>-72640.292529419356</v>
+        <v>-71564.6191</v>
       </c>
       <c r="D12" s="11">
         <f>0</f>
@@ -11130,7 +11134,7 @@
       </c>
       <c r="M12" s="11">
         <f>WorkCap</f>
-        <v>72640.292529419356</v>
+        <v>71564.6191</v>
       </c>
       <c r="N12" s="12">
         <f t="shared" si="0"/>
@@ -11201,51 +11205,51 @@
       </c>
       <c r="C14" s="13">
         <f t="shared" ref="C14:M14" si="1">SUM(C6:C13)</f>
-        <v>-579532.2925294193</v>
+        <v>-578456.6191</v>
       </c>
       <c r="D14" s="13">
         <f t="shared" si="1"/>
-        <v>95628.343067070949</v>
+        <v>35779.3236</v>
       </c>
       <c r="E14" s="13">
         <f t="shared" si="1"/>
-        <v>171112.35902366624</v>
+        <v>99995.5773317179</v>
       </c>
       <c r="F14" s="13">
         <f t="shared" si="1"/>
-        <v>204445.60754029307</v>
+        <v>122591.981815906</v>
       </c>
       <c r="G14" s="13">
         <f t="shared" si="1"/>
-        <v>198959.7400037926</v>
+        <v>117106.114279405</v>
       </c>
       <c r="H14" s="13">
         <f t="shared" si="1"/>
-        <v>192556.45206719151</v>
+        <v>110702.826342804</v>
       </c>
       <c r="I14" s="13">
         <f t="shared" si="1"/>
-        <v>183189.25743300267</v>
+        <v>101335.631708615</v>
       </c>
       <c r="J14" s="13">
         <f t="shared" si="1"/>
-        <v>180459.42138892156</v>
+        <v>98605.7956645344</v>
       </c>
       <c r="K14" s="13">
         <f t="shared" si="1"/>
-        <v>178717.65093388967</v>
+        <v>96864.0252095024</v>
       </c>
       <c r="L14" s="13">
         <f t="shared" si="1"/>
-        <v>172304.77592203219</v>
+        <v>90451.1501976449</v>
       </c>
       <c r="M14" s="13">
         <f t="shared" si="1"/>
-        <v>319580.97831441625</v>
+        <v>236651.67916061</v>
       </c>
       <c r="N14" s="12">
         <f t="shared" si="0"/>
-        <v>1317422.2931648574</v>
+        <v>531627.48621074</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -11257,47 +11261,47 @@
       </c>
       <c r="C15" s="11">
         <f>C14</f>
-        <v>-579532.2925294193</v>
+        <v>-578456.6191</v>
       </c>
       <c r="D15" s="11">
         <f t="shared" ref="D15:M15" si="2">C15+D14</f>
-        <v>-483903.94946234836</v>
+        <v>-542677.2955</v>
       </c>
       <c r="E15" s="11">
         <f t="shared" si="2"/>
-        <v>-312791.59043868212</v>
+        <v>-442681.718168282</v>
       </c>
       <c r="F15" s="11">
         <f t="shared" si="2"/>
-        <v>-108345.98289838905</v>
+        <v>-320089.736352376</v>
       </c>
       <c r="G15" s="11">
         <f t="shared" si="2"/>
-        <v>90613.757105403551</v>
+        <v>-202983.622072971</v>
       </c>
       <c r="H15" s="11">
         <f t="shared" si="2"/>
-        <v>283170.20917259506</v>
+        <v>-92280.7957301665</v>
       </c>
       <c r="I15" s="11">
         <f t="shared" si="2"/>
-        <v>466359.46660559776</v>
+        <v>9054.83597844899</v>
       </c>
       <c r="J15" s="11">
         <f t="shared" si="2"/>
-        <v>646818.88799451932</v>
+        <v>107660.631642983</v>
       </c>
       <c r="K15" s="11">
         <f t="shared" si="2"/>
-        <v>825536.53892840899</v>
+        <v>204524.656852486</v>
       </c>
       <c r="L15" s="11">
         <f t="shared" si="2"/>
-        <v>997841.31485044118</v>
+        <v>294975.807050131</v>
       </c>
       <c r="M15" s="11">
         <f t="shared" si="2"/>
-        <v>1317422.2931648574</v>
+        <v>531627.48621074</v>
       </c>
       <c r="N15" s="11"/>
     </row>
@@ -11314,43 +11318,43 @@
       </c>
       <c r="D16" s="44">
         <f>1/(1+DiscRate)^D$4</f>
-        <v>0.89285714285714279</v>
+        <v>0.892857142857143</v>
       </c>
       <c r="E16" s="44">
         <f>1/(1+DiscRate)^E$4</f>
-        <v>0.79719387755102034</v>
+        <v>0.79719387755102</v>
       </c>
       <c r="F16" s="44">
         <f>1/(1+DiscRate)^F$4</f>
-        <v>0.71178024781341087</v>
+        <v>0.711780247813411</v>
       </c>
       <c r="G16" s="44">
         <f>1/(1+DiscRate)^G$4</f>
-        <v>0.63551807840483121</v>
+        <v>0.635518078404831</v>
       </c>
       <c r="H16" s="44">
         <f>1/(1+DiscRate)^H$4</f>
-        <v>0.56742685571859919</v>
+        <v>0.567426855718599</v>
       </c>
       <c r="I16" s="44">
         <f>1/(1+DiscRate)^I$4</f>
-        <v>0.50663112117732068</v>
+        <v>0.506631121177321</v>
       </c>
       <c r="J16" s="44">
         <f>1/(1+DiscRate)^J$4</f>
-        <v>0.45234921533689343</v>
+        <v>0.452349215336893</v>
       </c>
       <c r="K16" s="44">
         <f>1/(1+DiscRate)^K$4</f>
-        <v>0.4038832279793691</v>
+        <v>0.403883227979369</v>
       </c>
       <c r="L16" s="44">
         <f>1/(1+DiscRate)^L$4</f>
-        <v>0.36061002498157957</v>
+        <v>0.360610024981579</v>
       </c>
       <c r="M16" s="44">
         <f>1/(1+DiscRate)^M$4</f>
-        <v>0.32197323659069599</v>
+        <v>0.321973236590696</v>
       </c>
       <c r="N16" s="11"/>
     </row>
@@ -11363,51 +11367,51 @@
       </c>
       <c r="C17" s="11">
         <f t="shared" ref="C17:M17" si="3">C14*C16</f>
-        <v>-579532.2925294193</v>
+        <v>-578456.6191</v>
       </c>
       <c r="D17" s="11">
         <f t="shared" si="3"/>
-        <v>85382.449167027633</v>
+        <v>31945.8246428571</v>
       </c>
       <c r="E17" s="11">
         <f t="shared" si="3"/>
-        <v>136409.72498697881</v>
+        <v>79715.8620310251</v>
       </c>
       <c r="F17" s="11">
         <f t="shared" si="3"/>
-        <v>145520.34519939314</v>
+        <v>87258.5511968627</v>
       </c>
       <c r="G17" s="11">
         <f t="shared" si="3"/>
-        <v>126442.51164713509</v>
+        <v>74423.0527163043</v>
       </c>
       <c r="H17" s="11">
         <f t="shared" si="3"/>
-        <v>109261.70214481563</v>
+        <v>62815.7566708596</v>
       </c>
       <c r="I17" s="11">
         <f t="shared" si="3"/>
-        <v>92809.378880922974</v>
+        <v>51339.7847077479</v>
       </c>
       <c r="J17" s="11">
         <f t="shared" si="3"/>
-        <v>81630.677665428477</v>
+        <v>44604.2542965222</v>
       </c>
       <c r="K17" s="11">
         <f t="shared" si="3"/>
-        <v>72181.061756069466</v>
+        <v>39121.7551766888</v>
       </c>
       <c r="L17" s="11">
         <f t="shared" si="3"/>
-        <v>62134.829549689501</v>
+        <v>32617.5915323853</v>
       </c>
       <c r="M17" s="11">
         <f t="shared" si="3"/>
-        <v>102896.52194071363</v>
+        <v>76195.5070839644</v>
       </c>
       <c r="N17" s="12">
         <f>SUM(C17:M17)</f>
-        <v>435136.91040875501</v>
+        <v>1581.32095521735</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -11419,47 +11423,47 @@
       </c>
       <c r="C18" s="11">
         <f>C17</f>
-        <v>-579532.2925294193</v>
+        <v>-578456.6191</v>
       </c>
       <c r="D18" s="11">
         <f t="shared" ref="D18:M18" si="4">C18+D17</f>
-        <v>-494149.84336239169</v>
+        <v>-546510.794457143</v>
       </c>
       <c r="E18" s="11">
         <f t="shared" si="4"/>
-        <v>-357740.11837541289</v>
+        <v>-466794.932426118</v>
       </c>
       <c r="F18" s="11">
         <f t="shared" si="4"/>
-        <v>-212219.77317601975</v>
+        <v>-379536.381229255</v>
       </c>
       <c r="G18" s="11">
         <f t="shared" si="4"/>
-        <v>-85777.261528884657</v>
+        <v>-305113.328512951</v>
       </c>
       <c r="H18" s="11">
         <f t="shared" si="4"/>
-        <v>23484.440615930973</v>
+        <v>-242297.571842091</v>
       </c>
       <c r="I18" s="11">
         <f t="shared" si="4"/>
-        <v>116293.81949685395</v>
+        <v>-190957.787134343</v>
       </c>
       <c r="J18" s="11">
         <f t="shared" si="4"/>
-        <v>197924.49716228241</v>
+        <v>-146353.532837821</v>
       </c>
       <c r="K18" s="11">
         <f t="shared" si="4"/>
-        <v>270105.55891835189</v>
+        <v>-107231.777661132</v>
       </c>
       <c r="L18" s="11">
         <f t="shared" si="4"/>
-        <v>332240.38846804138</v>
+        <v>-74614.1861287471</v>
       </c>
       <c r="M18" s="11">
         <f t="shared" si="4"/>
-        <v>435136.91040875501</v>
+        <v>1581.32095521738</v>
       </c>
       <c r="N18" s="11"/>
     </row>
@@ -11490,51 +11494,51 @@
       </c>
       <c r="C20" s="12">
         <f>C14+SunkCost</f>
-        <v>-379532.2925294193</v>
+        <v>-378456.6191</v>
       </c>
       <c r="D20" s="12">
         <f t="shared" ref="D20:M20" si="5">D14</f>
-        <v>95628.343067070949</v>
+        <v>35779.3236</v>
       </c>
       <c r="E20" s="12">
         <f t="shared" si="5"/>
-        <v>171112.35902366624</v>
+        <v>99995.5773317179</v>
       </c>
       <c r="F20" s="12">
         <f t="shared" si="5"/>
-        <v>204445.60754029307</v>
+        <v>122591.981815906</v>
       </c>
       <c r="G20" s="12">
         <f t="shared" si="5"/>
-        <v>198959.7400037926</v>
+        <v>117106.114279405</v>
       </c>
       <c r="H20" s="12">
         <f t="shared" si="5"/>
-        <v>192556.45206719151</v>
+        <v>110702.826342804</v>
       </c>
       <c r="I20" s="12">
         <f t="shared" si="5"/>
-        <v>183189.25743300267</v>
+        <v>101335.631708615</v>
       </c>
       <c r="J20" s="12">
         <f t="shared" si="5"/>
-        <v>180459.42138892156</v>
+        <v>98605.7956645344</v>
       </c>
       <c r="K20" s="12">
         <f t="shared" si="5"/>
-        <v>178717.65093388967</v>
+        <v>96864.0252095024</v>
       </c>
       <c r="L20" s="12">
         <f t="shared" si="5"/>
-        <v>172304.77592203219</v>
+        <v>90451.1501976449</v>
       </c>
       <c r="M20" s="12">
         <f t="shared" si="5"/>
-        <v>319580.97831441625</v>
+        <v>236651.67916061</v>
       </c>
       <c r="N20" s="12">
         <f>SUM(C20:M20)</f>
-        <v>1517422.2931648574</v>
+        <v>731627.48621074</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.2">
@@ -11623,23 +11627,23 @@
       </c>
       <c r="D23" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!D30</f>
-        <v>-26609.460064678446</v>
+        <v>-26609.4600646784</v>
       </c>
       <c r="E23" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!E30</f>
-        <v>-28206.027668559153</v>
+        <v>-28206.0276685592</v>
       </c>
       <c r="F23" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!F30</f>
-        <v>-29898.389328672703</v>
+        <v>-29898.3893286727</v>
       </c>
       <c r="G23" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!G30</f>
-        <v>-31692.292688393063</v>
+        <v>-31692.2926883931</v>
       </c>
       <c r="H23" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!H30</f>
-        <v>-33593.83024969665</v>
+        <v>-33593.8302496967</v>
       </c>
       <c r="I23" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!I30</f>
@@ -11682,19 +11686,19 @@
       </c>
       <c r="E24" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!E29</f>
-        <v>-7403.4323961192922</v>
+        <v>-7403.43239611929</v>
       </c>
       <c r="F24" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!F29</f>
-        <v>-5711.0707360057431</v>
+        <v>-5711.07073600574</v>
       </c>
       <c r="G24" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!G29</f>
-        <v>-3917.1673762853811</v>
+        <v>-3917.16737628538</v>
       </c>
       <c r="H24" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!H29</f>
-        <v>-2015.6298149817976</v>
+        <v>-2015.6298149818</v>
       </c>
       <c r="I24" s="11">
         <f>-'التكلفة الاستثمارية والتمويل'!I29</f>
@@ -11718,7 +11722,7 @@
       </c>
       <c r="N24" s="12">
         <f t="shared" si="6"/>
-        <v>-28047.300323392214</v>
+        <v>-28047.3003233922</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -11730,51 +11734,51 @@
       </c>
       <c r="C25" s="13">
         <f t="shared" ref="C25:M25" si="7">C14+C22+C23+C24</f>
-        <v>-429532.2925294193</v>
+        <v>-428456.6191</v>
       </c>
       <c r="D25" s="13">
         <f t="shared" si="7"/>
-        <v>60018.883002392511</v>
+        <v>169.863535321558</v>
       </c>
       <c r="E25" s="13">
         <f t="shared" si="7"/>
-        <v>135502.89895898779</v>
+        <v>64386.1172670394</v>
       </c>
       <c r="F25" s="13">
         <f t="shared" si="7"/>
-        <v>168836.14747561462</v>
+        <v>86982.5217512275</v>
       </c>
       <c r="G25" s="13">
         <f t="shared" si="7"/>
-        <v>163350.27993911415</v>
+        <v>81496.654214727</v>
       </c>
       <c r="H25" s="13">
         <f t="shared" si="7"/>
-        <v>156946.99200251306</v>
+        <v>75093.3662781259</v>
       </c>
       <c r="I25" s="13">
         <f t="shared" si="7"/>
-        <v>183189.25743300267</v>
+        <v>101335.631708615</v>
       </c>
       <c r="J25" s="13">
         <f t="shared" si="7"/>
-        <v>180459.42138892156</v>
+        <v>98605.7956645344</v>
       </c>
       <c r="K25" s="13">
         <f t="shared" si="7"/>
-        <v>178717.65093388967</v>
+        <v>96864.0252095024</v>
       </c>
       <c r="L25" s="13">
         <f t="shared" si="7"/>
-        <v>172304.77592203219</v>
+        <v>90451.1501976449</v>
       </c>
       <c r="M25" s="13">
         <f t="shared" si="7"/>
-        <v>319580.97831441625</v>
+        <v>236651.67916061</v>
       </c>
       <c r="N25" s="12">
         <f t="shared" si="6"/>
-        <v>1289374.9928414652</v>
+        <v>503580.185887348</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.2">
@@ -11786,47 +11790,47 @@
       </c>
       <c r="C26" s="11">
         <f>C25</f>
-        <v>-429532.2925294193</v>
+        <v>-428456.6191</v>
       </c>
       <c r="D26" s="11">
         <f t="shared" ref="D26:M26" si="8">C26+D25</f>
-        <v>-369513.40952702682</v>
+        <v>-428286.755564678</v>
       </c>
       <c r="E26" s="11">
         <f t="shared" si="8"/>
-        <v>-234010.51056803903</v>
+        <v>-363900.638297639</v>
       </c>
       <c r="F26" s="11">
         <f t="shared" si="8"/>
-        <v>-65174.363092424406</v>
+        <v>-276918.116546412</v>
       </c>
       <c r="G26" s="11">
         <f t="shared" si="8"/>
-        <v>98175.916846689739</v>
+        <v>-195421.462331685</v>
       </c>
       <c r="H26" s="11">
         <f t="shared" si="8"/>
-        <v>255122.90884920279</v>
+        <v>-120328.096053559</v>
       </c>
       <c r="I26" s="11">
         <f t="shared" si="8"/>
-        <v>438312.16628220549</v>
+        <v>-18992.4643449433</v>
       </c>
       <c r="J26" s="11">
         <f t="shared" si="8"/>
-        <v>618771.58767112705</v>
+        <v>79613.3313195911</v>
       </c>
       <c r="K26" s="11">
         <f t="shared" si="8"/>
-        <v>797489.23860501673</v>
+        <v>176477.356529093</v>
       </c>
       <c r="L26" s="11">
         <f t="shared" si="8"/>
-        <v>969794.01452704892</v>
+        <v>266928.506726738</v>
       </c>
       <c r="M26" s="11">
         <f t="shared" si="8"/>
-        <v>1289374.9928414652</v>
+        <v>503580.185887348</v>
       </c>
       <c r="N26" s="11"/>
     </row>
@@ -11840,23 +11844,23 @@
       <c r="C27" s="48"/>
       <c r="D27" s="48">
         <f>IF('التكلفة الاستثمارية والتمويل'!D28&gt;0,('قائمة الدخل'!D10-'قائمة الدخل'!D19)/'التكلفة الاستثمارية والتمويل'!D28,"")</f>
-        <v>2.6854757947292249</v>
+        <v>1.00477018003118</v>
       </c>
       <c r="E27" s="48">
         <f>IF('التكلفة الاستثمارية والتمويل'!E28&gt;0,('قائمة الدخل'!E10-'قائمة الدخل'!E19)/'التكلفة الاستثمارية والتمويل'!E28,"")</f>
-        <v>4.8052500294267366</v>
+        <v>2.80811832445909</v>
       </c>
       <c r="F27" s="48">
         <f>IF('التكلفة الاستثمارية والتمويل'!F28&gt;0,('قائمة الدخل'!F10-'قائمة الدخل'!F19)/'التكلفة الاستثمارية والتمويل'!F28,"")</f>
-        <v>5.7413284888047409</v>
+        <v>3.44268016401368</v>
       </c>
       <c r="G27" s="48">
         <f>IF('التكلفة الاستثمارية والتمويل'!G28&gt;0,('قائمة الدخل'!G10-'قائمة الدخل'!G19)/'التكلفة الاستثمارية والتمويل'!G28,"")</f>
-        <v>5.5872720238503062</v>
+        <v>3.28862369905925</v>
       </c>
       <c r="H27" s="48">
         <f>IF('التكلفة الاستثمارية والتمويل'!H28&gt;0,('قائمة الدخل'!H10-'قائمة الدخل'!H19)/'التكلفة الاستثمارية والتمويل'!H28,"")</f>
-        <v>5.4074521690990514</v>
+        <v>3.10880384430799</v>
       </c>
       <c r="I27" s="48" t="str">
         <f>IF('التكلفة الاستثمارية والتمويل'!I28&gt;0,('قائمة الدخل'!I10-'قائمة الدخل'!I19)/'التكلفة الاستثمارية والتمويل'!I28,"")</f>
@@ -11953,7 +11957,7 @@
       </c>
       <c r="B6" s="13">
         <f>'التدفقات النقدية'!C14+NPV(DiscRate,'التدفقات النقدية'!D14:M14)</f>
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>75</v>
@@ -11968,7 +11972,7 @@
       </c>
       <c r="B7" s="19">
         <f>IFERROR(IRR('التدفقات النقدية'!C14:M14),"غير محدد")</f>
-        <v>0.26454717403704664</v>
+        <v>0.120581152696055</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>72</v>
@@ -11983,7 +11987,7 @@
       </c>
       <c r="B8" s="20">
         <f>IFERROR(IF('التدفقات النقدية'!M15&lt;0,"لا يُسترد خلال مدة الدراسة",COUNTIF('التدفقات النقدية'!C15:M15,"&lt;0")-1+(-INDEX('التدفقات النقدية'!C15:M15,COUNTIF('التدفقات النقدية'!C15:M15,"&lt;0")))/INDEX('التدفقات النقدية'!C14:M14,COUNTIF('التدفقات النقدية'!C15:M15,"&lt;0")+1)),"غير محدد")</f>
-        <v>3.5445623466150677</v>
+        <v>5.91064509269074</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>95</v>
@@ -11998,7 +12002,7 @@
       </c>
       <c r="B9" s="49">
         <f>IFERROR(IF('التدفقات النقدية'!M18&lt;0,"لا يُسترد خلال مدة الدراسة",COUNTIF('التدفقات النقدية'!C18:M18,"&lt;0")-1+(-INDEX('التدفقات النقدية'!C18:M18,COUNTIF('التدفقات النقدية'!C18:M18,"&lt;0")))/INDEX('التدفقات النقدية'!C17:M17,COUNTIF('التدفقات النقدية'!C18:M18,"&lt;0")+1)),"غير محدد")</f>
-        <v>4.7850624678644982</v>
+        <v>9.97924653282411</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>95</v>
@@ -12013,7 +12017,7 @@
       </c>
       <c r="B10" s="48">
         <f>IF('التدفقات النقدية'!C14&lt;0,(B6-'التدفقات النقدية'!C14)/(-'التدفقات النقدية'!C14),0)</f>
-        <v>1.7508415251712062</v>
+        <v>1.00273368979281</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>335</v>
@@ -12036,7 +12040,7 @@
       </c>
       <c r="B12" s="11">
         <f>'التدفقات النقدية'!C20+NPV(DiscRate,'التدفقات النقدية'!D20:M20)</f>
-        <v>635136.91040875483</v>
+        <v>201581.320955217</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>75</v>
@@ -12051,7 +12055,7 @@
       </c>
       <c r="B13" s="17">
         <f>IFERROR(IRR('التدفقات النقدية'!C20:M20),"غير محدد")</f>
-        <v>0.41139050779826225</v>
+        <v>0.221307060418343</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>72</v>
@@ -12072,7 +12076,7 @@
       </c>
       <c r="B15" s="17">
         <f>IFERROR(IRR('التدفقات النقدية'!C25:M25),"غير محدد")</f>
-        <v>0.30082550347675108</v>
+        <v>0.129995377872366</v>
       </c>
       <c r="C15" s="7" t="s">
         <v>72</v>
@@ -12087,7 +12091,7 @@
       </c>
       <c r="B16" s="48">
         <f>IF(Loan&gt;0,MIN('التدفقات النقدية'!D27:M27),"لا يوجد قرض")</f>
-        <v>2.6854757947292249</v>
+        <v>1.00477018003118</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>335</v>
@@ -12102,7 +12106,7 @@
       </c>
       <c r="B17" s="11">
         <f>MIN('التدفقات النقدية'!D26:M26)</f>
-        <v>-369513.40952702682</v>
+        <v>-428286.755564678</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>75</v>
@@ -12123,7 +12127,7 @@
       </c>
       <c r="B19" s="11">
         <f>AVERAGE('قائمة الدخل'!D20:M20)</f>
-        <v>128937.49928414651</v>
+        <v>50358.0185887348</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>75</v>
@@ -12136,7 +12140,7 @@
       </c>
       <c r="B20" s="17">
         <f>B19/TotalInv</f>
-        <v>0.22248544377292168</v>
+        <v>0.0870558256677658</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>72</v>
@@ -12149,7 +12153,7 @@
       </c>
       <c r="B21" s="17">
         <f>'قائمة الدخل'!N21</f>
-        <v>0.36719523512144409</v>
+        <v>0.239642741630584</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>72</v>
@@ -12164,7 +12168,7 @@
       </c>
       <c r="B22" s="18">
         <f>'التكاليف التشغيلية'!N30</f>
-        <v>29.911941466626136</v>
+        <v>29.3954116085616</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>156</v>
@@ -12198,7 +12202,7 @@
       </c>
       <c r="B25" s="11">
         <f>'التكاليف التشغيلية'!F23+'قائمة الدخل'!F11+'قائمة الدخل'!F12+'قائمة الدخل'!F14</f>
-        <v>281906.18871800567</v>
+        <v>281906.188718006</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>75</v>
@@ -12211,7 +12215,7 @@
       </c>
       <c r="B26" s="18">
         <f>IF(B24&gt;0,'التكاليف التشغيلية'!F25/B24,0)</f>
-        <v>5.4247330212352933</v>
+        <v>5.42473302123529</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>156</v>
@@ -12224,7 +12228,7 @@
       </c>
       <c r="B27" s="18">
         <f>الإيرادات!F6*(1-RoyaltyRate-CommunityRate)</f>
-        <v>44.432701109677417</v>
+        <v>36.3404</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>156</v>
@@ -12237,7 +12241,7 @@
       </c>
       <c r="B28" s="19">
         <f>IF(B24&gt;0,(B25/(B27-B26))/B24,0)</f>
-        <v>0.60730145279235459</v>
+        <v>0.76626506899756</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>72</v>
@@ -12252,7 +12256,7 @@
       </c>
       <c r="B29" s="30">
         <f>IF(B24&gt;0,(B25+'التكاليف التشغيلية'!F25)/(B24*(1-RoyaltyRate-CommunityRate)),0)</f>
-        <v>30.972690118961705</v>
+        <v>30.9726901189617</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>156</v>
@@ -12267,7 +12271,7 @@
       </c>
       <c r="B30" s="11">
         <f>B28*B24</f>
-        <v>7226.8872882290198</v>
+        <v>9118.55432107096</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>289</v>
@@ -12280,7 +12284,7 @@
       </c>
       <c r="B31" s="17">
         <f>1-B28</f>
-        <v>0.39269854720764541</v>
+        <v>0.23373493100244</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>72</v>
@@ -12420,19 +12424,19 @@
       </c>
       <c r="B13" s="12">
         <f>K_NPV</f>
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="C13" s="46">
         <f>K_IRR</f>
-        <v>0.26454717403704664</v>
+        <v>0.120581152696055</v>
       </c>
       <c r="D13" s="46">
         <f>K_IRRNew</f>
-        <v>0.41139050779826225</v>
+        <v>0.221307060418343</v>
       </c>
       <c r="G13" s="12">
         <f>K_NPV</f>
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="H13" s="50">
         <v>0.7</v>
@@ -12462,38 +12466,38 @@
       </c>
       <c r="B14" s="11">
         <f t="dataTable" ref="B14:D20" dt2D="0" dtr="0" r1="B5"/>
-        <v>-281846.2981841953</v>
-      </c>
-      <c r="C14" s="17">
-        <v>5.2600400048943285E-3</v>
+        <v>-637951.901716282</v>
+      </c>
+      <c r="C14" s="17" t="str">
+        <v>غير محدد</v>
       </c>
       <c r="D14" s="17">
-        <v>7.4787373907806654E-2</v>
+        <v>0.0747873739078067</v>
       </c>
       <c r="G14" s="50">
         <v>0.7</v>
       </c>
       <c r="H14" s="11">
         <f t="dataTable" ref="H14:N20" dt2D="1" dtr="1" r1="B6" r2="B5" ca="1"/>
-        <v>-868967.73006860795</v>
+        <v>-1118822.13511422</v>
       </c>
       <c r="I14" s="11">
-        <v>-672984.16583420662</v>
+        <v>-958532.057314909</v>
       </c>
       <c r="J14" s="11">
-        <v>-477000.60159980517</v>
+        <v>-798241.979515596</v>
       </c>
       <c r="K14" s="11">
-        <v>-281846.2981841953</v>
+        <v>-637951.901716282</v>
       </c>
       <c r="L14" s="11">
-        <v>-112617.08104269317</v>
+        <v>-477661.823916968</v>
       </c>
       <c r="M14" s="11">
-        <v>54338.377301782602</v>
+        <v>-317371.746117655</v>
       </c>
       <c r="N14" s="11">
-        <v>221008.93430519791</v>
+        <v>-174258.189350794</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.2">
@@ -12501,37 +12505,37 @@
         <v>0.8</v>
       </c>
       <c r="B15" s="11">
-        <v>-41042.055929756258</v>
+        <v>-408966.076288691</v>
       </c>
       <c r="C15" s="17">
-        <v>0.1047188261508547</v>
+        <v>-0.058490980108997</v>
       </c>
       <c r="D15" s="17">
-        <v>0.20084901427692947</v>
+        <v>0.200849014276929</v>
       </c>
       <c r="G15" s="50">
         <v>0.8</v>
       </c>
       <c r="H15" s="11">
-        <v>-672984.16583420639</v>
+        <v>-958532.057314909</v>
       </c>
       <c r="I15" s="11">
-        <v>-449002.94956631894</v>
+        <v>-775343.396972837</v>
       </c>
       <c r="J15" s="11">
-        <v>-232512.23087091412</v>
+        <v>-592154.736630764</v>
       </c>
       <c r="K15" s="11">
-        <v>-41042.055929756258</v>
+        <v>-408966.076288691</v>
       </c>
       <c r="L15" s="11">
-        <v>149632.94227067987</v>
+        <v>-233163.0026881</v>
       </c>
       <c r="M15" s="11">
-        <v>339968.92102939647</v>
+        <v>-76427.9607054128</v>
       </c>
       <c r="N15" s="11">
-        <v>530304.89978811354</v>
+        <v>79590.6026158477</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.2">
@@ -12539,37 +12543,37 @@
         <v>0.9</v>
       </c>
       <c r="B16" s="11">
-        <v>197216.93696035864</v>
+        <v>-193849.159019778</v>
       </c>
       <c r="C16" s="17">
-        <v>0.18883481911013655</v>
+        <v>0.0439009030281142</v>
       </c>
       <c r="D16" s="17">
-        <v>0.31047951239728233</v>
+        <v>0.310479512397282</v>
       </c>
       <c r="G16" s="50">
         <v>0.9</v>
       </c>
       <c r="H16" s="11">
-        <v>-477000.60159980494</v>
+        <v>-798241.979515596</v>
       </c>
       <c r="I16" s="11">
-        <v>-232512.23087091441</v>
+        <v>-592154.736630764</v>
       </c>
       <c r="J16" s="11">
-        <v>-17196.947621871484</v>
+        <v>-386067.493745932</v>
       </c>
       <c r="K16" s="11">
-        <v>197216.93696035864</v>
+        <v>-193849.159019778</v>
       </c>
       <c r="L16" s="11">
-        <v>411344.9130639151</v>
+        <v>-17920.9994599399</v>
       </c>
       <c r="M16" s="11">
-        <v>625472.88916747156</v>
+        <v>157496.46224931</v>
       </c>
       <c r="N16" s="11">
-        <v>839600.86527102836</v>
+        <v>332626.402776353</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.2">
@@ -12577,37 +12581,37 @@
         <v>1</v>
       </c>
       <c r="B17" s="11">
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="C17" s="17">
-        <v>0.26454717403704664</v>
+        <v>0.120581152696055</v>
       </c>
       <c r="D17" s="17">
-        <v>0.41139050779826225</v>
+        <v>0.411390507798262</v>
       </c>
       <c r="G17" s="50">
         <v>1</v>
       </c>
       <c r="H17" s="11">
-        <v>-281846.29818419518</v>
+        <v>-637951.901716282</v>
       </c>
       <c r="I17" s="11">
-        <v>-41042.055929756374</v>
+        <v>-408966.076288691</v>
       </c>
       <c r="J17" s="11">
-        <v>197216.93696035864</v>
+        <v>-193849.159019778</v>
       </c>
       <c r="K17" s="11">
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="L17" s="11">
-        <v>673056.88385715103</v>
+        <v>196414.226810875</v>
       </c>
       <c r="M17" s="11">
-        <v>910976.85730554746</v>
+        <v>391003.0496187</v>
       </c>
       <c r="N17" s="11">
-        <v>1148896.8307539434</v>
+        <v>585591.872426526</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.2">
@@ -12615,37 +12619,37 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B18" s="11">
-        <v>673056.88385715079</v>
+        <v>196414.226810875</v>
       </c>
       <c r="C18" s="17">
-        <v>0.33507552787463357</v>
+        <v>0.18856770024166</v>
       </c>
       <c r="D18" s="17">
-        <v>0.50724291837366309</v>
+        <v>0.507242918373663</v>
       </c>
       <c r="G18" s="50">
         <v>1.1000000000000001</v>
       </c>
       <c r="H18" s="11">
-        <v>-112617.08104269323</v>
+        <v>-477661.823916969</v>
       </c>
       <c r="I18" s="11">
-        <v>149632.94227067928</v>
+        <v>-233163.0026881</v>
       </c>
       <c r="J18" s="11">
-        <v>411344.9130639151</v>
+        <v>-17920.9994599401</v>
       </c>
       <c r="K18" s="11">
-        <v>673056.88385715079</v>
+        <v>196414.226810875</v>
       </c>
       <c r="L18" s="11">
-        <v>934768.85465038707</v>
+        <v>410461.931899483</v>
       </c>
       <c r="M18" s="11">
-        <v>1196480.8254436222</v>
+        <v>624509.636988091</v>
       </c>
       <c r="N18" s="11">
-        <v>1458192.7962368585</v>
+        <v>838557.342076699</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.2">
@@ -12653,37 +12657,37 @@
         <v>1.2</v>
       </c>
       <c r="B19" s="11">
-        <v>910976.85730554676</v>
+        <v>391003.0496187</v>
       </c>
       <c r="C19" s="17">
-        <v>0.40211116300409588</v>
+        <v>0.250961332276969</v>
       </c>
       <c r="D19" s="17">
-        <v>0.59977403678094365</v>
+        <v>0.599774036780944</v>
       </c>
       <c r="G19" s="50">
         <v>1.2</v>
       </c>
       <c r="H19" s="11">
-        <v>54338.377301782486</v>
+        <v>-317371.746117655</v>
       </c>
       <c r="I19" s="11">
-        <v>339968.92102939647</v>
+        <v>-76427.9607054128</v>
       </c>
       <c r="J19" s="11">
-        <v>625472.88916747156</v>
+        <v>157496.46224931</v>
       </c>
       <c r="K19" s="11">
-        <v>910976.85730554676</v>
+        <v>391003.0496187</v>
       </c>
       <c r="L19" s="11">
-        <v>1196480.8254436222</v>
+        <v>624509.636988091</v>
       </c>
       <c r="M19" s="11">
-        <v>1481984.7935816972</v>
+        <v>858016.224357482</v>
       </c>
       <c r="N19" s="11">
-        <v>1767488.7617197731</v>
+        <v>1091522.81172687</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.2">
@@ -12691,37 +12695,37 @@
         <v>1.3</v>
       </c>
       <c r="B20" s="11">
-        <v>1148896.8307539434</v>
+        <v>585591.872426526</v>
       </c>
       <c r="C20" s="17">
-        <v>0.46666158672718328</v>
+        <v>0.309623708771856</v>
       </c>
       <c r="D20" s="17">
-        <v>0.68997540927608814</v>
+        <v>0.689975409276088</v>
       </c>
       <c r="G20" s="50">
         <v>1.3</v>
       </c>
       <c r="H20" s="11">
-        <v>221008.93430519814</v>
+        <v>-174258.189350794</v>
       </c>
       <c r="I20" s="11">
-        <v>530304.89978811354</v>
+        <v>79590.6026158477</v>
       </c>
       <c r="J20" s="11">
-        <v>839600.86527102836</v>
+        <v>332626.402776353</v>
       </c>
       <c r="K20" s="11">
-        <v>1148896.8307539434</v>
+        <v>585591.872426526</v>
       </c>
       <c r="L20" s="11">
-        <v>1458192.7962368592</v>
+        <v>838557.3420767</v>
       </c>
       <c r="M20" s="11">
-        <v>1767488.7617197735</v>
+        <v>1091522.81172687</v>
       </c>
       <c r="N20" s="11">
-        <v>2076784.7272026881</v>
+        <v>1344488.28137705</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.2">
@@ -12765,18 +12769,20 @@
       </c>
       <c r="B24" s="12">
         <f>K_NPV</f>
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="C24" s="46">
         <f>K_IRR</f>
-        <v>0.26454717403704664</v>
+        <v>0.120581152696055</v>
       </c>
       <c r="D24" s="46">
         <f>K_IRRNew</f>
-        <v>0.41139050779826225</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>719</v>
+        <v>0.221307060418343</v>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>• معامل السعر يُطبَّق على سعر البيع المعتمد (المرجّح بين البيع المحلي والتصدير).</t>
+        </is>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.2">
@@ -12785,13 +12791,13 @@
       </c>
       <c r="B25" s="11">
         <f t="dataTable" ref="B25:D31" dt2D="0" dtr="0" r1="B6" ca="1"/>
-        <v>-281846.29818419518</v>
-      </c>
-      <c r="C25" s="17">
-        <v>5.2600400048945506E-3</v>
+        <v>-637951.901716282</v>
+      </c>
+      <c r="C25" s="17" t="str">
+        <v>غير محدد</v>
       </c>
       <c r="D25" s="17">
-        <v>7.4787373907806876E-2</v>
+        <v>0.0747873739078069</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>720</v>
@@ -12802,13 +12808,13 @@
         <v>0.8</v>
       </c>
       <c r="B26" s="11">
-        <v>-41042.055929756374</v>
+        <v>-408966.076288691</v>
       </c>
       <c r="C26" s="17">
-        <v>0.1047188261508547</v>
+        <v>-0.058490980108997</v>
       </c>
       <c r="D26" s="17">
-        <v>0.20084901427692947</v>
+        <v>0.200849014276929</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.2">
@@ -12816,13 +12822,13 @@
         <v>0.9</v>
       </c>
       <c r="B27" s="11">
-        <v>197216.93696035864</v>
+        <v>-193849.159019778</v>
       </c>
       <c r="C27" s="17">
-        <v>0.18883481911013655</v>
+        <v>0.0439009030281142</v>
       </c>
       <c r="D27" s="17">
-        <v>0.31047951239728233</v>
+        <v>0.310479512397282</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.2">
@@ -12830,13 +12836,13 @@
         <v>1</v>
       </c>
       <c r="B28" s="11">
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="C28" s="17">
-        <v>0.26454717403704664</v>
+        <v>0.120581152696055</v>
       </c>
       <c r="D28" s="17">
-        <v>0.41139050779826225</v>
+        <v>0.411390507798262</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.2">
@@ -12844,13 +12850,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B29" s="11">
-        <v>673056.88385715103</v>
+        <v>196414.226810875</v>
       </c>
       <c r="C29" s="17">
-        <v>0.33507552787463379</v>
+        <v>0.18856770024166</v>
       </c>
       <c r="D29" s="17">
-        <v>0.50724291837366287</v>
+        <v>0.507242918373663</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.2">
@@ -12858,13 +12864,13 @@
         <v>1.2</v>
       </c>
       <c r="B30" s="11">
-        <v>910976.85730554746</v>
+        <v>391003.0496187</v>
       </c>
       <c r="C30" s="17">
-        <v>0.40211116300409611</v>
+        <v>0.250961332276969</v>
       </c>
       <c r="D30" s="17">
-        <v>0.5997740367809441</v>
+        <v>0.599774036780944</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.2">
@@ -12872,13 +12878,13 @@
         <v>1.3</v>
       </c>
       <c r="B31" s="11">
-        <v>1148896.8307539434</v>
+        <v>585591.872426526</v>
       </c>
       <c r="C31" s="17">
-        <v>0.46666158672718328</v>
+        <v>0.309623708771856</v>
       </c>
       <c r="D31" s="17">
-        <v>0.68997540927608814</v>
+        <v>0.689975409276088</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -12909,15 +12915,15 @@
       </c>
       <c r="B35" s="12">
         <f>K_NPV</f>
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="C35" s="46">
         <f>K_IRR</f>
-        <v>0.26454717403704664</v>
+        <v>0.120581152696055</v>
       </c>
       <c r="D35" s="46">
         <f>K_IRRNew</f>
-        <v>0.41139050779826225</v>
+        <v>0.221307060418343</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.2">
@@ -12926,13 +12932,13 @@
       </c>
       <c r="B36" s="11">
         <f t="dataTable" ref="B36:D42" dt2D="0" dtr="0" r1="B7" ca="1"/>
-        <v>884644.98092915304</v>
+        <v>451333.474523447</v>
       </c>
       <c r="C36" s="17">
-        <v>0.4068232849741964</v>
+        <v>0.276319700931073</v>
       </c>
       <c r="D36" s="17">
-        <v>0.62021880082324699</v>
+        <v>0.620218800823247</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.2">
@@ -12940,13 +12946,13 @@
         <v>0.8</v>
       </c>
       <c r="B37" s="11">
-        <v>734808.95742235309</v>
+        <v>301497.451016647</v>
       </c>
       <c r="C37" s="17">
-        <v>0.35951671594550016</v>
+        <v>0.225977196652049</v>
       </c>
       <c r="D37" s="17">
-        <v>0.5490951113729392</v>
+        <v>0.549095111372939</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.2">
@@ -12954,13 +12960,13 @@
         <v>0.9</v>
       </c>
       <c r="B38" s="11">
-        <v>584972.93391555408</v>
+        <v>151661.427509848</v>
       </c>
       <c r="C38" s="17">
-        <v>0.31219345187230729</v>
+        <v>0.174366032490541</v>
       </c>
       <c r="D38" s="17">
-        <v>0.4796271777116885</v>
+        <v>0.479627177711689</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.2">
@@ -12968,13 +12974,13 @@
         <v>1</v>
       </c>
       <c r="B39" s="11">
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="C39" s="17">
-        <v>0.26454717403704664</v>
+        <v>0.120581152696055</v>
       </c>
       <c r="D39" s="17">
-        <v>0.41139050779826225</v>
+        <v>0.411390507798262</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.2">
@@ -12982,13 +12988,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B40" s="11">
-        <v>285300.88690195559</v>
+        <v>-148863.874557402</v>
       </c>
       <c r="C40" s="17">
-        <v>0.21618042970502604</v>
+        <v>0.0635201014710609</v>
       </c>
       <c r="D40" s="17">
-        <v>0.34386144067907587</v>
+        <v>0.343861440679076</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.2">
@@ -12996,13 +13002,13 @@
         <v>1.2</v>
       </c>
       <c r="B41" s="11">
-        <v>135421.98353462142</v>
+        <v>-302204.450134779</v>
       </c>
       <c r="C41" s="17">
-        <v>0.16653699378870468</v>
+        <v>0.000342121358056492</v>
       </c>
       <c r="D41" s="17">
-        <v>0.27630588519923127</v>
+        <v>0.276305885199231</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.2">
@@ -13010,13 +13016,13 @@
         <v>1.3</v>
       </c>
       <c r="B42" s="11">
-        <v>-14797.079812037526</v>
+        <v>-477431.995103442</v>
       </c>
       <c r="C42" s="17">
-        <v>0.1147927380330882</v>
+        <v>-0.0843588405910537</v>
       </c>
       <c r="D42" s="17">
-        <v>0.20757782315564954</v>
+        <v>0.20757782315565</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.2">
@@ -13047,15 +13053,15 @@
       </c>
       <c r="B46" s="12">
         <f>K_NPV</f>
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="C46" s="46">
         <f>K_IRR</f>
-        <v>0.26454717403704664</v>
+        <v>0.120581152696055</v>
       </c>
       <c r="D46" s="46">
         <f>K_IRRNew</f>
-        <v>0.41139050779826225</v>
+        <v>0.221307060418343</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.2">
@@ -13064,13 +13070,13 @@
       </c>
       <c r="B47" s="11">
         <f t="dataTable" ref="B47:D53" dt2D="0" dtr="0" r1="B8" ca="1"/>
-        <v>519731.58403294458</v>
+        <v>86316.6554531314</v>
       </c>
       <c r="C47" s="17">
-        <v>0.30895658481286103</v>
+        <v>0.154595903405399</v>
       </c>
       <c r="D47" s="17">
-        <v>0.50278108175134717</v>
+        <v>0.502781081751347</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.2">
@@ -13078,13 +13084,13 @@
         <v>0.8</v>
       </c>
       <c r="B48" s="11">
-        <v>491533.35949154804</v>
+        <v>58071.5439538268</v>
       </c>
       <c r="C48" s="17">
-        <v>0.29317339588130276</v>
+        <v>0.142583174004156</v>
       </c>
       <c r="D48" s="17">
-        <v>0.46886742137909754</v>
+        <v>0.468867421379098</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.2">
@@ -13092,13 +13098,13 @@
         <v>0.9</v>
       </c>
       <c r="B49" s="11">
-        <v>463335.13495015143</v>
+        <v>29826.4324545221</v>
       </c>
       <c r="C49" s="17">
-        <v>0.27840677208960374</v>
+        <v>0.131268997566915</v>
       </c>
       <c r="D49" s="17">
-        <v>0.43860905582612886</v>
+        <v>0.438609055826129</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.2">
@@ -13106,13 +13112,13 @@
         <v>1</v>
       </c>
       <c r="B50" s="11">
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="C50" s="17">
-        <v>0.26454717403704664</v>
+        <v>0.120581152696055</v>
       </c>
       <c r="D50" s="17">
-        <v>0.41139050779826225</v>
+        <v>0.411390507798262</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
@@ -13120,13 +13126,13 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="B51" s="11">
-        <v>406938.68586735846</v>
+        <v>-26663.7905440873</v>
       </c>
       <c r="C51" s="17">
-        <v>0.25150079152734972</v>
+        <v>0.110457528450198</v>
       </c>
       <c r="D51" s="17">
-        <v>0.38673002890122188</v>
+        <v>0.386730028901222</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.2">
@@ -13134,13 +13140,13 @@
         <v>1.2</v>
       </c>
       <c r="B52" s="11">
-        <v>378740.46132596186</v>
+        <v>-54908.902043392</v>
       </c>
       <c r="C52" s="17">
-        <v>0.23918677869445371</v>
+        <v>0.100844375485634</v>
       </c>
       <c r="D52" s="17">
-        <v>0.36424485977124643</v>
+        <v>0.364244859771246</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.2">
@@ -13148,13 +13154,13 @@
         <v>1.3</v>
       </c>
       <c r="B53" s="11">
-        <v>350542.2367845655</v>
+        <v>-83154.0135426967</v>
       </c>
       <c r="C53" s="17">
-        <v>0.22753505641651195</v>
+        <v>0.0916949123837525</v>
       </c>
       <c r="D53" s="17">
-        <v>0.34362682699351876</v>
+        <v>0.343626826993519</v>
       </c>
     </row>
   </sheetData>
@@ -13280,13 +13286,14 @@
       </c>
       <c r="B8" s="18">
         <f>SalePrice</f>
-        <v>47.268830967741934</v>
+        <v>38.66</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D8" s="16" t="s">
-        <v>68</v>
+      <c r="D8" s="16" t="str">
+        <f>"بيع محلي "&amp;TEXT(LocalShare,"0%")&amp;" + تصدير "&amp;TEXT(1-LocalShare,"0%")&amp;" — متوسط مرجّح من ورقة «السوق والسعر»"</f>
+        <v>بيع محلي 100% + تصدير 0% — متوسط مرجّح من ورقة «السوق والسعر»</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
@@ -13308,7 +13315,7 @@
       </c>
       <c r="B10" s="17">
         <f>'الموارد البشرية'!B22</f>
-        <v>0.45454545454545453</v>
+        <v>0.454545454545455</v>
       </c>
       <c r="C10" s="7" t="s">
         <v>72</v>
@@ -13329,7 +13336,7 @@
       </c>
       <c r="B12" s="13">
         <f>TotalInv</f>
-        <v>579532.2925294193</v>
+        <v>578456.6191</v>
       </c>
       <c r="C12" s="7" t="s">
         <v>75</v>
@@ -13359,7 +13366,7 @@
       </c>
       <c r="B14" s="11">
         <f>NewInv</f>
-        <v>379532.2925294193</v>
+        <v>378456.6191</v>
       </c>
       <c r="C14" s="7" t="s">
         <v>75</v>
@@ -13395,7 +13402,7 @@
       </c>
       <c r="B17" s="11">
         <f>الإيرادات!F7</f>
-        <v>562499.08851612906</v>
+        <v>460054</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>75</v>
@@ -13408,7 +13415,7 @@
       </c>
       <c r="B18" s="11">
         <f>'التكاليف التشغيلية'!F29</f>
-        <v>330710.18624566763</v>
+        <v>324563.4809347</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>75</v>
@@ -13421,7 +13428,7 @@
       </c>
       <c r="B19" s="18">
         <f>'التكاليف التشغيلية'!F30</f>
-        <v>27.790771953417448</v>
+        <v>27.2742420953529</v>
       </c>
       <c r="C19" s="7" t="s">
         <v>67</v>
@@ -13434,7 +13441,7 @@
       </c>
       <c r="B20" s="11">
         <f>'قائمة الدخل'!F10</f>
-        <v>231788.90227046143</v>
+        <v>135490.5190653</v>
       </c>
       <c r="C20" s="7" t="s">
         <v>75</v>
@@ -13447,7 +13454,7 @@
       </c>
       <c r="B21" s="11">
         <f>'قائمة الدخل'!F20</f>
-        <v>154945.3368042873</v>
+        <v>73091.7110799002</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>75</v>
@@ -13468,7 +13475,7 @@
       </c>
       <c r="B23" s="13">
         <f>K_NPV</f>
-        <v>435136.91040875483</v>
+        <v>1581.32095521735</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>75</v>
@@ -13483,7 +13490,7 @@
       </c>
       <c r="B24" s="19">
         <f>K_IRR</f>
-        <v>0.26454717403704664</v>
+        <v>0.120581152696055</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>72</v>
@@ -13498,7 +13505,7 @@
       </c>
       <c r="B25" s="17">
         <f>K_IRRNew</f>
-        <v>0.41139050779826225</v>
+        <v>0.221307060418343</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>72</v>
@@ -13513,7 +13520,7 @@
       </c>
       <c r="B26" s="20">
         <f>K_Payback</f>
-        <v>3.5445623466150677</v>
+        <v>5.91064509269074</v>
       </c>
       <c r="C26" s="7" t="s">
         <v>95</v>
@@ -13528,7 +13535,7 @@
       </c>
       <c r="B27" s="18">
         <f>'المؤشرات المالية'!B29</f>
-        <v>30.972690118961705</v>
+        <v>30.9726901189617</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>67</v>
@@ -13543,7 +13550,7 @@
       </c>
       <c r="B28" s="17">
         <f>'المؤشرات المالية'!B28</f>
-        <v>0.60730145279235459</v>
+        <v>0.76626506899756</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>72</v>
@@ -14308,8 +14315,9 @@
       <c r="B29" s="9" t="s">
         <v>842</v>
       </c>
-      <c r="C29" s="9" t="s">
-        <v>843</v>
+      <c r="C29" s="9" t="str">
+        <f>"بيع محلي "&amp;TEXT(LocalShare,"0%")&amp;" بسعر "&amp;TEXT(LocalPrice,"0.00")&amp;" ر.ع/طن"</f>
+        <v>بيع محلي 100% بسعر 38.66 ر.ع/طن</v>
       </c>
       <c r="D29" s="9" t="s">
         <v>844</v>
@@ -14737,23 +14745,23 @@
       </c>
       <c r="G6" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B6)*D6/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H6" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B6)*D6/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I6" s="31">
         <f>IF(D6&gt;0,H6/D6,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J6" s="11">
         <f>SUM($H$6:H6)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="K6" s="11">
         <f>OreReserve-SUM($G$6:G6)</f>
-        <v>139183.33333333334</v>
+        <v>139183.333333333</v>
       </c>
       <c r="M6" s="9" t="inlineStr">
         <is>
@@ -14790,23 +14798,23 @@
       </c>
       <c r="G7" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B7)*D7/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H7" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B7)*D7/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I7" s="31">
         <f>IF(D7&gt;0,H7/D7,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J7" s="11">
         <f>SUM($H$6:H7)</f>
-        <v>1388.3333333333333</v>
+        <v>1388.33333333333</v>
       </c>
       <c r="K7" s="11">
         <f>OreReserve-SUM($G$6:G7)</f>
-        <v>138366.66666666666</v>
+        <v>138366.666666667</v>
       </c>
       <c r="M7" s="9" t="inlineStr">
         <is>
@@ -14843,15 +14851,15 @@
       </c>
       <c r="G8" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B8)*D8/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H8" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B8)*D8/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I8" s="31">
         <f>IF(D8&gt;0,H8/D8,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J8" s="11">
         <f>SUM($H$6:H8)</f>
@@ -14896,23 +14904,23 @@
       </c>
       <c r="G9" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B9)*D9/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H9" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B9)*D9/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I9" s="31">
         <f>IF(D9&gt;0,H9/D9,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J9" s="11">
         <f>SUM($H$6:H9)</f>
-        <v>2776.6666666666665</v>
+        <v>2776.66666666667</v>
       </c>
       <c r="K9" s="11">
         <f>OreReserve-SUM($G$6:G9)</f>
-        <v>136733.33333333334</v>
+        <v>136733.333333333</v>
       </c>
       <c r="M9" s="9" t="inlineStr">
         <is>
@@ -14949,23 +14957,23 @@
       </c>
       <c r="G10" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B10)*D10/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H10" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B10)*D10/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I10" s="31">
         <f>IF(D10&gt;0,H10/D10,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J10" s="11">
         <f>SUM($H$6:H10)</f>
-        <v>3470.833333333333</v>
+        <v>3470.83333333333</v>
       </c>
       <c r="K10" s="11">
         <f>OreReserve-SUM($G$6:G10)</f>
-        <v>135916.66666666666</v>
+        <v>135916.666666667</v>
       </c>
       <c r="M10" s="9" t="inlineStr">
         <is>
@@ -15002,15 +15010,15 @@
       </c>
       <c r="G11" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B11)*D11/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H11" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B11)*D11/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I11" s="31">
         <f>IF(D11&gt;0,H11/D11,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J11" s="11">
         <f>SUM($H$6:H11)</f>
@@ -15055,23 +15063,23 @@
       </c>
       <c r="G12" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B12)*D12/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H12" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B12)*D12/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I12" s="31">
         <f>IF(D12&gt;0,H12/D12,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J12" s="11">
         <f>SUM($H$6:H12)</f>
-        <v>4859.166666666667</v>
+        <v>4859.16666666667</v>
       </c>
       <c r="K12" s="11">
         <f>OreReserve-SUM($G$6:G12)</f>
-        <v>134283.33333333334</v>
+        <v>134283.333333333</v>
       </c>
       <c r="M12" s="9" t="inlineStr">
         <is>
@@ -15108,23 +15116,23 @@
       </c>
       <c r="G13" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B13)*D13/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H13" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B13)*D13/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I13" s="31">
         <f>IF(D13&gt;0,H13/D13,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J13" s="11">
         <f>SUM($H$6:H13)</f>
-        <v>5553.333333333334</v>
+        <v>5553.33333333333</v>
       </c>
       <c r="K13" s="11">
         <f>OreReserve-SUM($G$6:G13)</f>
-        <v>133466.66666666666</v>
+        <v>133466.666666667</v>
       </c>
       <c r="M13" s="9" t="inlineStr">
         <is>
@@ -15161,19 +15169,19 @@
       </c>
       <c r="G14" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B14)*D14/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H14" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B14)*D14/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I14" s="31">
         <f>IF(D14&gt;0,H14/D14,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J14" s="11">
         <f>SUM($H$6:H14)</f>
-        <v>6247.500000000001</v>
+        <v>6247.5</v>
       </c>
       <c r="K14" s="11">
         <f>OreReserve-SUM($G$6:G14)</f>
@@ -15214,23 +15222,23 @@
       </c>
       <c r="G15" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B15)*D15/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H15" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B15)*D15/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I15" s="31">
         <f>IF(D15&gt;0,H15/D15,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J15" s="11">
         <f>SUM($H$6:H15)</f>
-        <v>6941.666666666668</v>
+        <v>6941.66666666667</v>
       </c>
       <c r="K15" s="11">
         <f>OreReserve-SUM($G$6:G15)</f>
-        <v>131833.33333333334</v>
+        <v>131833.333333333</v>
       </c>
       <c r="M15" s="9" t="inlineStr">
         <is>
@@ -15267,23 +15275,23 @@
       </c>
       <c r="G16" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B16)*D16/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H16" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B16)*D16/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I16" s="31">
         <f>IF(D16&gt;0,H16/D16,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J16" s="11">
         <f>SUM($H$6:H16)</f>
-        <v>7635.833333333335</v>
+        <v>7635.83333333333</v>
       </c>
       <c r="K16" s="11">
         <f>OreReserve-SUM($G$6:G16)</f>
-        <v>131016.66666666667</v>
+        <v>131016.666666667</v>
       </c>
       <c r="M16" s="9" t="inlineStr">
         <is>
@@ -15320,19 +15328,19 @@
       </c>
       <c r="G17" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B17)*D17/$N$18,0)</f>
-        <v>816.6666666666666</v>
+        <v>816.666666666667</v>
       </c>
       <c r="H17" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B17)*D17/$N$18,0)</f>
-        <v>694.1666666666666</v>
+        <v>694.166666666667</v>
       </c>
       <c r="I17" s="31">
         <f>IF(D17&gt;0,H17/D17,0)</f>
-        <v>27.766666666666666</v>
+        <v>27.7666666666667</v>
       </c>
       <c r="J17" s="11">
         <f>SUM($H$6:H17)</f>
-        <v>8330.000000000002</v>
+        <v>8330</v>
       </c>
       <c r="K17" s="11">
         <f>OreReserve-SUM($G$6:G17)</f>
@@ -15385,7 +15393,7 @@
       </c>
       <c r="J18" s="11">
         <f>SUM($H$6:H18)</f>
-        <v>9222.500000000002</v>
+        <v>9222.5</v>
       </c>
       <c r="K18" s="11">
         <f>OreReserve-SUM($G$6:G18)</f>
@@ -15439,7 +15447,7 @@
       </c>
       <c r="J19" s="11">
         <f>SUM($H$6:H19)</f>
-        <v>10115.000000000002</v>
+        <v>10115</v>
       </c>
       <c r="K19" s="11">
         <f>OreReserve-SUM($G$6:G19)</f>
@@ -15493,7 +15501,7 @@
       </c>
       <c r="J20" s="11">
         <f>SUM($H$6:H20)</f>
-        <v>11007.500000000002</v>
+        <v>11007.5</v>
       </c>
       <c r="K20" s="11">
         <f>OreReserve-SUM($G$6:G20)</f>
@@ -15547,7 +15555,7 @@
       </c>
       <c r="J21" s="11">
         <f>SUM($H$6:H21)</f>
-        <v>11900.000000000002</v>
+        <v>11900</v>
       </c>
       <c r="K21" s="11">
         <f>OreReserve-SUM($G$6:G21)</f>
@@ -15601,7 +15609,7 @@
       </c>
       <c r="J22" s="11">
         <f>SUM($H$6:H22)</f>
-        <v>12792.500000000002</v>
+        <v>12792.5</v>
       </c>
       <c r="K22" s="11">
         <f>OreReserve-SUM($G$6:G22)</f>
@@ -15651,7 +15659,7 @@
       </c>
       <c r="J23" s="11">
         <f>SUM($H$6:H23)</f>
-        <v>13685.000000000002</v>
+        <v>13685</v>
       </c>
       <c r="K23" s="11">
         <f>OreReserve-SUM($G$6:G23)</f>
@@ -15696,7 +15704,7 @@
       </c>
       <c r="J24" s="11">
         <f>SUM($H$6:H24)</f>
-        <v>14577.500000000002</v>
+        <v>14577.5</v>
       </c>
       <c r="K24" s="11">
         <f>OreReserve-SUM($G$6:G24)</f>
@@ -15749,7 +15757,7 @@
       </c>
       <c r="J25" s="11">
         <f>SUM($H$6:H25)</f>
-        <v>15470.000000000002</v>
+        <v>15470</v>
       </c>
       <c r="K25" s="11">
         <f>OreReserve-SUM($G$6:G25)</f>
@@ -15814,7 +15822,7 @@
       </c>
       <c r="J26" s="11">
         <f>SUM($H$6:H26)</f>
-        <v>16362.500000000002</v>
+        <v>16362.5</v>
       </c>
       <c r="K26" s="11">
         <f>OreReserve-SUM($G$6:G26)</f>
@@ -16042,23 +16050,23 @@
       </c>
       <c r="G30" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B30)*D30/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H30" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B30)*D30/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I30" s="31">
         <f>IF(D30&gt;0,H30/D30,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J30" s="11">
         <f>SUM($H$6:H30)</f>
-        <v>20031.666666666668</v>
+        <v>20031.6666666667</v>
       </c>
       <c r="K30" s="11">
         <f>OreReserve-SUM($G$6:G30)</f>
-        <v>116433.33333333333</v>
+        <v>116433.333333333</v>
       </c>
       <c r="M30" s="7">
         <v>5</v>
@@ -16102,23 +16110,23 @@
       </c>
       <c r="G31" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B31)*D31/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H31" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B31)*D31/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I31" s="31">
         <f>IF(D31&gt;0,H31/D31,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J31" s="11">
         <f>SUM($H$6:H31)</f>
-        <v>21023.333333333336</v>
+        <v>21023.3333333333</v>
       </c>
       <c r="K31" s="11">
         <f>OreReserve-SUM($G$6:G31)</f>
-        <v>115266.66666666666</v>
+        <v>115266.666666667</v>
       </c>
       <c r="M31" s="7">
         <v>6</v>
@@ -16162,19 +16170,19 @@
       </c>
       <c r="G32" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B32)*D32/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H32" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B32)*D32/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I32" s="31">
         <f>IF(D32&gt;0,H32/D32,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J32" s="11">
         <f>SUM($H$6:H32)</f>
-        <v>22015.000000000004</v>
+        <v>22015</v>
       </c>
       <c r="K32" s="11">
         <f>OreReserve-SUM($G$6:G32)</f>
@@ -16222,23 +16230,23 @@
       </c>
       <c r="G33" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B33)*D33/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H33" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B33)*D33/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I33" s="31">
         <f>IF(D33&gt;0,H33/D33,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J33" s="11">
         <f>SUM($H$6:H33)</f>
-        <v>23006.66666666667</v>
+        <v>23006.6666666667</v>
       </c>
       <c r="K33" s="11">
         <f>OreReserve-SUM($G$6:G33)</f>
-        <v>112933.33333333333</v>
+        <v>112933.333333333</v>
       </c>
       <c r="M33" s="7">
         <v>8</v>
@@ -16282,23 +16290,23 @@
       </c>
       <c r="G34" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B34)*D34/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H34" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B34)*D34/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I34" s="31">
         <f>IF(D34&gt;0,H34/D34,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J34" s="11">
         <f>SUM($H$6:H34)</f>
-        <v>23998.33333333334</v>
+        <v>23998.3333333333</v>
       </c>
       <c r="K34" s="11">
         <f>OreReserve-SUM($G$6:G34)</f>
-        <v>111766.66666666666</v>
+        <v>111766.666666667</v>
       </c>
       <c r="M34" s="7">
         <v>9</v>
@@ -16342,19 +16350,19 @@
       </c>
       <c r="G35" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B35)*D35/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H35" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B35)*D35/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I35" s="31">
         <f>IF(D35&gt;0,H35/D35,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J35" s="11">
         <f>SUM($H$6:H35)</f>
-        <v>24990.000000000007</v>
+        <v>24990</v>
       </c>
       <c r="K35" s="11">
         <f>OreReserve-SUM($G$6:G35)</f>
@@ -16402,23 +16410,23 @@
       </c>
       <c r="G36" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B36)*D36/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H36" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B36)*D36/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I36" s="31">
         <f>IF(D36&gt;0,H36/D36,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J36" s="11">
         <f>SUM($H$6:H36)</f>
-        <v>25981.666666666675</v>
+        <v>25981.6666666667</v>
       </c>
       <c r="K36" s="11">
         <f>OreReserve-SUM($G$6:G36)</f>
-        <v>109433.33333333333</v>
+        <v>109433.333333333</v>
       </c>
       <c r="M36" s="32" t="inlineStr">
         <is>
@@ -16464,23 +16472,23 @@
       </c>
       <c r="G37" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B37)*D37/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H37" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B37)*D37/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I37" s="31">
         <f>IF(D37&gt;0,H37/D37,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J37" s="11">
         <f>SUM($H$6:H37)</f>
-        <v>26973.333333333343</v>
+        <v>26973.3333333333</v>
       </c>
       <c r="K37" s="11">
         <f>OreReserve-SUM($G$6:G37)</f>
-        <v>108266.66666666666</v>
+        <v>108266.666666667</v>
       </c>
       <c r="M37" s="32" t="inlineStr">
         <is>
@@ -16518,19 +16526,19 @@
       </c>
       <c r="G38" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B38)*D38/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H38" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B38)*D38/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I38" s="31">
         <f>IF(D38&gt;0,H38/D38,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J38" s="11">
         <f>SUM($H$6:H38)</f>
-        <v>27965.00000000001</v>
+        <v>27965</v>
       </c>
       <c r="K38" s="11">
         <f>OreReserve-SUM($G$6:G38)</f>
@@ -16563,23 +16571,23 @@
       </c>
       <c r="G39" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B39)*D39/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H39" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B39)*D39/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I39" s="31">
         <f>IF(D39&gt;0,H39/D39,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J39" s="11">
         <f>SUM($H$6:H39)</f>
-        <v>28956.66666666668</v>
+        <v>28956.6666666667</v>
       </c>
       <c r="K39" s="11">
         <f>OreReserve-SUM($G$6:G39)</f>
-        <v>105933.33333333333</v>
+        <v>105933.333333333</v>
       </c>
     </row>
     <row r="40">
@@ -16608,23 +16616,23 @@
       </c>
       <c r="G40" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B40)*D40/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H40" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B40)*D40/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I40" s="31">
         <f>IF(D40&gt;0,H40/D40,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J40" s="11">
         <f>SUM($H$6:H40)</f>
-        <v>29948.333333333347</v>
+        <v>29948.3333333333</v>
       </c>
       <c r="K40" s="11">
         <f>OreReserve-SUM($G$6:G40)</f>
-        <v>104766.66666666666</v>
+        <v>104766.666666667</v>
       </c>
     </row>
     <row r="41">
@@ -16653,19 +16661,19 @@
       </c>
       <c r="G41" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B41)*D41/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H41" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B41)*D41/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I41" s="31">
         <f>IF(D41&gt;0,H41/D41,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J41" s="11">
         <f>SUM($H$6:H41)</f>
-        <v>30940.000000000015</v>
+        <v>30940</v>
       </c>
       <c r="K41" s="11">
         <f>OreReserve-SUM($G$6:G41)</f>
@@ -16698,23 +16706,23 @@
       </c>
       <c r="G42" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B42)*D42/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H42" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B42)*D42/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I42" s="31">
         <f>IF(D42&gt;0,H42/D42,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J42" s="11">
         <f>SUM($H$6:H42)</f>
-        <v>31931.666666666682</v>
+        <v>31931.6666666667</v>
       </c>
       <c r="K42" s="11">
         <f>OreReserve-SUM($G$6:G42)</f>
-        <v>102433.33333333334</v>
+        <v>102433.333333333</v>
       </c>
     </row>
     <row r="43">
@@ -16743,23 +16751,23 @@
       </c>
       <c r="G43" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B43)*D43/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H43" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B43)*D43/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I43" s="31">
         <f>IF(D43&gt;0,H43/D43,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J43" s="11">
         <f>SUM($H$6:H43)</f>
-        <v>32923.33333333335</v>
+        <v>32923.3333333333</v>
       </c>
       <c r="K43" s="11">
         <f>OreReserve-SUM($G$6:G43)</f>
-        <v>101266.66666666667</v>
+        <v>101266.666666667</v>
       </c>
     </row>
     <row r="44">
@@ -16788,19 +16796,19 @@
       </c>
       <c r="G44" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B44)*D44/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H44" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B44)*D44/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I44" s="31">
         <f>IF(D44&gt;0,H44/D44,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J44" s="11">
         <f>SUM($H$6:H44)</f>
-        <v>33915.000000000015</v>
+        <v>33915</v>
       </c>
       <c r="K44" s="11">
         <f>OreReserve-SUM($G$6:G44)</f>
@@ -16833,23 +16841,23 @@
       </c>
       <c r="G45" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B45)*D45/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H45" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B45)*D45/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I45" s="31">
         <f>IF(D45&gt;0,H45/D45,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J45" s="11">
         <f>SUM($H$6:H45)</f>
-        <v>34906.66666666668</v>
+        <v>34906.6666666667</v>
       </c>
       <c r="K45" s="11">
         <f>OreReserve-SUM($G$6:G45)</f>
-        <v>98933.33333333334</v>
+        <v>98933.3333333333</v>
       </c>
     </row>
     <row r="46">
@@ -16878,23 +16886,23 @@
       </c>
       <c r="G46" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B46)*D46/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H46" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B46)*D46/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I46" s="31">
         <f>IF(D46&gt;0,H46/D46,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J46" s="11">
         <f>SUM($H$6:H46)</f>
-        <v>35898.33333333334</v>
+        <v>35898.3333333333</v>
       </c>
       <c r="K46" s="11">
         <f>OreReserve-SUM($G$6:G46)</f>
-        <v>97766.66666666669</v>
+        <v>97766.6666666667</v>
       </c>
     </row>
     <row r="47">
@@ -16923,23 +16931,23 @@
       </c>
       <c r="G47" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B47)*D47/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H47" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B47)*D47/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I47" s="31">
         <f>IF(D47&gt;0,H47/D47,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J47" s="11">
         <f>SUM($H$6:H47)</f>
-        <v>36890.00000000001</v>
+        <v>36890</v>
       </c>
       <c r="K47" s="11">
         <f>OreReserve-SUM($G$6:G47)</f>
-        <v>96600.00000000001</v>
+        <v>96600</v>
       </c>
     </row>
     <row r="48">
@@ -16968,23 +16976,23 @@
       </c>
       <c r="G48" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B48)*D48/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H48" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B48)*D48/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I48" s="31">
         <f>IF(D48&gt;0,H48/D48,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J48" s="11">
         <f>SUM($H$6:H48)</f>
-        <v>37881.66666666667</v>
+        <v>37881.6666666667</v>
       </c>
       <c r="K48" s="11">
         <f>OreReserve-SUM($G$6:G48)</f>
-        <v>95433.33333333334</v>
+        <v>95433.3333333333</v>
       </c>
     </row>
     <row r="49">
@@ -17013,23 +17021,23 @@
       </c>
       <c r="G49" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B49)*D49/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H49" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B49)*D49/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I49" s="31">
         <f>IF(D49&gt;0,H49/D49,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J49" s="11">
         <f>SUM($H$6:H49)</f>
-        <v>38873.333333333336</v>
+        <v>38873.3333333333</v>
       </c>
       <c r="K49" s="11">
         <f>OreReserve-SUM($G$6:G49)</f>
-        <v>94266.66666666669</v>
+        <v>94266.6666666667</v>
       </c>
     </row>
     <row r="50">
@@ -17058,15 +17066,15 @@
       </c>
       <c r="G50" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B50)*D50/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H50" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B50)*D50/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I50" s="31">
         <f>IF(D50&gt;0,H50/D50,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J50" s="11">
         <f>SUM($H$6:H50)</f>
@@ -17074,7 +17082,7 @@
       </c>
       <c r="K50" s="11">
         <f>OreReserve-SUM($G$6:G50)</f>
-        <v>93100.00000000003</v>
+        <v>93100</v>
       </c>
     </row>
     <row r="51">
@@ -17103,23 +17111,23 @@
       </c>
       <c r="G51" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B51)*D51/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H51" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B51)*D51/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I51" s="31">
         <f>IF(D51&gt;0,H51/D51,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J51" s="11">
         <f>SUM($H$6:H51)</f>
-        <v>40856.666666666664</v>
+        <v>40856.6666666667</v>
       </c>
       <c r="K51" s="11">
         <f>OreReserve-SUM($G$6:G51)</f>
-        <v>91933.33333333336</v>
+        <v>91933.3333333333</v>
       </c>
     </row>
     <row r="52">
@@ -17148,23 +17156,23 @@
       </c>
       <c r="G52" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B52)*D52/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H52" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B52)*D52/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I52" s="31">
         <f>IF(D52&gt;0,H52/D52,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J52" s="11">
         <f>SUM($H$6:H52)</f>
-        <v>41848.33333333333</v>
+        <v>41848.3333333333</v>
       </c>
       <c r="K52" s="11">
         <f>OreReserve-SUM($G$6:G52)</f>
-        <v>90766.66666666669</v>
+        <v>90766.6666666667</v>
       </c>
     </row>
     <row r="53">
@@ -17193,23 +17201,23 @@
       </c>
       <c r="G53" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B53)*D53/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H53" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B53)*D53/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I53" s="31">
         <f>IF(D53&gt;0,H53/D53,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J53" s="11">
         <f>SUM($H$6:H53)</f>
-        <v>42839.99999999999</v>
+        <v>42840</v>
       </c>
       <c r="K53" s="11">
         <f>OreReserve-SUM($G$6:G53)</f>
-        <v>89600.00000000003</v>
+        <v>89600</v>
       </c>
     </row>
     <row r="54">
@@ -17238,23 +17246,23 @@
       </c>
       <c r="G54" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B54)*D54/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H54" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B54)*D54/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I54" s="31">
         <f>IF(D54&gt;0,H54/D54,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J54" s="11">
         <f>SUM($H$6:H54)</f>
-        <v>43831.66666666666</v>
+        <v>43831.6666666667</v>
       </c>
       <c r="K54" s="11">
         <f>OreReserve-SUM($G$6:G54)</f>
-        <v>88433.33333333337</v>
+        <v>88433.3333333333</v>
       </c>
     </row>
     <row r="55">
@@ -17283,19 +17291,19 @@
       </c>
       <c r="G55" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B55)*D55/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H55" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B55)*D55/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I55" s="31">
         <f>IF(D55&gt;0,H55/D55,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J55" s="11">
         <f>SUM($H$6:H55)</f>
-        <v>44823.33333333332</v>
+        <v>44823.3333333333</v>
       </c>
       <c r="K55" s="11">
         <f>OreReserve-SUM($G$6:G55)</f>
@@ -17328,23 +17336,23 @@
       </c>
       <c r="G56" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B56)*D56/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H56" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B56)*D56/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I56" s="31">
         <f>IF(D56&gt;0,H56/D56,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J56" s="11">
         <f>SUM($H$6:H56)</f>
-        <v>45814.999999999985</v>
+        <v>45815</v>
       </c>
       <c r="K56" s="11">
         <f>OreReserve-SUM($G$6:G56)</f>
-        <v>86100.00000000003</v>
+        <v>86100</v>
       </c>
     </row>
     <row r="57">
@@ -17373,23 +17381,23 @@
       </c>
       <c r="G57" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B57)*D57/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H57" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B57)*D57/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I57" s="31">
         <f>IF(D57&gt;0,H57/D57,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J57" s="11">
         <f>SUM($H$6:H57)</f>
-        <v>46806.66666666665</v>
+        <v>46806.6666666667</v>
       </c>
       <c r="K57" s="11">
         <f>OreReserve-SUM($G$6:G57)</f>
-        <v>84933.33333333337</v>
+        <v>84933.3333333333</v>
       </c>
     </row>
     <row r="58">
@@ -17418,23 +17426,23 @@
       </c>
       <c r="G58" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B58)*D58/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H58" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B58)*D58/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I58" s="31">
         <f>IF(D58&gt;0,H58/D58,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J58" s="11">
         <f>SUM($H$6:H58)</f>
-        <v>47798.333333333314</v>
+        <v>47798.3333333333</v>
       </c>
       <c r="K58" s="11">
         <f>OreReserve-SUM($G$6:G58)</f>
-        <v>83766.66666666672</v>
+        <v>83766.6666666667</v>
       </c>
     </row>
     <row r="59">
@@ -17463,23 +17471,23 @@
       </c>
       <c r="G59" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B59)*D59/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H59" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B59)*D59/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I59" s="31">
         <f>IF(D59&gt;0,H59/D59,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J59" s="11">
         <f>SUM($H$6:H59)</f>
-        <v>48789.99999999998</v>
+        <v>48790</v>
       </c>
       <c r="K59" s="11">
         <f>OreReserve-SUM($G$6:G59)</f>
-        <v>82600.00000000004</v>
+        <v>82600</v>
       </c>
     </row>
     <row r="60">
@@ -17508,23 +17516,23 @@
       </c>
       <c r="G60" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B60)*D60/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H60" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B60)*D60/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I60" s="31">
         <f>IF(D60&gt;0,H60/D60,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J60" s="11">
         <f>SUM($H$6:H60)</f>
-        <v>49781.66666666664</v>
+        <v>49781.6666666667</v>
       </c>
       <c r="K60" s="11">
         <f>OreReserve-SUM($G$6:G60)</f>
-        <v>81433.33333333337</v>
+        <v>81433.3333333333</v>
       </c>
     </row>
     <row r="61">
@@ -17553,23 +17561,23 @@
       </c>
       <c r="G61" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B61)*D61/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H61" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B61)*D61/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I61" s="31">
         <f>IF(D61&gt;0,H61/D61,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J61" s="11">
         <f>SUM($H$6:H61)</f>
-        <v>50773.33333333331</v>
+        <v>50773.3333333333</v>
       </c>
       <c r="K61" s="11">
         <f>OreReserve-SUM($G$6:G61)</f>
-        <v>80266.66666666672</v>
+        <v>80266.6666666667</v>
       </c>
     </row>
     <row r="62">
@@ -17598,23 +17606,23 @@
       </c>
       <c r="G62" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B62)*D62/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H62" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B62)*D62/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I62" s="31">
         <f>IF(D62&gt;0,H62/D62,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J62" s="11">
         <f>SUM($H$6:H62)</f>
-        <v>51764.99999999997</v>
+        <v>51765</v>
       </c>
       <c r="K62" s="11">
         <f>OreReserve-SUM($G$6:G62)</f>
-        <v>79100.00000000006</v>
+        <v>79100</v>
       </c>
     </row>
     <row r="63">
@@ -17643,23 +17651,23 @@
       </c>
       <c r="G63" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B63)*D63/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H63" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B63)*D63/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I63" s="31">
         <f>IF(D63&gt;0,H63/D63,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J63" s="11">
         <f>SUM($H$6:H63)</f>
-        <v>52756.666666666635</v>
+        <v>52756.6666666667</v>
       </c>
       <c r="K63" s="11">
         <f>OreReserve-SUM($G$6:G63)</f>
-        <v>77933.33333333339</v>
+        <v>77933.3333333333</v>
       </c>
     </row>
     <row r="64">
@@ -17688,15 +17696,15 @@
       </c>
       <c r="G64" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B64)*D64/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H64" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B64)*D64/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I64" s="31">
         <f>IF(D64&gt;0,H64/D64,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J64" s="11">
         <f>SUM($H$6:H64)</f>
@@ -17704,7 +17712,7 @@
       </c>
       <c r="K64" s="11">
         <f>OreReserve-SUM($G$6:G64)</f>
-        <v>76766.66666666672</v>
+        <v>76766.6666666667</v>
       </c>
     </row>
     <row r="65">
@@ -17733,23 +17741,23 @@
       </c>
       <c r="G65" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B65)*D65/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H65" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B65)*D65/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I65" s="31">
         <f>IF(D65&gt;0,H65/D65,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J65" s="11">
         <f>SUM($H$6:H65)</f>
-        <v>54739.99999999996</v>
+        <v>54740</v>
       </c>
       <c r="K65" s="11">
         <f>OreReserve-SUM($G$6:G65)</f>
-        <v>75600.00000000006</v>
+        <v>75600</v>
       </c>
     </row>
     <row r="66">
@@ -17778,23 +17786,23 @@
       </c>
       <c r="G66" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B66)*D66/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H66" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B66)*D66/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I66" s="31">
         <f>IF(D66&gt;0,H66/D66,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J66" s="11">
         <f>SUM($H$6:H66)</f>
-        <v>55731.66666666663</v>
+        <v>55731.6666666667</v>
       </c>
       <c r="K66" s="11">
         <f>OreReserve-SUM($G$6:G66)</f>
-        <v>74433.33333333339</v>
+        <v>74433.3333333333</v>
       </c>
     </row>
     <row r="67">
@@ -17823,23 +17831,23 @@
       </c>
       <c r="G67" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B67)*D67/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H67" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B67)*D67/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I67" s="31">
         <f>IF(D67&gt;0,H67/D67,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J67" s="11">
         <f>SUM($H$6:H67)</f>
-        <v>56723.33333333329</v>
+        <v>56723.3333333333</v>
       </c>
       <c r="K67" s="11">
         <f>OreReserve-SUM($G$6:G67)</f>
-        <v>73266.66666666672</v>
+        <v>73266.6666666667</v>
       </c>
     </row>
     <row r="68">
@@ -17868,23 +17876,23 @@
       </c>
       <c r="G68" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B68)*D68/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H68" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B68)*D68/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I68" s="31">
         <f>IF(D68&gt;0,H68/D68,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J68" s="11">
         <f>SUM($H$6:H68)</f>
-        <v>57714.999999999956</v>
+        <v>57715</v>
       </c>
       <c r="K68" s="11">
         <f>OreReserve-SUM($G$6:G68)</f>
-        <v>72100.00000000004</v>
+        <v>72100</v>
       </c>
     </row>
     <row r="69">
@@ -17913,23 +17921,23 @@
       </c>
       <c r="G69" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B69)*D69/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H69" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B69)*D69/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I69" s="31">
         <f>IF(D69&gt;0,H69/D69,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J69" s="11">
         <f>SUM($H$6:H69)</f>
-        <v>58706.66666666662</v>
+        <v>58706.6666666667</v>
       </c>
       <c r="K69" s="11">
         <f>OreReserve-SUM($G$6:G69)</f>
-        <v>70933.33333333337</v>
+        <v>70933.3333333333</v>
       </c>
     </row>
     <row r="70">
@@ -17958,19 +17966,19 @@
       </c>
       <c r="G70" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B70)*D70/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H70" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B70)*D70/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I70" s="31">
         <f>IF(D70&gt;0,H70/D70,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J70" s="11">
         <f>SUM($H$6:H70)</f>
-        <v>59698.333333333285</v>
+        <v>59698.3333333333</v>
       </c>
       <c r="K70" s="11">
         <f>OreReserve-SUM($G$6:G70)</f>
@@ -18003,23 +18011,23 @@
       </c>
       <c r="G71" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B71)*D71/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H71" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B71)*D71/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I71" s="31">
         <f>IF(D71&gt;0,H71/D71,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J71" s="11">
         <f>SUM($H$6:H71)</f>
-        <v>60689.99999999995</v>
+        <v>60690</v>
       </c>
       <c r="K71" s="11">
         <f>OreReserve-SUM($G$6:G71)</f>
-        <v>68600.00000000003</v>
+        <v>68600</v>
       </c>
     </row>
     <row r="72">
@@ -18048,23 +18056,23 @@
       </c>
       <c r="G72" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B72)*D72/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H72" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B72)*D72/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I72" s="31">
         <f>IF(D72&gt;0,H72/D72,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J72" s="11">
         <f>SUM($H$6:H72)</f>
-        <v>61681.66666666661</v>
+        <v>61681.6666666667</v>
       </c>
       <c r="K72" s="11">
         <f>OreReserve-SUM($G$6:G72)</f>
-        <v>67433.33333333336</v>
+        <v>67433.3333333333</v>
       </c>
     </row>
     <row r="73">
@@ -18093,23 +18101,23 @@
       </c>
       <c r="G73" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B73)*D73/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H73" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B73)*D73/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I73" s="31">
         <f>IF(D73&gt;0,H73/D73,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J73" s="11">
         <f>SUM($H$6:H73)</f>
-        <v>62673.33333333328</v>
+        <v>62673.3333333333</v>
       </c>
       <c r="K73" s="11">
         <f>OreReserve-SUM($G$6:G73)</f>
-        <v>66266.66666666669</v>
+        <v>66266.6666666667</v>
       </c>
     </row>
     <row r="74">
@@ -18138,23 +18146,23 @@
       </c>
       <c r="G74" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B74)*D74/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H74" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B74)*D74/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I74" s="31">
         <f>IF(D74&gt;0,H74/D74,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J74" s="11">
         <f>SUM($H$6:H74)</f>
-        <v>63664.99999999994</v>
+        <v>63665</v>
       </c>
       <c r="K74" s="11">
         <f>OreReserve-SUM($G$6:G74)</f>
-        <v>65100.000000000015</v>
+        <v>65100</v>
       </c>
     </row>
     <row r="75">
@@ -18183,23 +18191,23 @@
       </c>
       <c r="G75" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B75)*D75/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H75" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B75)*D75/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I75" s="31">
         <f>IF(D75&gt;0,H75/D75,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J75" s="11">
         <f>SUM($H$6:H75)</f>
-        <v>64656.666666666606</v>
+        <v>64656.6666666667</v>
       </c>
       <c r="K75" s="11">
         <f>OreReserve-SUM($G$6:G75)</f>
-        <v>63933.33333333334</v>
+        <v>63933.3333333333</v>
       </c>
     </row>
     <row r="76">
@@ -18228,23 +18236,23 @@
       </c>
       <c r="G76" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B76)*D76/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H76" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B76)*D76/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I76" s="31">
         <f>IF(D76&gt;0,H76/D76,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J76" s="11">
         <f>SUM($H$6:H76)</f>
-        <v>65648.33333333327</v>
+        <v>65648.3333333333</v>
       </c>
       <c r="K76" s="11">
         <f>OreReserve-SUM($G$6:G76)</f>
-        <v>62766.66666666667</v>
+        <v>62766.6666666667</v>
       </c>
     </row>
     <row r="77">
@@ -18273,19 +18281,19 @@
       </c>
       <c r="G77" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B77)*D77/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H77" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B77)*D77/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I77" s="31">
         <f>IF(D77&gt;0,H77/D77,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J77" s="11">
         <f>SUM($H$6:H77)</f>
-        <v>66639.99999999994</v>
+        <v>66640</v>
       </c>
       <c r="K77" s="11">
         <f>OreReserve-SUM($G$6:G77)</f>
@@ -18318,23 +18326,23 @@
       </c>
       <c r="G78" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B78)*D78/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H78" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B78)*D78/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I78" s="31">
         <f>IF(D78&gt;0,H78/D78,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J78" s="11">
         <f>SUM($H$6:H78)</f>
-        <v>67631.66666666661</v>
+        <v>67631.6666666667</v>
       </c>
       <c r="K78" s="11">
         <f>OreReserve-SUM($G$6:G78)</f>
-        <v>60433.33333333333</v>
+        <v>60433.3333333333</v>
       </c>
     </row>
     <row r="79">
@@ -18363,23 +18371,23 @@
       </c>
       <c r="G79" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B79)*D79/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H79" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B79)*D79/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I79" s="31">
         <f>IF(D79&gt;0,H79/D79,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J79" s="11">
         <f>SUM($H$6:H79)</f>
-        <v>68623.33333333328</v>
+        <v>68623.3333333333</v>
       </c>
       <c r="K79" s="11">
         <f>OreReserve-SUM($G$6:G79)</f>
-        <v>59266.66666666666</v>
+        <v>59266.6666666667</v>
       </c>
     </row>
     <row r="80">
@@ -18408,23 +18416,23 @@
       </c>
       <c r="G80" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B80)*D80/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H80" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B80)*D80/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I80" s="31">
         <f>IF(D80&gt;0,H80/D80,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J80" s="11">
         <f>SUM($H$6:H80)</f>
-        <v>69614.99999999996</v>
+        <v>69615</v>
       </c>
       <c r="K80" s="11">
         <f>OreReserve-SUM($G$6:G80)</f>
-        <v>58099.999999999985</v>
+        <v>58100</v>
       </c>
     </row>
     <row r="81">
@@ -18453,23 +18461,23 @@
       </c>
       <c r="G81" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B81)*D81/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H81" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B81)*D81/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I81" s="31">
         <f>IF(D81&gt;0,H81/D81,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J81" s="11">
         <f>SUM($H$6:H81)</f>
-        <v>70606.66666666663</v>
+        <v>70606.6666666667</v>
       </c>
       <c r="K81" s="11">
         <f>OreReserve-SUM($G$6:G81)</f>
-        <v>56933.333333333314</v>
+        <v>56933.3333333333</v>
       </c>
     </row>
     <row r="82">
@@ -18498,15 +18506,15 @@
       </c>
       <c r="G82" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B82)*D82/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H82" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B82)*D82/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I82" s="31">
         <f>IF(D82&gt;0,H82/D82,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J82" s="11">
         <f>SUM($H$6:H82)</f>
@@ -18514,7 +18522,7 @@
       </c>
       <c r="K82" s="11">
         <f>OreReserve-SUM($G$6:G82)</f>
-        <v>55766.66666666664</v>
+        <v>55766.6666666667</v>
       </c>
     </row>
     <row r="83">
@@ -18543,23 +18551,23 @@
       </c>
       <c r="G83" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B83)*D83/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H83" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B83)*D83/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I83" s="31">
         <f>IF(D83&gt;0,H83/D83,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J83" s="11">
         <f>SUM($H$6:H83)</f>
-        <v>72589.99999999997</v>
+        <v>72590</v>
       </c>
       <c r="K83" s="11">
         <f>OreReserve-SUM($G$6:G83)</f>
-        <v>54599.99999999997</v>
+        <v>54600</v>
       </c>
     </row>
     <row r="84">
@@ -18588,19 +18596,19 @@
       </c>
       <c r="G84" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B84)*D84/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H84" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B84)*D84/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I84" s="31">
         <f>IF(D84&gt;0,H84/D84,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J84" s="11">
         <f>SUM($H$6:H84)</f>
-        <v>73581.66666666664</v>
+        <v>73581.6666666667</v>
       </c>
       <c r="K84" s="11">
         <f>OreReserve-SUM($G$6:G84)</f>
@@ -18633,23 +18641,23 @@
       </c>
       <c r="G85" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B85)*D85/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H85" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B85)*D85/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I85" s="31">
         <f>IF(D85&gt;0,H85/D85,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J85" s="11">
         <f>SUM($H$6:H85)</f>
-        <v>74573.33333333331</v>
+        <v>74573.3333333333</v>
       </c>
       <c r="K85" s="11">
         <f>OreReserve-SUM($G$6:G85)</f>
-        <v>52266.66666666663</v>
+        <v>52266.6666666667</v>
       </c>
     </row>
     <row r="86">
@@ -18678,23 +18686,23 @@
       </c>
       <c r="G86" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B86)*D86/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H86" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B86)*D86/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I86" s="31">
         <f>IF(D86&gt;0,H86/D86,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J86" s="11">
         <f>SUM($H$6:H86)</f>
-        <v>75564.99999999999</v>
+        <v>75565</v>
       </c>
       <c r="K86" s="11">
         <f>OreReserve-SUM($G$6:G86)</f>
-        <v>51099.999999999956</v>
+        <v>51100</v>
       </c>
     </row>
     <row r="87">
@@ -18723,23 +18731,23 @@
       </c>
       <c r="G87" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B87)*D87/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H87" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B87)*D87/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I87" s="31">
         <f>IF(D87&gt;0,H87/D87,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J87" s="11">
         <f>SUM($H$6:H87)</f>
-        <v>76556.66666666666</v>
+        <v>76556.6666666667</v>
       </c>
       <c r="K87" s="11">
         <f>OreReserve-SUM($G$6:G87)</f>
-        <v>49933.333333333285</v>
+        <v>49933.3333333333</v>
       </c>
     </row>
     <row r="88">
@@ -18768,23 +18776,23 @@
       </c>
       <c r="G88" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B88)*D88/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H88" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B88)*D88/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I88" s="31">
         <f>IF(D88&gt;0,H88/D88,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J88" s="11">
         <f>SUM($H$6:H88)</f>
-        <v>77548.33333333333</v>
+        <v>77548.3333333333</v>
       </c>
       <c r="K88" s="11">
         <f>OreReserve-SUM($G$6:G88)</f>
-        <v>48766.66666666661</v>
+        <v>48766.6666666667</v>
       </c>
     </row>
     <row r="89">
@@ -18813,15 +18821,15 @@
       </c>
       <c r="G89" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B89)*D89/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H89" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B89)*D89/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I89" s="31">
         <f>IF(D89&gt;0,H89/D89,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J89" s="11">
         <f>SUM($H$6:H89)</f>
@@ -18829,7 +18837,7 @@
       </c>
       <c r="K89" s="11">
         <f>OreReserve-SUM($G$6:G89)</f>
-        <v>47599.99999999994</v>
+        <v>47600</v>
       </c>
     </row>
     <row r="90">
@@ -18858,23 +18866,23 @@
       </c>
       <c r="G90" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B90)*D90/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H90" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B90)*D90/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I90" s="31">
         <f>IF(D90&gt;0,H90/D90,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J90" s="11">
         <f>SUM($H$6:H90)</f>
-        <v>79531.66666666667</v>
+        <v>79531.6666666667</v>
       </c>
       <c r="K90" s="11">
         <f>OreReserve-SUM($G$6:G90)</f>
-        <v>46433.33333333327</v>
+        <v>46433.3333333333</v>
       </c>
     </row>
     <row r="91">
@@ -18903,23 +18911,23 @@
       </c>
       <c r="G91" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B91)*D91/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H91" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B91)*D91/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I91" s="31">
         <f>IF(D91&gt;0,H91/D91,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J91" s="11">
         <f>SUM($H$6:H91)</f>
-        <v>80523.33333333334</v>
+        <v>80523.3333333333</v>
       </c>
       <c r="K91" s="11">
         <f>OreReserve-SUM($G$6:G91)</f>
-        <v>45266.6666666666</v>
+        <v>45266.6666666667</v>
       </c>
     </row>
     <row r="92">
@@ -18948,23 +18956,23 @@
       </c>
       <c r="G92" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B92)*D92/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H92" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B92)*D92/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I92" s="31">
         <f>IF(D92&gt;0,H92/D92,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J92" s="11">
         <f>SUM($H$6:H92)</f>
-        <v>81515.00000000001</v>
+        <v>81515</v>
       </c>
       <c r="K92" s="11">
         <f>OreReserve-SUM($G$6:G92)</f>
-        <v>44099.99999999993</v>
+        <v>44100</v>
       </c>
     </row>
     <row r="93">
@@ -18993,23 +19001,23 @@
       </c>
       <c r="G93" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B93)*D93/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H93" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B93)*D93/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I93" s="31">
         <f>IF(D93&gt;0,H93/D93,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J93" s="11">
         <f>SUM($H$6:H93)</f>
-        <v>82506.66666666669</v>
+        <v>82506.6666666667</v>
       </c>
       <c r="K93" s="11">
         <f>OreReserve-SUM($G$6:G93)</f>
-        <v>42933.333333333256</v>
+        <v>42933.3333333333</v>
       </c>
     </row>
     <row r="94">
@@ -19038,23 +19046,23 @@
       </c>
       <c r="G94" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B94)*D94/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H94" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B94)*D94/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I94" s="31">
         <f>IF(D94&gt;0,H94/D94,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J94" s="11">
         <f>SUM($H$6:H94)</f>
-        <v>83498.33333333336</v>
+        <v>83498.3333333333</v>
       </c>
       <c r="K94" s="11">
         <f>OreReserve-SUM($G$6:G94)</f>
-        <v>41766.666666666584</v>
+        <v>41766.6666666667</v>
       </c>
     </row>
     <row r="95">
@@ -19083,23 +19091,23 @@
       </c>
       <c r="G95" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B95)*D95/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H95" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B95)*D95/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I95" s="31">
         <f>IF(D95&gt;0,H95/D95,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J95" s="11">
         <f>SUM($H$6:H95)</f>
-        <v>84490.00000000003</v>
+        <v>84490</v>
       </c>
       <c r="K95" s="11">
         <f>OreReserve-SUM($G$6:G95)</f>
-        <v>40599.99999999991</v>
+        <v>40600</v>
       </c>
     </row>
     <row r="96">
@@ -19128,15 +19136,15 @@
       </c>
       <c r="G96" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B96)*D96/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H96" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B96)*D96/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I96" s="31">
         <f>IF(D96&gt;0,H96/D96,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J96" s="11">
         <f>SUM($H$6:H96)</f>
@@ -19144,7 +19152,7 @@
       </c>
       <c r="K96" s="11">
         <f>OreReserve-SUM($G$6:G96)</f>
-        <v>39433.33333333324</v>
+        <v>39433.3333333333</v>
       </c>
     </row>
     <row r="97">
@@ -19173,23 +19181,23 @@
       </c>
       <c r="G97" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B97)*D97/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H97" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B97)*D97/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I97" s="31">
         <f>IF(D97&gt;0,H97/D97,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J97" s="11">
         <f>SUM($H$6:H97)</f>
-        <v>86473.33333333337</v>
+        <v>86473.3333333333</v>
       </c>
       <c r="K97" s="11">
         <f>OreReserve-SUM($G$6:G97)</f>
-        <v>38266.66666666657</v>
+        <v>38266.6666666667</v>
       </c>
     </row>
     <row r="98">
@@ -19218,23 +19226,23 @@
       </c>
       <c r="G98" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B98)*D98/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H98" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B98)*D98/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I98" s="31">
         <f>IF(D98&gt;0,H98/D98,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J98" s="11">
         <f>SUM($H$6:H98)</f>
-        <v>87465.00000000004</v>
+        <v>87465</v>
       </c>
       <c r="K98" s="11">
         <f>OreReserve-SUM($G$6:G98)</f>
-        <v>37099.9999999999</v>
+        <v>37100</v>
       </c>
     </row>
     <row r="99">
@@ -19263,23 +19271,23 @@
       </c>
       <c r="G99" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B99)*D99/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H99" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B99)*D99/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I99" s="31">
         <f>IF(D99&gt;0,H99/D99,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J99" s="11">
         <f>SUM($H$6:H99)</f>
-        <v>88456.66666666672</v>
+        <v>88456.6666666667</v>
       </c>
       <c r="K99" s="11">
         <f>OreReserve-SUM($G$6:G99)</f>
-        <v>35933.33333333323</v>
+        <v>35933.3333333333</v>
       </c>
     </row>
     <row r="100">
@@ -19308,23 +19316,23 @@
       </c>
       <c r="G100" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B100)*D100/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H100" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B100)*D100/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I100" s="31">
         <f>IF(D100&gt;0,H100/D100,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J100" s="11">
         <f>SUM($H$6:H100)</f>
-        <v>89448.33333333339</v>
+        <v>89448.3333333333</v>
       </c>
       <c r="K100" s="11">
         <f>OreReserve-SUM($G$6:G100)</f>
-        <v>34766.666666666555</v>
+        <v>34766.6666666667</v>
       </c>
     </row>
     <row r="101">
@@ -19353,23 +19361,23 @@
       </c>
       <c r="G101" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B101)*D101/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H101" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B101)*D101/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I101" s="31">
         <f>IF(D101&gt;0,H101/D101,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J101" s="11">
         <f>SUM($H$6:H101)</f>
-        <v>90440.00000000006</v>
+        <v>90440</v>
       </c>
       <c r="K101" s="11">
         <f>OreReserve-SUM($G$6:G101)</f>
-        <v>33599.99999999988</v>
+        <v>33600</v>
       </c>
     </row>
     <row r="102">
@@ -19398,23 +19406,23 @@
       </c>
       <c r="G102" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B102)*D102/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H102" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B102)*D102/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I102" s="31">
         <f>IF(D102&gt;0,H102/D102,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J102" s="11">
         <f>SUM($H$6:H102)</f>
-        <v>91431.66666666673</v>
+        <v>91431.6666666667</v>
       </c>
       <c r="K102" s="11">
         <f>OreReserve-SUM($G$6:G102)</f>
-        <v>32433.333333333212</v>
+        <v>32433.3333333333</v>
       </c>
     </row>
     <row r="103">
@@ -19443,23 +19451,23 @@
       </c>
       <c r="G103" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B103)*D103/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H103" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B103)*D103/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I103" s="31">
         <f>IF(D103&gt;0,H103/D103,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J103" s="11">
         <f>SUM($H$6:H103)</f>
-        <v>92423.3333333334</v>
+        <v>92423.3333333333</v>
       </c>
       <c r="K103" s="11">
         <f>OreReserve-SUM($G$6:G103)</f>
-        <v>31266.66666666654</v>
+        <v>31266.6666666667</v>
       </c>
     </row>
     <row r="104">
@@ -19488,23 +19496,23 @@
       </c>
       <c r="G104" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B104)*D104/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H104" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B104)*D104/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I104" s="31">
         <f>IF(D104&gt;0,H104/D104,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J104" s="11">
         <f>SUM($H$6:H104)</f>
-        <v>93415.00000000007</v>
+        <v>93415</v>
       </c>
       <c r="K104" s="11">
         <f>OreReserve-SUM($G$6:G104)</f>
-        <v>30099.99999999987</v>
+        <v>30100</v>
       </c>
     </row>
     <row r="105">
@@ -19533,23 +19541,23 @@
       </c>
       <c r="G105" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B105)*D105/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H105" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B105)*D105/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I105" s="31">
         <f>IF(D105&gt;0,H105/D105,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J105" s="11">
         <f>SUM($H$6:H105)</f>
-        <v>94406.66666666674</v>
+        <v>94406.6666666667</v>
       </c>
       <c r="K105" s="11">
         <f>OreReserve-SUM($G$6:G105)</f>
-        <v>28933.333333333198</v>
+        <v>28933.3333333333</v>
       </c>
     </row>
     <row r="106">
@@ -19578,23 +19586,23 @@
       </c>
       <c r="G106" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B106)*D106/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H106" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B106)*D106/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I106" s="31">
         <f>IF(D106&gt;0,H106/D106,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J106" s="11">
         <f>SUM($H$6:H106)</f>
-        <v>95398.33333333342</v>
+        <v>95398.3333333333</v>
       </c>
       <c r="K106" s="11">
         <f>OreReserve-SUM($G$6:G106)</f>
-        <v>27766.666666666526</v>
+        <v>27766.6666666667</v>
       </c>
     </row>
     <row r="107">
@@ -19623,23 +19631,23 @@
       </c>
       <c r="G107" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B107)*D107/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H107" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B107)*D107/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I107" s="31">
         <f>IF(D107&gt;0,H107/D107,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J107" s="11">
         <f>SUM($H$6:H107)</f>
-        <v>96390.00000000009</v>
+        <v>96390</v>
       </c>
       <c r="K107" s="11">
         <f>OreReserve-SUM($G$6:G107)</f>
-        <v>26599.999999999854</v>
+        <v>26600</v>
       </c>
     </row>
     <row r="108">
@@ -19668,23 +19676,23 @@
       </c>
       <c r="G108" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B108)*D108/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H108" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B108)*D108/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I108" s="31">
         <f>IF(D108&gt;0,H108/D108,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J108" s="11">
         <f>SUM($H$6:H108)</f>
-        <v>97381.66666666676</v>
+        <v>97381.6666666667</v>
       </c>
       <c r="K108" s="11">
         <f>OreReserve-SUM($G$6:G108)</f>
-        <v>25433.333333333183</v>
+        <v>25433.3333333333</v>
       </c>
     </row>
     <row r="109">
@@ -19713,23 +19721,23 @@
       </c>
       <c r="G109" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B109)*D109/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H109" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B109)*D109/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I109" s="31">
         <f>IF(D109&gt;0,H109/D109,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J109" s="11">
         <f>SUM($H$6:H109)</f>
-        <v>98373.33333333343</v>
+        <v>98373.3333333333</v>
       </c>
       <c r="K109" s="11">
         <f>OreReserve-SUM($G$6:G109)</f>
-        <v>24266.66666666651</v>
+        <v>24266.6666666667</v>
       </c>
     </row>
     <row r="110">
@@ -19758,23 +19766,23 @@
       </c>
       <c r="G110" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B110)*D110/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H110" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B110)*D110/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I110" s="31">
         <f>IF(D110&gt;0,H110/D110,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J110" s="11">
         <f>SUM($H$6:H110)</f>
-        <v>99365.0000000001</v>
+        <v>99365</v>
       </c>
       <c r="K110" s="11">
         <f>OreReserve-SUM($G$6:G110)</f>
-        <v>23099.99999999984</v>
+        <v>23100</v>
       </c>
     </row>
     <row r="111">
@@ -19803,23 +19811,23 @@
       </c>
       <c r="G111" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B111)*D111/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H111" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B111)*D111/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I111" s="31">
         <f>IF(D111&gt;0,H111/D111,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J111" s="11">
         <f>SUM($H$6:H111)</f>
-        <v>100356.66666666677</v>
+        <v>100356.666666667</v>
       </c>
       <c r="K111" s="11">
         <f>OreReserve-SUM($G$6:G111)</f>
-        <v>21933.33333333317</v>
+        <v>21933.3333333333</v>
       </c>
     </row>
     <row r="112">
@@ -19848,23 +19856,23 @@
       </c>
       <c r="G112" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B112)*D112/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H112" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B112)*D112/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I112" s="31">
         <f>IF(D112&gt;0,H112/D112,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J112" s="11">
         <f>SUM($H$6:H112)</f>
-        <v>101348.33333333344</v>
+        <v>101348.333333333</v>
       </c>
       <c r="K112" s="11">
         <f>OreReserve-SUM($G$6:G112)</f>
-        <v>20766.666666666497</v>
+        <v>20766.6666666667</v>
       </c>
     </row>
     <row r="113">
@@ -19893,23 +19901,23 @@
       </c>
       <c r="G113" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B113)*D113/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H113" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B113)*D113/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I113" s="31">
         <f>IF(D113&gt;0,H113/D113,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J113" s="11">
         <f>SUM($H$6:H113)</f>
-        <v>102340.00000000012</v>
+        <v>102340</v>
       </c>
       <c r="K113" s="11">
         <f>OreReserve-SUM($G$6:G113)</f>
-        <v>19599.999999999825</v>
+        <v>19600</v>
       </c>
     </row>
     <row r="114">
@@ -19938,23 +19946,23 @@
       </c>
       <c r="G114" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B114)*D114/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H114" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B114)*D114/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I114" s="31">
         <f>IF(D114&gt;0,H114/D114,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J114" s="11">
         <f>SUM($H$6:H114)</f>
-        <v>103331.66666666679</v>
+        <v>103331.666666667</v>
       </c>
       <c r="K114" s="11">
         <f>OreReserve-SUM($G$6:G114)</f>
-        <v>18433.333333333154</v>
+        <v>18433.3333333333</v>
       </c>
     </row>
     <row r="115">
@@ -19983,23 +19991,23 @@
       </c>
       <c r="G115" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B115)*D115/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H115" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B115)*D115/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I115" s="31">
         <f>IF(D115&gt;0,H115/D115,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J115" s="11">
         <f>SUM($H$6:H115)</f>
-        <v>104323.33333333346</v>
+        <v>104323.333333333</v>
       </c>
       <c r="K115" s="11">
         <f>OreReserve-SUM($G$6:G115)</f>
-        <v>17266.666666666482</v>
+        <v>17266.6666666667</v>
       </c>
     </row>
     <row r="116">
@@ -20028,23 +20036,23 @@
       </c>
       <c r="G116" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B116)*D116/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H116" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B116)*D116/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I116" s="31">
         <f>IF(D116&gt;0,H116/D116,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J116" s="11">
         <f>SUM($H$6:H116)</f>
-        <v>105315.00000000013</v>
+        <v>105315</v>
       </c>
       <c r="K116" s="11">
         <f>OreReserve-SUM($G$6:G116)</f>
-        <v>16099.99999999981</v>
+        <v>16100</v>
       </c>
     </row>
     <row r="117">
@@ -20073,23 +20081,23 @@
       </c>
       <c r="G117" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B117)*D117/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H117" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B117)*D117/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I117" s="31">
         <f>IF(D117&gt;0,H117/D117,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J117" s="11">
         <f>SUM($H$6:H117)</f>
-        <v>106306.6666666668</v>
+        <v>106306.666666667</v>
       </c>
       <c r="K117" s="11">
         <f>OreReserve-SUM($G$6:G117)</f>
-        <v>14933.33333333314</v>
+        <v>14933.3333333333</v>
       </c>
     </row>
     <row r="118">
@@ -20118,23 +20126,23 @@
       </c>
       <c r="G118" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B118)*D118/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H118" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B118)*D118/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I118" s="31">
         <f>IF(D118&gt;0,H118/D118,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J118" s="11">
         <f>SUM($H$6:H118)</f>
-        <v>107298.33333333347</v>
+        <v>107298.333333333</v>
       </c>
       <c r="K118" s="11">
         <f>OreReserve-SUM($G$6:G118)</f>
-        <v>13766.666666666468</v>
+        <v>13766.6666666667</v>
       </c>
     </row>
     <row r="119">
@@ -20163,23 +20171,23 @@
       </c>
       <c r="G119" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B119)*D119/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H119" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B119)*D119/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I119" s="31">
         <f>IF(D119&gt;0,H119/D119,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J119" s="11">
         <f>SUM($H$6:H119)</f>
-        <v>108290.00000000015</v>
+        <v>108290</v>
       </c>
       <c r="K119" s="11">
         <f>OreReserve-SUM($G$6:G119)</f>
-        <v>12599.999999999796</v>
+        <v>12600</v>
       </c>
     </row>
     <row r="120">
@@ -20208,23 +20216,23 @@
       </c>
       <c r="G120" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B120)*D120/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H120" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B120)*D120/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I120" s="31">
         <f>IF(D120&gt;0,H120/D120,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J120" s="11">
         <f>SUM($H$6:H120)</f>
-        <v>109281.66666666682</v>
+        <v>109281.666666667</v>
       </c>
       <c r="K120" s="11">
         <f>OreReserve-SUM($G$6:G120)</f>
-        <v>11433.333333333125</v>
+        <v>11433.3333333333</v>
       </c>
     </row>
     <row r="121">
@@ -20253,23 +20261,23 @@
       </c>
       <c r="G121" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B121)*D121/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H121" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B121)*D121/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I121" s="31">
         <f>IF(D121&gt;0,H121/D121,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J121" s="11">
         <f>SUM($H$6:H121)</f>
-        <v>110273.33333333349</v>
+        <v>110273.333333333</v>
       </c>
       <c r="K121" s="11">
         <f>OreReserve-SUM($G$6:G121)</f>
-        <v>10266.666666666453</v>
+        <v>10266.6666666667</v>
       </c>
     </row>
     <row r="122">
@@ -20298,23 +20306,23 @@
       </c>
       <c r="G122" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B122)*D122/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H122" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B122)*D122/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I122" s="31">
         <f>IF(D122&gt;0,H122/D122,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J122" s="11">
         <f>SUM($H$6:H122)</f>
-        <v>111265.00000000016</v>
+        <v>111265</v>
       </c>
       <c r="K122" s="11">
         <f>OreReserve-SUM($G$6:G122)</f>
-        <v>9099.999999999782</v>
+        <v>9099.99999999999</v>
       </c>
     </row>
     <row r="123">
@@ -20343,23 +20351,23 @@
       </c>
       <c r="G123" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B123)*D123/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H123" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B123)*D123/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I123" s="31">
         <f>IF(D123&gt;0,H123/D123,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J123" s="11">
         <f>SUM($H$6:H123)</f>
-        <v>112256.66666666683</v>
+        <v>112256.666666667</v>
       </c>
       <c r="K123" s="11">
         <f>OreReserve-SUM($G$6:G123)</f>
-        <v>7933.33333333311</v>
+        <v>7933.33333333334</v>
       </c>
     </row>
     <row r="124">
@@ -20388,23 +20396,23 @@
       </c>
       <c r="G124" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B124)*D124/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H124" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B124)*D124/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I124" s="31">
         <f>IF(D124&gt;0,H124/D124,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J124" s="11">
         <f>SUM($H$6:H124)</f>
-        <v>113248.3333333335</v>
+        <v>113248.333333333</v>
       </c>
       <c r="K124" s="11">
         <f>OreReserve-SUM($G$6:G124)</f>
-        <v>6766.666666666453</v>
+        <v>6766.66666666666</v>
       </c>
     </row>
     <row r="125">
@@ -20433,23 +20441,23 @@
       </c>
       <c r="G125" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$17:$M$17,B125)*D125/$N$18,0)</f>
-        <v>1166.6666666666665</v>
+        <v>1166.66666666667</v>
       </c>
       <c r="H125" s="13">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$18:$M$18,B125)*D125/$N$18,0)</f>
-        <v>991.6666666666666</v>
+        <v>991.666666666667</v>
       </c>
       <c r="I125" s="31">
         <f>IF(D125&gt;0,H125/D125,0)</f>
-        <v>39.666666666666664</v>
+        <v>39.6666666666667</v>
       </c>
       <c r="J125" s="11">
         <f>SUM($H$6:H125)</f>
-        <v>114240.00000000017</v>
+        <v>114240</v>
       </c>
       <c r="K125" s="11">
         <f>OreReserve-SUM($G$6:G125)</f>
-        <v>5599.999999999796</v>
+        <v>5600</v>
       </c>
     </row>
     <row r="126">
@@ -21592,7 +21600,7 @@
     <tabColor rgb="FFC55A11"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="52.7109375" style="1" customWidth="1"/>
@@ -21681,7 +21689,7 @@
       </c>
       <c r="B9" s="30">
         <f>B8/B7</f>
-        <v>38.660292014072347</v>
+        <v>38.6602920140724</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>156</v>
@@ -21710,7 +21718,7 @@
       </c>
       <c r="B11" s="11">
         <f>B6/B10</f>
-        <v>12190.965517241379</v>
+        <v>12190.9655172414</v>
       </c>
       <c r="C11" s="7" t="s">
         <v>301</v>
@@ -21840,7 +21848,7 @@
       </c>
       <c r="B21" s="18">
         <f>B20/(BenchGrade*100)</f>
-        <v>6.4516129032258061</v>
+        <v>6.45161290322581</v>
       </c>
       <c r="C21" s="7" t="s">
         <v>320</v>
@@ -21870,7 +21878,7 @@
       </c>
       <c r="B23" s="18">
         <f>B21*B22*100</f>
-        <v>206.45161290322579</v>
+        <v>206.451612903226</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>149</v>
@@ -21883,7 +21891,7 @@
       </c>
       <c r="B24" s="18">
         <f>B23*FxRate</f>
-        <v>79.380645161290317</v>
+        <v>79.3806451612903</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>156</v>
@@ -21896,7 +21904,7 @@
       </c>
       <c r="B25" s="18">
         <f>SeaFreight*FxRate</f>
-        <v>9.2279999999999998</v>
+        <v>9.228</v>
       </c>
       <c r="C25" s="7" t="s">
         <v>156</v>
@@ -21922,7 +21930,7 @@
       </c>
       <c r="B27" s="18">
         <f>B24*TraderM</f>
-        <v>7.9380645161290317</v>
+        <v>7.93806451612903</v>
       </c>
       <c r="C27" s="7" t="s">
         <v>156</v>
@@ -21935,7 +21943,7 @@
       </c>
       <c r="B28" s="33">
         <f>B24-B25-B26-B27</f>
-        <v>59.714580645161291</v>
+        <v>59.7145806451613</v>
       </c>
       <c r="C28" s="7" t="s">
         <v>156</v>
@@ -21961,7 +21969,7 @@
       </c>
       <c r="B30" s="33">
         <f>B28-B29</f>
-        <v>53.714580645161291</v>
+        <v>53.7145806451613</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>156</v>
@@ -21974,7 +21982,7 @@
       </c>
       <c r="B31" s="18">
         <f>B30*PriceDisc</f>
-        <v>6.4457496774193546</v>
+        <v>6.44574967741936</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>156</v>
@@ -21982,18 +21990,22 @@
       <c r="D31" s="16"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="32" t="s">
-        <v>331</v>
-      </c>
-      <c r="B32" s="30">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>صافي سعر التصدير عند موقع التجميع</t>
+        </is>
+      </c>
+      <c r="B32" s="33">
         <f>B30-B31</f>
-        <v>47.268830967741934</v>
+        <v>47.2688309677419</v>
       </c>
       <c r="C32" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="D32" s="16" t="s">
-        <v>332</v>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>يُستخدم لحصة التصدير فقط — انظر «خامساً» أدناه</t>
+        </is>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.2">
@@ -22010,13 +22022,14 @@
       </c>
       <c r="B34" s="34">
         <f>SalePrice/NatAvgPrice</f>
-        <v>1.2226713380886021</v>
+        <v>0.999992446666667</v>
       </c>
       <c r="C34" s="7" t="s">
         <v>335</v>
       </c>
-      <c r="D34" s="16" t="s">
-        <v>336</v>
+      <c r="D34" s="16" t="str">
+        <f>IF(ABS(B34-1)&lt;0.005,"السعر المعتمد يساوي المتوسط الوطني المحقق 2025.",IF(B34&gt;1,"السعر المعتمد أعلى من المتوسط الوطني المحقق 2025 — يُبرَّر بعقد أو عرض شراء.","السعر المعتمد أقل من المتوسط الوطني المحقق 2025 (تحفّظ)."))</f>
+        <v>السعر المعتمد يساوي المتوسط الوطني المحقق 2025.</v>
       </c>
     </row>
     <row r="35" spans="1:4" ht="25.5" x14ac:dyDescent="0.2">
@@ -22035,7 +22048,128 @@
         <v>تنبيه: الدرجة أقل من 36% — لا يُسمح بتصدير الخام غير المعالج. يُباع محلياً (مصانع المعالجة/الفيروكروم) أو يُعالَج ويُصدَّر عبر شركة متاجرة المعادن بموافقة الوزارة، وقد ينخفض السعر المحقق عن المحتسب أعلاه.</v>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="15" t="inlineStr">
+        <is>
+          <t>خامساً: مسار البيع — بيع محلي و/أو تصدير</t>
+        </is>
+      </c>
+      <c r="B37" s="15"/>
+      <c r="C37" s="15"/>
+      <c r="D37" s="15"/>
+    </row>
+    <row r="38" ht="25.5" customHeight="1">
+      <c r="A38" s="9" t="inlineStr">
+        <is>
+          <t>سعر البيع المحلي عند موقع التجميع</t>
+        </is>
+      </c>
+      <c r="B38" s="28">
+        <v>38.66</v>
+      </c>
+      <c r="C38" s="7" t="inlineStr">
+        <is>
+          <t>ر.ع / طن</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
+        <is>
+          <t>افتراض يحتاج تأكيداً = متوسط السعر الوطني المحقق 2025 (B9). يُستبدل بعرض مشترٍ محلي (مصانع المعالجة / الفيروكروم) تسليم موقع التجميع</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="25.5" customHeight="1">
+      <c r="A39" s="9" t="inlineStr">
+        <is>
+          <t>نسبة المبيعات المحلية من الكمية المباعة</t>
+        </is>
+      </c>
+      <c r="B39" s="26">
+        <v>1</v>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="inlineStr">
+        <is>
+          <t>100% = بيع محلي بالكامل (الحالة الأساسية لأن درجة الخام أقل من 36%). الباقي يُصدَّر عبر شركة متاجرة المعادن بصافي سعر التصدير</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="9" t="inlineStr">
+        <is>
+          <t>صافي سعر التصدير عند موقع التجميع</t>
+        </is>
+      </c>
+      <c r="B40" s="18">
+        <f>B32</f>
+        <v>47.2688309677419</v>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>ر.ع / طن</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="inlineStr">
+        <is>
+          <t>من «ثالثاً» أعلاه</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>سعر البيع المعتمد في الدراسة (متوسط مرجّح)</t>
+        </is>
+      </c>
+      <c r="B41" s="30">
+        <f>B38*B39+B40*(1-B39)</f>
+        <v>38.66</v>
+      </c>
+      <c r="C41" s="7" t="inlineStr">
+        <is>
+          <t>ر.ع / طن</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
+        <is>
+          <t>يُستخدم في الإيرادات وجميع المؤشرات والحساسية</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="25.5" customHeight="1">
+      <c r="A42" s="9" t="inlineStr">
+        <is>
+          <t>التحقق من شرط درجة التصدير</t>
+        </is>
+      </c>
+      <c r="B42" s="35" t="str">
+        <f>IF(OR(B39&gt;=1,OreGrade&gt;=MinExportGrade),"مطابق","مخالف")</f>
+        <v>مطابق</v>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D42" s="9" t="str">
+        <f>IF(B39&gt;=1,"البيع محلي بالكامل — لا ينطبق شرط درجة التصدير.",IF(OreGrade&gt;=MinExportGrade,"الدرجة تسمح بتصدير الخام غير المعالج عبر شركة متاجرة المعادن.","تنبيه: جزء من المبيعات مفترض للتصدير والدرجة أقل من 36% — يلزم معالجة الخام وموافقة الوزارة، أو رفع نسبة البيع المحلي إلى 100%."))</f>
+        <v>البيع محلي بالكامل — لا ينطبق شرط درجة التصدير.</v>
+      </c>
+    </row>
   </sheetData>
+  <dataValidations count="2">
+    <dataValidation type="decimal" allowBlank="1" showErrorMessage="1" errorTitle="قيمة غير صحيحة" error="أدخل نسبة بين 0% و100%" sqref="B39">
+      <formula1>0</formula1>
+      <formula2>1</formula2>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showErrorMessage="1" errorTitle="قيمة غير صحيحة" error="السعر يجب أن يكون أكبر من صفر" sqref="B38">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.3888888888888889" right="0.3888888888888889" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="83" fitToHeight="0" orientation="landscape" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
@@ -22183,7 +22317,7 @@
       </c>
       <c r="C11" s="11">
         <f>NatAvgOutput</f>
-        <v>12190.965517241379</v>
+        <v>12190.9655172414</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>353</v>
@@ -24286,7 +24420,7 @@
       </c>
       <c r="B13" s="11">
         <f>PreOp/AmortYrs</f>
-        <v>22939.200000000001</v>
+        <v>22939.2</v>
       </c>
       <c r="C13" s="7" t="s">
         <v>216</v>

--- a/chromite-quarry-feasibility/Chromite-Quarry-Feasibility-Monthly-Production.xlsx
+++ b/chromite-quarry-feasibility/Chromite-Quarry-Feasibility-Monthly-Production.xlsx
@@ -7890,7 +7890,7 @@
     <row r="35">
       <c r="A35" s="2" t="str">
         <f>"5) الحفارات: "&amp;'الخطة الفنية والإنتاج'!C14&amp;" — الاحتياطي: "&amp;'الخطة الفنية والإنتاج'!B28</f>
-        <v>5) الحفارات: غير كافية — المطلوب 155% من طاقتها؛ يلزم ألا تزيد نسبة التعرية عن 4.8 أو إنتاجية أعلى أو حفارات إضافية — الاحتياطي: تنبيه: الاحتياطي المفترض (140,000 طن) لا يكفي — المطلوب 352,941 طن خام لخمس سنوات</v>
+        <v>5) الحفارات: كافية — المطلوب 86% من طاقة الحفارات — الاحتياطي: الاحتياطي المفترض كافٍ لخمس سنوات تشغيل</v>
       </c>
     </row>
   </sheetData>
@@ -9881,10 +9881,9 @@
           <t>الاحتياطي ودرجة الخام</t>
         </is>
       </c>
-      <c r="C27" s="43" t="inlineStr">
-        <is>
-          <t>140,000 طن بدرجة 32%</t>
-        </is>
+      <c r="C27" s="43" t="str">
+        <f>TEXT(OreReserve,"#,##0")&amp;" طن بدرجة "&amp;TEXT(OreGrade,"0%")</f>
+        <v>400,000 طن بدرجة 32%</v>
       </c>
       <c r="D27" s="43" t="inlineStr">
         <is>
@@ -9905,10 +9904,9 @@
           <t>نسبة التعرية وإنتاجية التكسير</t>
         </is>
       </c>
-      <c r="C28" s="43" t="inlineStr">
-        <is>
-          <t>8 طن/طن و35 طن/ساعة</t>
-        </is>
+      <c r="C28" s="43" t="str">
+        <f>TEXT(StripRatio,"0.0")&amp;" طن/طن و"&amp;TEXT(BrkProd,"0")&amp;" طن/ساعة"</f>
+        <v>4.0 طن/طن و35 طن/ساعة</v>
       </c>
       <c r="D28" s="43" t="inlineStr">
         <is>
@@ -10512,7 +10510,7 @@
         </is>
       </c>
       <c r="B12" s="10" t="n">
-        <v>140000</v>
+        <v>400000</v>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
@@ -10521,7 +10519,7 @@
       </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
-          <t>افتراض يحتاج تأكيداً — غير وارد في الملف الأصلي. يُستبدل برقم التقرير الاستكشافي المعتمد</t>
+          <t>معطى من المالك (أكتوبر 2026) — يُوثَّق بالتقرير الاستكشافي المعتمد</t>
         </is>
       </c>
     </row>
@@ -10552,7 +10550,7 @@
         </is>
       </c>
       <c r="B14" s="27" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
@@ -10561,7 +10559,7 @@
       </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
-          <t>افتراض يحتاج تأكيداً — يحدد حجم الصخور المطلوب تحريكها وكفاية الحفارات</t>
+          <t>معطى من المالك (أكتوبر 2026) — يحدد حجم الصخور المطلوب تحريكها وكفاية الحفارات</t>
         </is>
       </c>
     </row>
@@ -12859,7 +12857,7 @@
       </c>
       <c r="C10" s="11">
         <f>ROMCap*(1+StripRatio)</f>
-        <v>635294.117647059</v>
+        <v>352941.176470588</v>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
@@ -12880,7 +12878,7 @@
       </c>
       <c r="C11" s="11">
         <f>RockCap-ROMCap</f>
-        <v>564705.882352941</v>
+        <v>282352.941176471</v>
       </c>
     </row>
     <row r="12">
@@ -12917,7 +12915,7 @@
       </c>
       <c r="C13" s="17">
         <f>IF(C12&gt;0,C10/C12,0)</f>
-        <v>1.5513897866839</v>
+        <v>0.861883214824391</v>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
@@ -12934,7 +12932,7 @@
       <c r="B14" s="22" t="n"/>
       <c r="C14" s="22" t="str">
         <f>IF(C13&lt;=1,"كافية — المطلوب "&amp;TEXT(C13,"0%")&amp;" من طاقة الحفارات","غير كافية — المطلوب "&amp;TEXT(C13,"0%")&amp;" من طاقتها؛ يلزم ألا تزيد نسبة التعرية عن "&amp;TEXT(C15,"0.0")&amp;" أو إنتاجية أعلى أو حفارات إضافية")</f>
-        <v>غير كافية — المطلوب 155% من طاقتها؛ يلزم ألا تزيد نسبة التعرية عن 4.8 أو إنتاجية أعلى أو حفارات إضافية</v>
+        <v>كافية — المطلوب 86% من طاقة الحفارات</v>
       </c>
       <c r="D14" s="22" t="n"/>
       <c r="E14" s="22" t="n"/>
@@ -12997,7 +12995,7 @@
       </c>
       <c r="C17" s="31">
         <f>IF(ROMCap&gt;0,OreReserve/ROMCap,0)</f>
-        <v>1.98333333333333</v>
+        <v>5.66666666666667</v>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
@@ -13107,27 +13105,27 @@
       </c>
       <c r="D22" s="11">
         <f>RockCap*D20</f>
-        <v>635294.117647059</v>
+        <v>352941.176470588</v>
       </c>
       <c r="E22" s="11">
         <f>RockCap*E20</f>
-        <v>635294.117647059</v>
+        <v>352941.176470588</v>
       </c>
       <c r="F22" s="11">
         <f>RockCap*F20</f>
-        <v>635294.117647059</v>
+        <v>352941.176470588</v>
       </c>
       <c r="G22" s="11">
         <f>RockCap*G20</f>
-        <v>635294.117647059</v>
+        <v>352941.176470588</v>
       </c>
       <c r="H22" s="11">
         <f>RockCap*H20</f>
-        <v>635294.117647059</v>
+        <v>352941.176470588</v>
       </c>
       <c r="I22" s="12">
         <f>SUM(D22:H22)</f>
-        <v>3176470.58823529</v>
+        <v>1764705.88235294</v>
       </c>
     </row>
     <row r="23">
@@ -13283,27 +13281,27 @@
       </c>
       <c r="C27" s="11">
         <f>OreReserve</f>
-        <v>140000</v>
+        <v>400000</v>
       </c>
       <c r="D27" s="11">
         <f>OreReserve-D26</f>
-        <v>69411.7647058824</v>
+        <v>329411.764705882</v>
       </c>
       <c r="E27" s="11">
         <f>OreReserve-E26</f>
-        <v>-1176.4705882353</v>
+        <v>258823.529411765</v>
       </c>
       <c r="F27" s="11">
         <f>OreReserve-F26</f>
-        <v>-71764.705882353</v>
+        <v>188235.294117647</v>
       </c>
       <c r="G27" s="11">
         <f>OreReserve-G26</f>
-        <v>-142352.941176471</v>
+        <v>117647.058823529</v>
       </c>
       <c r="H27" s="11">
         <f>OreReserve-H26</f>
-        <v>-212941.176470588</v>
+        <v>47058.8235294118</v>
       </c>
     </row>
     <row r="28">
@@ -13314,7 +13312,7 @@
       </c>
       <c r="B28" s="21" t="str">
         <f>IF($H$27&gt;=0,"الاحتياطي المفترض كافٍ لخمس سنوات تشغيل","تنبيه: الاحتياطي المفترض ("&amp;TEXT(OreReserve,"#,##0")&amp;" طن) لا يكفي — المطلوب "&amp;TEXT($H$26,"#,##0")&amp;" طن خام لخمس سنوات")</f>
-        <v>تنبيه: الاحتياطي المفترض (140,000 طن) لا يكفي — المطلوب 352,941 طن خام لخمس سنوات</v>
+        <v>الاحتياطي المفترض كافٍ لخمس سنوات تشغيل</v>
       </c>
       <c r="C28" s="22" t="n"/>
       <c r="D28" s="22" t="n"/>
@@ -13542,7 +13540,7 @@
       </c>
       <c r="F6" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B6)*D6/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G6" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B6)*D6/$N$18,0)</f>
@@ -13562,7 +13560,7 @@
       </c>
       <c r="K6" s="11">
         <f>OreReserve-SUM($G$6:G6)</f>
-        <v>134117.647058824</v>
+        <v>394117.647058824</v>
       </c>
       <c r="M6" s="43" t="inlineStr">
         <is>
@@ -13595,7 +13593,7 @@
       </c>
       <c r="F7" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B7)*D7/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G7" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B7)*D7/$N$18,0)</f>
@@ -13615,7 +13613,7 @@
       </c>
       <c r="K7" s="11">
         <f>OreReserve-SUM($G$6:G7)</f>
-        <v>128235.294117647</v>
+        <v>388235.294117647</v>
       </c>
       <c r="M7" s="43" t="inlineStr">
         <is>
@@ -13648,7 +13646,7 @@
       </c>
       <c r="F8" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B8)*D8/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G8" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B8)*D8/$N$18,0)</f>
@@ -13668,7 +13666,7 @@
       </c>
       <c r="K8" s="11">
         <f>OreReserve-SUM($G$6:G8)</f>
-        <v>122352.941176471</v>
+        <v>382352.941176471</v>
       </c>
       <c r="M8" s="43" t="inlineStr">
         <is>
@@ -13701,7 +13699,7 @@
       </c>
       <c r="F9" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B9)*D9/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G9" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B9)*D9/$N$18,0)</f>
@@ -13721,7 +13719,7 @@
       </c>
       <c r="K9" s="11">
         <f>OreReserve-SUM($G$6:G9)</f>
-        <v>116470.588235294</v>
+        <v>376470.588235294</v>
       </c>
       <c r="M9" s="43" t="inlineStr">
         <is>
@@ -13754,7 +13752,7 @@
       </c>
       <c r="F10" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B10)*D10/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G10" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B10)*D10/$N$18,0)</f>
@@ -13774,7 +13772,7 @@
       </c>
       <c r="K10" s="11">
         <f>OreReserve-SUM($G$6:G10)</f>
-        <v>110588.235294118</v>
+        <v>370588.235294118</v>
       </c>
       <c r="M10" s="43" t="inlineStr">
         <is>
@@ -13807,7 +13805,7 @@
       </c>
       <c r="F11" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B11)*D11/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G11" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B11)*D11/$N$18,0)</f>
@@ -13827,7 +13825,7 @@
       </c>
       <c r="K11" s="11">
         <f>OreReserve-SUM($G$6:G11)</f>
-        <v>104705.882352941</v>
+        <v>364705.882352941</v>
       </c>
       <c r="M11" s="43" t="inlineStr">
         <is>
@@ -13860,7 +13858,7 @@
       </c>
       <c r="F12" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B12)*D12/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G12" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B12)*D12/$N$18,0)</f>
@@ -13880,7 +13878,7 @@
       </c>
       <c r="K12" s="11">
         <f>OreReserve-SUM($G$6:G12)</f>
-        <v>98823.5294117647</v>
+        <v>358823.529411765</v>
       </c>
       <c r="M12" s="43" t="inlineStr">
         <is>
@@ -13913,7 +13911,7 @@
       </c>
       <c r="F13" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B13)*D13/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G13" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B13)*D13/$N$18,0)</f>
@@ -13933,7 +13931,7 @@
       </c>
       <c r="K13" s="11">
         <f>OreReserve-SUM($G$6:G13)</f>
-        <v>92941.1764705882</v>
+        <v>352941.176470588</v>
       </c>
       <c r="M13" s="43" t="inlineStr">
         <is>
@@ -13966,7 +13964,7 @@
       </c>
       <c r="F14" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B14)*D14/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G14" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B14)*D14/$N$18,0)</f>
@@ -13986,7 +13984,7 @@
       </c>
       <c r="K14" s="11">
         <f>OreReserve-SUM($G$6:G14)</f>
-        <v>87058.8235294118</v>
+        <v>347058.823529412</v>
       </c>
       <c r="M14" s="43" t="inlineStr">
         <is>
@@ -14019,7 +14017,7 @@
       </c>
       <c r="F15" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B15)*D15/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G15" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B15)*D15/$N$18,0)</f>
@@ -14039,7 +14037,7 @@
       </c>
       <c r="K15" s="11">
         <f>OreReserve-SUM($G$6:G15)</f>
-        <v>81176.4705882353</v>
+        <v>341176.470588235</v>
       </c>
       <c r="M15" s="43" t="inlineStr">
         <is>
@@ -14072,7 +14070,7 @@
       </c>
       <c r="F16" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B16)*D16/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G16" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B16)*D16/$N$18,0)</f>
@@ -14092,7 +14090,7 @@
       </c>
       <c r="K16" s="11">
         <f>OreReserve-SUM($G$6:G16)</f>
-        <v>75294.1176470588</v>
+        <v>335294.117647059</v>
       </c>
       <c r="M16" s="43" t="inlineStr">
         <is>
@@ -14125,7 +14123,7 @@
       </c>
       <c r="F17" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B17)*D17/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G17" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B17)*D17/$N$18,0)</f>
@@ -14145,7 +14143,7 @@
       </c>
       <c r="K17" s="11">
         <f>OreReserve-SUM($G$6:G17)</f>
-        <v>69411.7647058824</v>
+        <v>329411.764705882</v>
       </c>
       <c r="M17" s="43" t="inlineStr">
         <is>
@@ -14178,7 +14176,7 @@
       </c>
       <c r="F18" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B18)*D18/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G18" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B18)*D18/$N$18,0)</f>
@@ -14198,7 +14196,7 @@
       </c>
       <c r="K18" s="11">
         <f>OreReserve-SUM($G$6:G18)</f>
-        <v>63529.4117647059</v>
+        <v>323529.411764706</v>
       </c>
       <c r="M18" s="32" t="inlineStr">
         <is>
@@ -14232,7 +14230,7 @@
       </c>
       <c r="F19" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B19)*D19/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G19" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B19)*D19/$N$18,0)</f>
@@ -14252,7 +14250,7 @@
       </c>
       <c r="K19" s="11">
         <f>OreReserve-SUM($G$6:G19)</f>
-        <v>57647.0588235294</v>
+        <v>317647.058823529</v>
       </c>
       <c r="M19" s="43" t="inlineStr">
         <is>
@@ -14286,7 +14284,7 @@
       </c>
       <c r="F20" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B20)*D20/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G20" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B20)*D20/$N$18,0)</f>
@@ -14306,7 +14304,7 @@
       </c>
       <c r="K20" s="11">
         <f>OreReserve-SUM($G$6:G20)</f>
-        <v>51764.7058823529</v>
+        <v>311764.705882353</v>
       </c>
       <c r="M20" s="43" t="inlineStr">
         <is>
@@ -14340,7 +14338,7 @@
       </c>
       <c r="F21" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B21)*D21/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G21" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B21)*D21/$N$18,0)</f>
@@ -14360,7 +14358,7 @@
       </c>
       <c r="K21" s="11">
         <f>OreReserve-SUM($G$6:G21)</f>
-        <v>45882.3529411765</v>
+        <v>305882.352941177</v>
       </c>
       <c r="M21" s="43" t="inlineStr">
         <is>
@@ -14394,7 +14392,7 @@
       </c>
       <c r="F22" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B22)*D22/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G22" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B22)*D22/$N$18,0)</f>
@@ -14414,7 +14412,7 @@
       </c>
       <c r="K22" s="11">
         <f>OreReserve-SUM($G$6:G22)</f>
-        <v>40000</v>
+        <v>300000</v>
       </c>
       <c r="M22" s="5" t="inlineStr">
         <is>
@@ -14444,7 +14442,7 @@
       </c>
       <c r="F23" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B23)*D23/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G23" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B23)*D23/$N$18,0)</f>
@@ -14464,7 +14462,7 @@
       </c>
       <c r="K23" s="11">
         <f>OreReserve-SUM($G$6:G23)</f>
-        <v>34117.6470588235</v>
+        <v>294117.647058824</v>
       </c>
     </row>
     <row r="24">
@@ -14489,7 +14487,7 @@
       </c>
       <c r="F24" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B24)*D24/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G24" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B24)*D24/$N$18,0)</f>
@@ -14509,7 +14507,7 @@
       </c>
       <c r="K24" s="11">
         <f>OreReserve-SUM($G$6:G24)</f>
-        <v>28235.2941176471</v>
+        <v>288235.294117647</v>
       </c>
       <c r="M24" s="15" t="inlineStr">
         <is>
@@ -14542,7 +14540,7 @@
       </c>
       <c r="F25" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B25)*D25/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G25" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B25)*D25/$N$18,0)</f>
@@ -14562,7 +14560,7 @@
       </c>
       <c r="K25" s="11">
         <f>OreReserve-SUM($G$6:G25)</f>
-        <v>22352.9411764706</v>
+        <v>282352.941176471</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -14607,7 +14605,7 @@
       </c>
       <c r="F26" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B26)*D26/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G26" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B26)*D26/$N$18,0)</f>
@@ -14627,7 +14625,7 @@
       </c>
       <c r="K26" s="11">
         <f>OreReserve-SUM($G$6:G26)</f>
-        <v>16470.5882352941</v>
+        <v>276470.588235294</v>
       </c>
       <c r="M26" s="7" t="n">
         <v>1</v>
@@ -14667,7 +14665,7 @@
       </c>
       <c r="F27" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B27)*D27/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G27" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B27)*D27/$N$18,0)</f>
@@ -14687,7 +14685,7 @@
       </c>
       <c r="K27" s="11">
         <f>OreReserve-SUM($G$6:G27)</f>
-        <v>10588.2352941177</v>
+        <v>270588.235294118</v>
       </c>
       <c r="M27" s="7" t="n">
         <v>2</v>
@@ -14727,7 +14725,7 @@
       </c>
       <c r="F28" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B28)*D28/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G28" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B28)*D28/$N$18,0)</f>
@@ -14747,7 +14745,7 @@
       </c>
       <c r="K28" s="11">
         <f>OreReserve-SUM($G$6:G28)</f>
-        <v>4705.88235294118</v>
+        <v>264705.882352941</v>
       </c>
       <c r="M28" s="7" t="n">
         <v>3</v>
@@ -14787,7 +14785,7 @@
       </c>
       <c r="F29" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B29)*D29/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G29" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B29)*D29/$N$18,0)</f>
@@ -14807,7 +14805,7 @@
       </c>
       <c r="K29" s="11">
         <f>OreReserve-SUM($G$6:G29)</f>
-        <v>-1176.4705882353</v>
+        <v>258823.529411765</v>
       </c>
       <c r="M29" s="7" t="n">
         <v>4</v>
@@ -14847,7 +14845,7 @@
       </c>
       <c r="F30" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B30)*D30/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G30" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B30)*D30/$N$18,0)</f>
@@ -14867,7 +14865,7 @@
       </c>
       <c r="K30" s="11">
         <f>OreReserve-SUM($G$6:G30)</f>
-        <v>-7058.82352941178</v>
+        <v>252941.176470588</v>
       </c>
       <c r="M30" s="7" t="n">
         <v>5</v>
@@ -14907,7 +14905,7 @@
       </c>
       <c r="F31" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B31)*D31/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G31" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B31)*D31/$N$18,0)</f>
@@ -14927,7 +14925,7 @@
       </c>
       <c r="K31" s="11">
         <f>OreReserve-SUM($G$6:G31)</f>
-        <v>-12941.1764705882</v>
+        <v>247058.823529412</v>
       </c>
       <c r="M31" s="32" t="inlineStr">
         <is>
@@ -14969,7 +14967,7 @@
       </c>
       <c r="F32" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B32)*D32/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G32" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B32)*D32/$N$18,0)</f>
@@ -14989,7 +14987,7 @@
       </c>
       <c r="K32" s="11">
         <f>OreReserve-SUM($G$6:G32)</f>
-        <v>-18823.5294117647</v>
+        <v>241176.470588235</v>
       </c>
       <c r="M32" s="32" t="inlineStr">
         <is>
@@ -15023,7 +15021,7 @@
       </c>
       <c r="F33" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B33)*D33/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G33" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B33)*D33/$N$18,0)</f>
@@ -15043,7 +15041,7 @@
       </c>
       <c r="K33" s="11">
         <f>OreReserve-SUM($G$6:G33)</f>
-        <v>-24705.8823529412</v>
+        <v>235294.117647059</v>
       </c>
     </row>
     <row r="34">
@@ -15068,7 +15066,7 @@
       </c>
       <c r="F34" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B34)*D34/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G34" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B34)*D34/$N$18,0)</f>
@@ -15088,7 +15086,7 @@
       </c>
       <c r="K34" s="11">
         <f>OreReserve-SUM($G$6:G34)</f>
-        <v>-30588.2352941177</v>
+        <v>229411.764705882</v>
       </c>
     </row>
     <row r="35">
@@ -15113,7 +15111,7 @@
       </c>
       <c r="F35" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B35)*D35/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G35" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B35)*D35/$N$18,0)</f>
@@ -15133,7 +15131,7 @@
       </c>
       <c r="K35" s="11">
         <f>OreReserve-SUM($G$6:G35)</f>
-        <v>-36470.5882352941</v>
+        <v>223529.411764706</v>
       </c>
     </row>
     <row r="36">
@@ -15158,7 +15156,7 @@
       </c>
       <c r="F36" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B36)*D36/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G36" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B36)*D36/$N$18,0)</f>
@@ -15178,7 +15176,7 @@
       </c>
       <c r="K36" s="11">
         <f>OreReserve-SUM($G$6:G36)</f>
-        <v>-42352.9411764706</v>
+        <v>217647.058823529</v>
       </c>
     </row>
     <row r="37">
@@ -15203,7 +15201,7 @@
       </c>
       <c r="F37" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B37)*D37/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G37" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B37)*D37/$N$18,0)</f>
@@ -15223,7 +15221,7 @@
       </c>
       <c r="K37" s="11">
         <f>OreReserve-SUM($G$6:G37)</f>
-        <v>-48235.2941176471</v>
+        <v>211764.705882353</v>
       </c>
     </row>
     <row r="38">
@@ -15248,7 +15246,7 @@
       </c>
       <c r="F38" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B38)*D38/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G38" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B38)*D38/$N$18,0)</f>
@@ -15268,7 +15266,7 @@
       </c>
       <c r="K38" s="11">
         <f>OreReserve-SUM($G$6:G38)</f>
-        <v>-54117.6470588235</v>
+        <v>205882.352941176</v>
       </c>
     </row>
     <row r="39">
@@ -15293,7 +15291,7 @@
       </c>
       <c r="F39" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B39)*D39/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G39" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B39)*D39/$N$18,0)</f>
@@ -15313,7 +15311,7 @@
       </c>
       <c r="K39" s="11">
         <f>OreReserve-SUM($G$6:G39)</f>
-        <v>-60000</v>
+        <v>200000</v>
       </c>
     </row>
     <row r="40">
@@ -15338,7 +15336,7 @@
       </c>
       <c r="F40" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B40)*D40/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G40" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B40)*D40/$N$18,0)</f>
@@ -15358,7 +15356,7 @@
       </c>
       <c r="K40" s="11">
         <f>OreReserve-SUM($G$6:G40)</f>
-        <v>-65882.3529411765</v>
+        <v>194117.647058824</v>
       </c>
     </row>
     <row r="41">
@@ -15383,7 +15381,7 @@
       </c>
       <c r="F41" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B41)*D41/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G41" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B41)*D41/$N$18,0)</f>
@@ -15403,7 +15401,7 @@
       </c>
       <c r="K41" s="11">
         <f>OreReserve-SUM($G$6:G41)</f>
-        <v>-71764.7058823529</v>
+        <v>188235.294117647</v>
       </c>
     </row>
     <row r="42">
@@ -15428,7 +15426,7 @@
       </c>
       <c r="F42" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B42)*D42/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G42" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B42)*D42/$N$18,0)</f>
@@ -15448,7 +15446,7 @@
       </c>
       <c r="K42" s="11">
         <f>OreReserve-SUM($G$6:G42)</f>
-        <v>-77647.0588235294</v>
+        <v>182352.941176471</v>
       </c>
     </row>
     <row r="43">
@@ -15473,7 +15471,7 @@
       </c>
       <c r="F43" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B43)*D43/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G43" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B43)*D43/$N$18,0)</f>
@@ -15493,7 +15491,7 @@
       </c>
       <c r="K43" s="11">
         <f>OreReserve-SUM($G$6:G43)</f>
-        <v>-83529.4117647059</v>
+        <v>176470.588235294</v>
       </c>
     </row>
     <row r="44">
@@ -15518,7 +15516,7 @@
       </c>
       <c r="F44" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B44)*D44/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G44" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B44)*D44/$N$18,0)</f>
@@ -15538,7 +15536,7 @@
       </c>
       <c r="K44" s="11">
         <f>OreReserve-SUM($G$6:G44)</f>
-        <v>-89411.7647058824</v>
+        <v>170588.235294118</v>
       </c>
     </row>
     <row r="45">
@@ -15563,7 +15561,7 @@
       </c>
       <c r="F45" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B45)*D45/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G45" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B45)*D45/$N$18,0)</f>
@@ -15583,7 +15581,7 @@
       </c>
       <c r="K45" s="11">
         <f>OreReserve-SUM($G$6:G45)</f>
-        <v>-95294.1176470588</v>
+        <v>164705.882352941</v>
       </c>
     </row>
     <row r="46">
@@ -15608,7 +15606,7 @@
       </c>
       <c r="F46" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B46)*D46/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G46" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B46)*D46/$N$18,0)</f>
@@ -15628,7 +15626,7 @@
       </c>
       <c r="K46" s="11">
         <f>OreReserve-SUM($G$6:G46)</f>
-        <v>-101176.470588235</v>
+        <v>158823.529411765</v>
       </c>
     </row>
     <row r="47">
@@ -15653,7 +15651,7 @@
       </c>
       <c r="F47" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B47)*D47/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G47" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B47)*D47/$N$18,0)</f>
@@ -15673,7 +15671,7 @@
       </c>
       <c r="K47" s="11">
         <f>OreReserve-SUM($G$6:G47)</f>
-        <v>-107058.823529412</v>
+        <v>152941.176470588</v>
       </c>
     </row>
     <row r="48">
@@ -15698,7 +15696,7 @@
       </c>
       <c r="F48" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B48)*D48/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G48" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B48)*D48/$N$18,0)</f>
@@ -15718,7 +15716,7 @@
       </c>
       <c r="K48" s="11">
         <f>OreReserve-SUM($G$6:G48)</f>
-        <v>-112941.176470588</v>
+        <v>147058.823529412</v>
       </c>
     </row>
     <row r="49">
@@ -15743,7 +15741,7 @@
       </c>
       <c r="F49" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B49)*D49/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G49" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B49)*D49/$N$18,0)</f>
@@ -15763,7 +15761,7 @@
       </c>
       <c r="K49" s="11">
         <f>OreReserve-SUM($G$6:G49)</f>
-        <v>-118823.529411765</v>
+        <v>141176.470588235</v>
       </c>
     </row>
     <row r="50">
@@ -15788,7 +15786,7 @@
       </c>
       <c r="F50" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B50)*D50/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G50" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B50)*D50/$N$18,0)</f>
@@ -15808,7 +15806,7 @@
       </c>
       <c r="K50" s="11">
         <f>OreReserve-SUM($G$6:G50)</f>
-        <v>-124705.882352941</v>
+        <v>135294.117647059</v>
       </c>
     </row>
     <row r="51">
@@ -15833,7 +15831,7 @@
       </c>
       <c r="F51" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B51)*D51/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G51" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B51)*D51/$N$18,0)</f>
@@ -15853,7 +15851,7 @@
       </c>
       <c r="K51" s="11">
         <f>OreReserve-SUM($G$6:G51)</f>
-        <v>-130588.235294118</v>
+        <v>129411.764705882</v>
       </c>
     </row>
     <row r="52">
@@ -15878,7 +15876,7 @@
       </c>
       <c r="F52" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B52)*D52/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G52" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B52)*D52/$N$18,0)</f>
@@ -15898,7 +15896,7 @@
       </c>
       <c r="K52" s="11">
         <f>OreReserve-SUM($G$6:G52)</f>
-        <v>-136470.588235294</v>
+        <v>123529.411764706</v>
       </c>
     </row>
     <row r="53">
@@ -15923,7 +15921,7 @@
       </c>
       <c r="F53" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B53)*D53/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G53" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B53)*D53/$N$18,0)</f>
@@ -15943,7 +15941,7 @@
       </c>
       <c r="K53" s="11">
         <f>OreReserve-SUM($G$6:G53)</f>
-        <v>-142352.941176471</v>
+        <v>117647.058823529</v>
       </c>
     </row>
     <row r="54">
@@ -15968,7 +15966,7 @@
       </c>
       <c r="F54" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B54)*D54/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G54" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B54)*D54/$N$18,0)</f>
@@ -15988,7 +15986,7 @@
       </c>
       <c r="K54" s="11">
         <f>OreReserve-SUM($G$6:G54)</f>
-        <v>-148235.294117647</v>
+        <v>111764.705882353</v>
       </c>
     </row>
     <row r="55">
@@ -16013,7 +16011,7 @@
       </c>
       <c r="F55" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B55)*D55/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G55" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B55)*D55/$N$18,0)</f>
@@ -16033,7 +16031,7 @@
       </c>
       <c r="K55" s="11">
         <f>OreReserve-SUM($G$6:G55)</f>
-        <v>-154117.647058824</v>
+        <v>105882.352941177</v>
       </c>
     </row>
     <row r="56">
@@ -16058,7 +16056,7 @@
       </c>
       <c r="F56" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B56)*D56/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G56" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B56)*D56/$N$18,0)</f>
@@ -16078,7 +16076,7 @@
       </c>
       <c r="K56" s="11">
         <f>OreReserve-SUM($G$6:G56)</f>
-        <v>-160000</v>
+        <v>100000</v>
       </c>
     </row>
     <row r="57">
@@ -16103,7 +16101,7 @@
       </c>
       <c r="F57" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B57)*D57/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G57" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B57)*D57/$N$18,0)</f>
@@ -16123,7 +16121,7 @@
       </c>
       <c r="K57" s="11">
         <f>OreReserve-SUM($G$6:G57)</f>
-        <v>-165882.352941176</v>
+        <v>94117.6470588236</v>
       </c>
     </row>
     <row r="58">
@@ -16148,7 +16146,7 @@
       </c>
       <c r="F58" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B58)*D58/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G58" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B58)*D58/$N$18,0)</f>
@@ -16168,7 +16166,7 @@
       </c>
       <c r="K58" s="11">
         <f>OreReserve-SUM($G$6:G58)</f>
-        <v>-171764.705882353</v>
+        <v>88235.2941176471</v>
       </c>
     </row>
     <row r="59">
@@ -16193,7 +16191,7 @@
       </c>
       <c r="F59" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B59)*D59/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G59" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B59)*D59/$N$18,0)</f>
@@ -16213,7 +16211,7 @@
       </c>
       <c r="K59" s="11">
         <f>OreReserve-SUM($G$6:G59)</f>
-        <v>-177647.058823529</v>
+        <v>82352.9411764706</v>
       </c>
     </row>
     <row r="60">
@@ -16238,7 +16236,7 @@
       </c>
       <c r="F60" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B60)*D60/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G60" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B60)*D60/$N$18,0)</f>
@@ -16258,7 +16256,7 @@
       </c>
       <c r="K60" s="11">
         <f>OreReserve-SUM($G$6:G60)</f>
-        <v>-183529.411764706</v>
+        <v>76470.5882352942</v>
       </c>
     </row>
     <row r="61">
@@ -16283,7 +16281,7 @@
       </c>
       <c r="F61" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B61)*D61/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G61" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B61)*D61/$N$18,0)</f>
@@ -16303,7 +16301,7 @@
       </c>
       <c r="K61" s="11">
         <f>OreReserve-SUM($G$6:G61)</f>
-        <v>-189411.764705882</v>
+        <v>70588.2352941177</v>
       </c>
     </row>
     <row r="62">
@@ -16328,7 +16326,7 @@
       </c>
       <c r="F62" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B62)*D62/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G62" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B62)*D62/$N$18,0)</f>
@@ -16348,7 +16346,7 @@
       </c>
       <c r="K62" s="11">
         <f>OreReserve-SUM($G$6:G62)</f>
-        <v>-195294.117647059</v>
+        <v>64705.8823529412</v>
       </c>
     </row>
     <row r="63">
@@ -16373,7 +16371,7 @@
       </c>
       <c r="F63" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B63)*D63/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G63" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B63)*D63/$N$18,0)</f>
@@ -16393,7 +16391,7 @@
       </c>
       <c r="K63" s="11">
         <f>OreReserve-SUM($G$6:G63)</f>
-        <v>-201176.470588235</v>
+        <v>58823.5294117648</v>
       </c>
     </row>
     <row r="64">
@@ -16418,7 +16416,7 @@
       </c>
       <c r="F64" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B64)*D64/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G64" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B64)*D64/$N$18,0)</f>
@@ -16438,7 +16436,7 @@
       </c>
       <c r="K64" s="11">
         <f>OreReserve-SUM($G$6:G64)</f>
-        <v>-207058.823529412</v>
+        <v>52941.1764705883</v>
       </c>
     </row>
     <row r="65">
@@ -16463,7 +16461,7 @@
       </c>
       <c r="F65" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$22:$H$22,B65)*D65/$N$18,0)</f>
-        <v>52941.1764705882</v>
+        <v>29411.7647058824</v>
       </c>
       <c r="G65" s="11">
         <f>IF($N$18&gt;0,INDEX('الخطة الفنية والإنتاج'!$D$23:$H$23,B65)*D65/$N$18,0)</f>
@@ -16483,7 +16481,7 @@
       </c>
       <c r="K65" s="11">
         <f>OreReserve-SUM($G$6:G65)</f>
-        <v>-212941.176470588</v>
+        <v>47058.8235294118</v>
       </c>
     </row>
     <row r="66">
@@ -16501,7 +16499,7 @@
       <c r="E66" s="12" t="n"/>
       <c r="F66" s="12">
         <f>SUM(F6:F65)</f>
-        <v>3176470.58823529</v>
+        <v>1764705.88235294</v>
       </c>
       <c r="G66" s="12">
         <f>SUM(G6:G65)</f>
